--- a/Edu/Linear_algebra/linal_session_task.xlsx
+++ b/Edu/Linear_algebra/linal_session_task.xlsx
@@ -5,16 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iTonyJah\DataScience\Edu\Linear_algebra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LysogorA\DataScience\Edu\Linear_algebra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14622D1-950D-4276-8BAF-F21B4B73FF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8E7406-2506-41C1-BA10-E37616AD4BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" r:id="rId1"/>
-    <sheet name="2" sheetId="2" r:id="rId2"/>
+    <sheet name="calc" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="81">
   <si>
     <t>Рабочая таблица с данными:</t>
   </si>
@@ -244,9 +243,6 @@
   </si>
   <si>
     <t>1.</t>
-  </si>
-  <si>
-    <t>2.</t>
   </si>
   <si>
     <t>Матрица признаков Х (5х6)</t>
@@ -288,7 +284,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -432,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -456,13 +452,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -475,7 +468,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{D5C79018-182E-4F9A-AB42-D02B8D90860C}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -497,8 +492,8 @@
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="914400" cy="228600"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -540,6 +535,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -604,7 +600,7 @@
                           <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
-                          <m:t>-1</m:t>
+                          <m:t>−1</m:t>
                         </m:r>
                       </m:sup>
                     </m:sSup>
@@ -647,7 +643,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -711,8 +707,8 @@
       <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="914400" cy="228600"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -754,6 +750,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -811,7 +808,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -875,8 +872,8 @@
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="654050" cy="228600"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -918,6 +915,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -950,7 +948,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -1014,8 +1012,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="546100" cy="228600"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="TextBox 6">
@@ -1057,6 +1055,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1102,7 +1101,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="TextBox 6">
@@ -1166,8 +1165,8 @@
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="914400" cy="228600"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -1209,6 +1208,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1266,7 +1266,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -1330,8 +1330,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="546100" cy="210507"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -1373,6 +1373,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1405,7 +1406,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -1481,8 +1482,8 @@
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="546100" cy="209550"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="TextBox 12">
@@ -1524,6 +1525,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1563,7 +1565,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="TextBox 12">
@@ -1627,8 +1629,8 @@
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="546100" cy="177800"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="TextBox 13">
@@ -1670,6 +1672,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1715,7 +1718,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="TextBox 13">
@@ -1779,8 +1782,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="546100" cy="209550"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -1822,6 +1825,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1861,7 +1865,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -1925,8 +1929,8 @@
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="546100" cy="190500"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="TextBox 16">
@@ -1968,6 +1972,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1988,7 +1993,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="TextBox 16">
@@ -2052,8 +2057,8 @@
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="596900" cy="203200"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="TextBox 25">
@@ -2095,6 +2100,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2152,7 +2158,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="TextBox 25">
@@ -2216,8 +2222,8 @@
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1431353" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -2259,6 +2265,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2377,7 +2384,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -2441,8 +2448,8 @@
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="991875" cy="461345"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="32" name="TextBox 31">
@@ -2484,6 +2491,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2646,7 +2654,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="32" name="TextBox 31">
@@ -2695,1730 +2703,6 @@
                 <a:t>(𝑥_𝑠𝑡 ) ⃗=(𝑥_𝑐𝑒𝑛𝑡 ) ⃗/(\|(𝑥_𝑐𝑒𝑛𝑡 ) ⃗\|)</a:t>
               </a:r>
               <a:endParaRPr lang="ru-RU" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="914400" cy="228600"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2" name="TextBox 1">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{929052F3-C66C-4F86-8233-773967A1B565}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="25400" y="2533650"/>
-              <a:ext cx="914400" cy="228600"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSup>
-                      <m:sSupPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSupPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>(</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑋</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sup>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑇</m:t>
-                        </m:r>
-                      </m:sup>
-                    </m:sSup>
-                    <m:sSup>
-                      <m:sSupPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSupPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑋</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>)</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sup>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>-1</m:t>
-                        </m:r>
-                      </m:sup>
-                    </m:sSup>
-                    <m:sSup>
-                      <m:sSupPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSupPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑋</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sup>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑇</m:t>
-                        </m:r>
-                      </m:sup>
-                    </m:sSup>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑌</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2" name="TextBox 1">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{929052F3-C66C-4F86-8233-773967A1B565}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="25400" y="2533650"/>
-              <a:ext cx="914400" cy="228600"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>〖(𝑋〗^𝑇 〖𝑋)〗^(-1) 𝑋^𝑇 𝑌</a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>374650</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="914400" cy="228600"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0D48B6F-E69B-46F6-980C-4DA63F9FB042}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2203450" y="4387850"/>
-              <a:ext cx="914400" cy="228600"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSup>
-                      <m:sSupPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSupPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑋</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sup>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑇</m:t>
-                        </m:r>
-                      </m:sup>
-                    </m:sSup>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>(</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑋𝑌</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>)</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0D48B6F-E69B-46F6-980C-4DA63F9FB042}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2203450" y="4387850"/>
-              <a:ext cx="914400" cy="228600"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑋^𝑇 (𝑋𝑌)</a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="654050" cy="228600"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6943E3A2-EB3E-4BBE-A59D-2C64BE30F571}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2952750" y="4775200"/>
-              <a:ext cx="654050" cy="228600"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑢</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>=</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑋𝑌</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6943E3A2-EB3E-4BBE-A59D-2C64BE30F571}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2952750" y="4775200"/>
-              <a:ext cx="654050" cy="228600"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑢=𝑋𝑌</a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="546100" cy="228600"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0ECADD3-9A6F-4549-9EC1-91A86F3AF6D2}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4267200" y="4781550"/>
-              <a:ext cx="546100" cy="228600"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSup>
-                      <m:sSupPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSupPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑋</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sup>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑇</m:t>
-                        </m:r>
-                      </m:sup>
-                    </m:sSup>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑢</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0ECADD3-9A6F-4549-9EC1-91A86F3AF6D2}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4267200" y="4781550"/>
-              <a:ext cx="546100" cy="228600"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑋^𝑇 𝑢</a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>355600</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="914400" cy="228600"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{718B0606-25A2-4171-807E-88FA812B1EEB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2794000" y="5137150"/>
-              <a:ext cx="914400" cy="228600"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSup>
-                      <m:sSupPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSupPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑀</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>=</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑋</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sup>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑇</m:t>
-                        </m:r>
-                      </m:sup>
-                    </m:sSup>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑋</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{718B0606-25A2-4171-807E-88FA812B1EEB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2794000" y="5137150"/>
-              <a:ext cx="914400" cy="228600"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>〖𝑀=𝑋〗^𝑇 𝑋</a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="546100" cy="210507"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="7" name="TextBox 6">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81E014EF-31B1-460A-9580-4F8ADB5678C0}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4267200" y="5149850"/>
-              <a:ext cx="546100" cy="210507"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:solidFill>
-                          <a:schemeClr val="tx1"/>
-                        </a:solidFill>
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        <a:ea typeface="+mn-ea"/>
-                        <a:cs typeface="+mn-cs"/>
-                      </a:rPr>
-                      <m:t>𝑀𝑌</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1400" b="0" i="1">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:endParaRPr>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="7" name="TextBox 6">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81E014EF-31B1-460A-9580-4F8ADB5678C0}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4267200" y="5149850"/>
-              <a:ext cx="546100" cy="210507"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:rPr>
-                <a:t>𝑀𝑌</a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1400" b="0" i="1">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:endParaRPr>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="546100" cy="209550"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="TextBox 7">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C01BE8A9-A19D-46B2-9E64-7EDC1BDCBC4B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3657600" y="7924800"/>
-              <a:ext cx="546100" cy="209550"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSup>
-                      <m:sSupPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSupPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑋</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sup>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑇</m:t>
-                        </m:r>
-                      </m:sup>
-                    </m:sSup>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="TextBox 7">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C01BE8A9-A19D-46B2-9E64-7EDC1BDCBC4B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3657600" y="7924800"/>
-              <a:ext cx="546100" cy="209550"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑋^𝑇</a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="546100" cy="177800"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="9" name="TextBox 8">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{746C753A-AAE2-4D49-A996-E1949D6FEA0A}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="7912100"/>
-              <a:ext cx="546100" cy="177800"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSup>
-                      <m:sSupPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSupPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑋</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sup>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑇</m:t>
-                        </m:r>
-                      </m:sup>
-                    </m:sSup>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑢</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="9" name="TextBox 8">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{746C753A-AAE2-4D49-A996-E1949D6FEA0A}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="7912100"/>
-              <a:ext cx="546100" cy="177800"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑋^𝑇 𝑢</a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="546100" cy="209550"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="TextBox 9">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0DDCD70-35D5-46BD-AB10-C7EA98BB39C2}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3695700" y="9220200"/>
-              <a:ext cx="546100" cy="209550"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSup>
-                      <m:sSupPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSupPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑋</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sup>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑇</m:t>
-                        </m:r>
-                      </m:sup>
-                    </m:sSup>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="TextBox 9">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0DDCD70-35D5-46BD-AB10-C7EA98BB39C2}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3695700" y="9220200"/>
-              <a:ext cx="546100" cy="209550"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑋^𝑇</a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="546100" cy="190500"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="TextBox 10">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDE7F6EA-57FD-4F2B-BA74-9E7734625934}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="11214100"/>
-              <a:ext cx="546100" cy="190500"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑀𝑌</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="TextBox 10">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDE7F6EA-57FD-4F2B-BA74-9E7734625934}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="11214100"/>
-              <a:ext cx="546100" cy="190500"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑀𝑌</a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="596900" cy="203200"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="TextBox 11">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D44DF6A-3904-42AD-9DE7-5B51625B8468}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6350" y="12515850"/>
-              <a:ext cx="596900" cy="203200"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSup>
-                      <m:sSupPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSupPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑋</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sup>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑇</m:t>
-                        </m:r>
-                      </m:sup>
-                    </m:sSup>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>(</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑋𝑌</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>)</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="TextBox 11">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D44DF6A-3904-42AD-9DE7-5B51625B8468}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6350" y="12515850"/>
-              <a:ext cx="596900" cy="203200"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑋^𝑇 (𝑋𝑌)</a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1400" i="1"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -4747,14 +3031,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472F5A48-0D57-45D1-AF67-58628EB4925B}">
   <dimension ref="A1:L109"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4777,7 +3061,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -4800,7 +3084,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -4823,7 +3107,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -4846,7 +3130,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -4869,7 +3153,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -4892,32 +3176,32 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="23" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -4925,7 +3209,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>3</v>
       </c>
@@ -4939,7 +3223,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>1</v>
       </c>
@@ -4953,7 +3237,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>2</v>
       </c>
@@ -4967,22 +3251,22 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -4990,12 +3274,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -5003,42 +3287,42 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>28</v>
       </c>
@@ -5049,7 +3333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <f>F38*J$38+G38*J$39+H38*J$40</f>
         <v>93900</v>
@@ -5071,7 +3355,7 @@
       </c>
       <c r="L38" s="8"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <f t="shared" ref="A39:A40" si="0">F39*J$38+G39*J$39+H39*J$40</f>
         <v>52100</v>
@@ -5093,7 +3377,7 @@
       </c>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <f t="shared" si="0"/>
         <v>80200</v>
@@ -5115,23 +3399,23 @@
       </c>
       <c r="L40" s="8"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B41" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="J43" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
         <f>F44*J$44+G44*J$45+H44*J$46</f>
         <v>494200</v>
@@ -5153,7 +3437,7 @@
       </c>
       <c r="L44" s="8"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
         <f t="shared" ref="A45:A46" si="1">F45*J$44+G45*J$45+H45*J$46</f>
         <v>9960900</v>
@@ -5175,7 +3459,7 @@
       </c>
       <c r="L45" s="8"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
         <f t="shared" si="1"/>
         <v>494200</v>
@@ -5197,22 +3481,22 @@
       </c>
       <c r="L46" s="8"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B47" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B50" s="6" t="s">
         <v>43</v>
       </c>
@@ -5220,7 +3504,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -5252,7 +3536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="12">
         <f t="shared" ref="A52:A53" si="4">$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -5284,7 +3568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="12">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -5316,12 +3600,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>38</v>
       </c>
@@ -5332,7 +3616,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -5355,7 +3639,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
         <f>$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -5378,7 +3662,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="12">
         <f>$F53*J$51+$G53*J$52+$H53*J$53</f>
         <v>14</v>
@@ -5401,19 +3685,19 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B59" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>51</v>
       </c>
       <c r="B60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G61" s="6" t="s">
         <v>43</v>
       </c>
@@ -5421,12 +3705,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="12">
         <f>F62*J$62+G62*J$63+H62*J$64</f>
         <v>494200</v>
       </c>
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="8" t="s">
         <v>53</v>
       </c>
       <c r="F62" s="12">
@@ -5442,12 +3726,12 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="12">
         <f t="shared" ref="A63:A64" si="5">F63*J$62+G63*J$63+H63*J$64</f>
         <v>9960900</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="8" t="s">
         <v>52</v>
       </c>
       <c r="F63" s="12">
@@ -5463,12 +3747,12 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="12">
         <f t="shared" si="5"/>
         <v>494200</v>
       </c>
-      <c r="B64" s="15" t="s">
+      <c r="B64" s="8" t="s">
         <v>53</v>
       </c>
       <c r="F64" s="12">
@@ -5484,117 +3768,117 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B65" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B67" s="15"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C68" s="16" t="s">
+      <c r="B67" s="8"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C68" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="12">
         <v>494200</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="C69" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="12">
         <v>9960900</v>
       </c>
-      <c r="C70" s="17" t="s">
+      <c r="C70" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="12">
         <v>494200</v>
       </c>
-      <c r="C71" s="17" t="s">
+      <c r="C71" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="23" x14ac:dyDescent="0.35">
-      <c r="A74" s="18" t="s">
+    <row r="74" spans="1:3" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A74" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>1</v>
       </c>
@@ -5617,19 +3901,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C90" s="19"/>
-      <c r="D90" s="19"/>
-      <c r="E90" s="19" t="s">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C90" s="16"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F90" s="16"/>
+      <c r="G90" s="16"/>
+      <c r="I90" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F90" s="19"/>
-      <c r="G90" s="19"/>
-      <c r="I90" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B91" s="7">
         <v>3</v>
       </c>
@@ -5652,7 +3936,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B92" s="7">
         <v>1</v>
       </c>
@@ -5675,7 +3959,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B93" s="7">
         <v>2</v>
       </c>
@@ -5698,7 +3982,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B94" s="7">
         <v>3</v>
       </c>
@@ -5721,7 +4005,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B95" s="7">
         <v>1</v>
       </c>
@@ -5744,19 +4028,19 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>77</v>
       </c>
       <c r="B99">
         <f>SUM(B91:B95)</f>
@@ -5787,15 +4071,15 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B100">
         <f>B99/5</f>
         <v>2</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="17">
         <f t="shared" ref="C100:I100" si="7">C99/5</f>
         <v>45.2</v>
       </c>
@@ -5803,11 +4087,11 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="17">
         <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="17">
         <f t="shared" si="7"/>
         <v>0.8</v>
       </c>
@@ -5820,17 +4104,17 @@
         <v>2440</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B102" s="7">
         <f>B91-B$100</f>
         <v>1</v>
       </c>
-      <c r="C102" s="20">
+      <c r="C102" s="17">
         <f t="shared" ref="C102:G102" si="8">C91-C$100</f>
         <v>5.7999999999999972</v>
       </c>
@@ -5838,11 +4122,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="E102" s="7">
+      <c r="E102" s="17">
         <f t="shared" si="8"/>
         <v>-0.2</v>
       </c>
-      <c r="F102" s="7">
+      <c r="F102" s="17">
         <f t="shared" si="8"/>
         <v>0.19999999999999996</v>
       </c>
@@ -5855,12 +4139,12 @@
         <v>-240</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B103" s="7">
         <f t="shared" ref="B103:G103" si="10">B92-B$100</f>
         <v>-1</v>
       </c>
-      <c r="C103" s="20">
+      <c r="C103" s="17">
         <f t="shared" si="10"/>
         <v>-15.200000000000003</v>
       </c>
@@ -5868,11 +4152,11 @@
         <f t="shared" si="10"/>
         <v>-1</v>
       </c>
-      <c r="E103" s="7">
+      <c r="E103" s="17">
         <f t="shared" si="10"/>
         <v>-0.2</v>
       </c>
-      <c r="F103" s="7">
+      <c r="F103" s="17">
         <f t="shared" si="10"/>
         <v>0.19999999999999996</v>
       </c>
@@ -5885,12 +4169,12 @@
         <v>-840</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B104" s="7">
         <f t="shared" ref="B104:G104" si="12">B93-B$100</f>
         <v>0</v>
       </c>
-      <c r="C104" s="20">
+      <c r="C104" s="17">
         <f t="shared" si="12"/>
         <v>-0.20000000000000284</v>
       </c>
@@ -5898,11 +4182,11 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="E104" s="7">
+      <c r="E104" s="17">
         <f t="shared" si="12"/>
         <v>-0.2</v>
       </c>
-      <c r="F104" s="7">
+      <c r="F104" s="17">
         <f t="shared" si="12"/>
         <v>0.19999999999999996</v>
       </c>
@@ -5915,12 +4199,12 @@
         <v>-540</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B105" s="7">
         <f t="shared" ref="B105:G105" si="14">B94-B$100</f>
         <v>1</v>
       </c>
-      <c r="C105" s="20">
+      <c r="C105" s="17">
         <f t="shared" si="14"/>
         <v>9.7999999999999972</v>
       </c>
@@ -5928,11 +4212,11 @@
         <f t="shared" si="14"/>
         <v>-1</v>
       </c>
-      <c r="E105" s="7">
+      <c r="E105" s="17">
         <f t="shared" si="14"/>
         <v>-0.2</v>
       </c>
-      <c r="F105" s="7">
+      <c r="F105" s="17">
         <f t="shared" si="14"/>
         <v>0.19999999999999996</v>
       </c>
@@ -5945,12 +4229,12 @@
         <v>-440</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B106" s="7">
         <f t="shared" ref="B106:G106" si="16">B95-B$100</f>
         <v>-1</v>
       </c>
-      <c r="C106" s="20">
+      <c r="C106" s="17">
         <f t="shared" si="16"/>
         <v>-0.20000000000000284</v>
       </c>
@@ -5958,11 +4242,11 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="E106" s="7">
+      <c r="E106" s="17">
         <f t="shared" si="16"/>
         <v>0.8</v>
       </c>
-      <c r="F106" s="7">
+      <c r="F106" s="17">
         <f t="shared" si="16"/>
         <v>-0.8</v>
       </c>
@@ -5975,17 +4259,17 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B109">
         <f>(B102^2+B103^2+B104^2+B105^2+B106^2)^(1/2)</f>
         <v>2</v>
@@ -6017,1002 +4301,6 @@
       <c r="I109">
         <f t="shared" si="18"/>
         <v>2343.5016535091245</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D34DEDF-4E36-4037-8F0A-6A5E0D2037C2}">
-  <dimension ref="A1:L94"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2">
-        <v>51</v>
-      </c>
-      <c r="C3" s="2">
-        <v>3</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="3">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3">
-        <v>30</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3">
-        <v>45</v>
-      </c>
-      <c r="C5" s="3">
-        <v>2</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="3">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3">
-        <v>55</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3">
-        <v>45</v>
-      </c>
-      <c r="C7" s="3">
-        <v>3</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="23" x14ac:dyDescent="0.5">
-      <c r="A9" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="2">
-        <v>3</v>
-      </c>
-      <c r="B18" s="2">
-        <v>51</v>
-      </c>
-      <c r="C18" s="2">
-        <v>3</v>
-      </c>
-      <c r="E18" s="2">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="3">
-        <v>1</v>
-      </c>
-      <c r="B19" s="3">
-        <v>30</v>
-      </c>
-      <c r="C19" s="3">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="3">
-        <v>2</v>
-      </c>
-      <c r="B20" s="3">
-        <v>45</v>
-      </c>
-      <c r="C20" s="3">
-        <v>2</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="16" x14ac:dyDescent="0.4">
-      <c r="A33" s="14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A37" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38" s="7">
-        <f>F38*J$38+G38*J$39+H38*J$40</f>
-        <v>93900</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F38" s="7">
-        <v>3</v>
-      </c>
-      <c r="G38" s="7">
-        <v>51</v>
-      </c>
-      <c r="H38" s="7">
-        <v>3</v>
-      </c>
-      <c r="J38" s="7">
-        <v>2200</v>
-      </c>
-      <c r="L38" s="8"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A39" s="7">
-        <f t="shared" ref="A39:A40" si="0">F39*J$38+G39*J$39+H39*J$40</f>
-        <v>52100</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" s="7">
-        <v>1</v>
-      </c>
-      <c r="G39" s="7">
-        <v>30</v>
-      </c>
-      <c r="H39" s="7">
-        <v>1</v>
-      </c>
-      <c r="J39" s="7">
-        <v>1600</v>
-      </c>
-      <c r="L39" s="8"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A40" s="7">
-        <f t="shared" si="0"/>
-        <v>80200</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F40" s="7">
-        <v>2</v>
-      </c>
-      <c r="G40" s="7">
-        <v>45</v>
-      </c>
-      <c r="H40" s="7">
-        <v>2</v>
-      </c>
-      <c r="J40" s="7">
-        <v>1900</v>
-      </c>
-      <c r="L40" s="8"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B41" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43" s="10"/>
-      <c r="J43" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A44" s="12">
-        <f>F44*J$44+G44*J$45+H44*J$46</f>
-        <v>494200</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F44" s="7">
-        <v>3</v>
-      </c>
-      <c r="G44" s="7">
-        <v>1</v>
-      </c>
-      <c r="H44" s="7">
-        <v>2</v>
-      </c>
-      <c r="J44" s="12">
-        <v>93900</v>
-      </c>
-      <c r="L44" s="8"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
-        <f t="shared" ref="A45:A46" si="1">F45*J$44+G45*J$45+H45*J$46</f>
-        <v>9960900</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F45" s="7">
-        <v>51</v>
-      </c>
-      <c r="G45" s="7">
-        <v>30</v>
-      </c>
-      <c r="H45" s="7">
-        <v>45</v>
-      </c>
-      <c r="J45" s="12">
-        <v>52100</v>
-      </c>
-      <c r="L45" s="8"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
-        <f t="shared" si="1"/>
-        <v>494200</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F46" s="7">
-        <v>3</v>
-      </c>
-      <c r="G46" s="7">
-        <v>1</v>
-      </c>
-      <c r="H46" s="7">
-        <v>2</v>
-      </c>
-      <c r="J46" s="12">
-        <v>80200</v>
-      </c>
-      <c r="L46" s="8"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B47" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A48" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K50" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A51" s="12">
-        <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
-        <v>14</v>
-      </c>
-      <c r="B51" s="12">
-        <f t="shared" ref="B51:C53" si="2">$F51*K$51+$G51*K$52+$H51*K$53</f>
-        <v>273</v>
-      </c>
-      <c r="C51" s="12">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="F51" s="7">
-        <v>3</v>
-      </c>
-      <c r="G51" s="7">
-        <v>1</v>
-      </c>
-      <c r="H51" s="7">
-        <v>2</v>
-      </c>
-      <c r="J51" s="7">
-        <v>3</v>
-      </c>
-      <c r="K51" s="7">
-        <v>51</v>
-      </c>
-      <c r="L51" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A52" s="12">
-        <f t="shared" ref="A52:A53" si="3">$F52*J$51+$G52*J$52+$H52*J$53</f>
-        <v>273</v>
-      </c>
-      <c r="B52" s="12">
-        <f t="shared" si="2"/>
-        <v>5526</v>
-      </c>
-      <c r="C52" s="12">
-        <f t="shared" si="2"/>
-        <v>273</v>
-      </c>
-      <c r="F52" s="7">
-        <v>51</v>
-      </c>
-      <c r="G52" s="7">
-        <v>30</v>
-      </c>
-      <c r="H52" s="7">
-        <v>45</v>
-      </c>
-      <c r="J52" s="7">
-        <v>1</v>
-      </c>
-      <c r="K52" s="7">
-        <v>30</v>
-      </c>
-      <c r="L52" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A53" s="12">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="B53" s="12">
-        <f t="shared" si="2"/>
-        <v>273</v>
-      </c>
-      <c r="C53" s="12">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="F53" s="7">
-        <v>3</v>
-      </c>
-      <c r="G53" s="7">
-        <v>1</v>
-      </c>
-      <c r="H53" s="7">
-        <v>2</v>
-      </c>
-      <c r="J53" s="7">
-        <v>2</v>
-      </c>
-      <c r="K53" s="7">
-        <v>45</v>
-      </c>
-      <c r="L53" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>38</v>
-      </c>
-      <c r="E55" t="s">
-        <v>39</v>
-      </c>
-      <c r="I55" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A56" s="12">
-        <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
-        <v>14</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E56" s="12">
-        <f>$F51*K$51+$G51*K$52+$H51*K$53</f>
-        <v>273</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I56" s="12">
-        <f>$F51*L$51+$G51*L$52+$H51*L$53</f>
-        <v>14</v>
-      </c>
-      <c r="J56" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A57" s="12">
-        <f>$F52*J$51+$G52*J$52+$H52*J$53</f>
-        <v>273</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E57" s="12">
-        <f>$F52*K$51+$G52*K$52+$H52*K$53</f>
-        <v>5526</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I57" s="12">
-        <f>$F52*L$51+$G52*L$52+$H52*L$53</f>
-        <v>273</v>
-      </c>
-      <c r="J57" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A58" s="12">
-        <f>$F53*J$51+$G53*J$52+$H53*J$53</f>
-        <v>14</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E58" s="12">
-        <f>$F53*K$51+$G53*K$52+$H53*K$53</f>
-        <v>273</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I58" s="12">
-        <f>$F53*L$51+$G53*L$52+$H53*L$53</f>
-        <v>14</v>
-      </c>
-      <c r="J58" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B59" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60" s="8"/>
-      <c r="F60" s="8"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="G61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J61" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A62" s="12">
-        <f>F62*J$62+G62*J$63+H62*J$64</f>
-        <v>494200</v>
-      </c>
-      <c r="B62" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F62" s="12">
-        <v>14</v>
-      </c>
-      <c r="G62" s="12">
-        <v>273</v>
-      </c>
-      <c r="H62" s="12">
-        <v>14</v>
-      </c>
-      <c r="J62" s="7">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A63" s="12">
-        <f t="shared" ref="A63:A64" si="4">F63*J$62+G63*J$63+H63*J$64</f>
-        <v>9960900</v>
-      </c>
-      <c r="B63" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F63" s="12">
-        <v>273</v>
-      </c>
-      <c r="G63" s="12">
-        <v>5526</v>
-      </c>
-      <c r="H63" s="12">
-        <v>273</v>
-      </c>
-      <c r="J63" s="7">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A64" s="12">
-        <f t="shared" si="4"/>
-        <v>494200</v>
-      </c>
-      <c r="B64" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F64" s="12">
-        <v>14</v>
-      </c>
-      <c r="G64" s="12">
-        <v>273</v>
-      </c>
-      <c r="H64" s="12">
-        <v>14</v>
-      </c>
-      <c r="J64" s="7">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B65" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B67" s="15"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C68" s="16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="12">
-        <v>494200</v>
-      </c>
-      <c r="C69" s="16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="12">
-        <v>9960900</v>
-      </c>
-      <c r="C70" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="12">
-        <v>494200</v>
-      </c>
-      <c r="C71" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="23" x14ac:dyDescent="0.35">
-      <c r="A74" s="18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A84" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A85" s="13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>1</v>
-      </c>
-      <c r="B86" t="s">
-        <v>2</v>
-      </c>
-      <c r="C86" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" t="s">
-        <v>4</v>
-      </c>
-      <c r="E86" t="s">
-        <v>5</v>
-      </c>
-      <c r="F86" t="s">
-        <v>6</v>
-      </c>
-      <c r="H86" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B87" s="19"/>
-      <c r="C87" s="19"/>
-      <c r="D87" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E87" s="19"/>
-      <c r="F87" s="19"/>
-      <c r="H87" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A88" s="7">
-        <v>3</v>
-      </c>
-      <c r="B88" s="7">
-        <v>51</v>
-      </c>
-      <c r="C88" s="7">
-        <v>3</v>
-      </c>
-      <c r="D88" s="7">
-        <v>0</v>
-      </c>
-      <c r="E88" s="7">
-        <v>1</v>
-      </c>
-      <c r="F88" s="7">
-        <v>0</v>
-      </c>
-      <c r="H88" s="7">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A89" s="7">
-        <v>1</v>
-      </c>
-      <c r="B89" s="7">
-        <v>30</v>
-      </c>
-      <c r="C89" s="7">
-        <v>1</v>
-      </c>
-      <c r="D89" s="7">
-        <v>0</v>
-      </c>
-      <c r="E89" s="7">
-        <v>1</v>
-      </c>
-      <c r="F89" s="7">
-        <v>0</v>
-      </c>
-      <c r="H89" s="7">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A90" s="7">
-        <v>2</v>
-      </c>
-      <c r="B90" s="7">
-        <v>45</v>
-      </c>
-      <c r="C90" s="7">
-        <v>2</v>
-      </c>
-      <c r="D90" s="7">
-        <v>0</v>
-      </c>
-      <c r="E90" s="7">
-        <v>1</v>
-      </c>
-      <c r="F90" s="7">
-        <v>0</v>
-      </c>
-      <c r="H90" s="7">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A91" s="7">
-        <v>3</v>
-      </c>
-      <c r="B91" s="7">
-        <v>55</v>
-      </c>
-      <c r="C91" s="7">
-        <v>1</v>
-      </c>
-      <c r="D91" s="7">
-        <v>0</v>
-      </c>
-      <c r="E91" s="7">
-        <v>1</v>
-      </c>
-      <c r="F91" s="7">
-        <v>0</v>
-      </c>
-      <c r="H91" s="7">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A92" s="7">
-        <v>1</v>
-      </c>
-      <c r="B92" s="7">
-        <v>45</v>
-      </c>
-      <c r="C92" s="7">
-        <v>3</v>
-      </c>
-      <c r="D92" s="7">
-        <v>1</v>
-      </c>
-      <c r="E92" s="7">
-        <v>0</v>
-      </c>
-      <c r="F92" s="7">
-        <v>0</v>
-      </c>
-      <c r="H92" s="7">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A94" s="13" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Edu/Linear_algebra/linal_session_task.xlsx
+++ b/Edu/Linear_algebra/linal_session_task.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LysogorA\DataScience\Edu\Linear_algebra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8E7406-2506-41C1-BA10-E37616AD4BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0538AAFC-DB83-4BFC-B05A-A9F8A28FD179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
+    <workbookView xWindow="3240" yWindow="1125" windowWidth="16455" windowHeight="12390" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="86">
   <si>
     <t>Рабочая таблица с данными:</t>
   </si>
@@ -279,6 +279,21 @@
   </si>
   <si>
     <t>Длина вектора:</t>
+  </si>
+  <si>
+    <t>Стандартизированные:</t>
+  </si>
+  <si>
+    <t>\displaystyle \frac{2 \sqrt{2255}}{5}</t>
+  </si>
+  <si>
+    <t>(29/5, -76/5, -1/5, 49/5, -1/5)</t>
+  </si>
+  <si>
+    <t>90-14</t>
+  </si>
+  <si>
+    <t>90+14</t>
   </si>
 </sst>
 </file>
@@ -428,7 +443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -463,6 +478,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3030,8 +3046,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472F5A48-0D57-45D1-AF67-58628EB4925B}">
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:AC119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="25" max="25" width="12.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
@@ -4028,17 +4047,17 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>76</v>
       </c>
@@ -4071,7 +4090,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>77</v>
       </c>
@@ -4104,12 +4123,12 @@
         <v>2440</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B102" s="7">
         <f>B91-B$100</f>
         <v>1</v>
@@ -4138,8 +4157,14 @@
         <f t="shared" ref="I102" si="9">I91-I$100</f>
         <v>-240</v>
       </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M102" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z102">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B103" s="7">
         <f t="shared" ref="B103:G103" si="10">B92-B$100</f>
         <v>-1</v>
@@ -4169,7 +4194,7 @@
         <v>-840</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B104" s="7">
         <f t="shared" ref="B104:G104" si="12">B93-B$100</f>
         <v>0</v>
@@ -4198,8 +4223,15 @@
         <f t="shared" ref="I104" si="13">I93-I$100</f>
         <v>-540</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M104">
+        <v>29</v>
+      </c>
+      <c r="N104">
+        <f>M104^2</f>
+        <v>841</v>
+      </c>
+    </row>
+    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B105" s="7">
         <f t="shared" ref="B105:G105" si="14">B94-B$100</f>
         <v>1</v>
@@ -4228,83 +4260,435 @@
         <f t="shared" ref="I105" si="15">I94-I$100</f>
         <v>-440</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M105">
+        <v>76</v>
+      </c>
+      <c r="N105">
+        <f t="shared" ref="N105:N108" si="16">M105^2</f>
+        <v>5776</v>
+      </c>
+      <c r="R105">
+        <f>5*451</f>
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B106" s="7">
-        <f t="shared" ref="B106:G106" si="16">B95-B$100</f>
+        <f t="shared" ref="B106:G106" si="17">B95-B$100</f>
         <v>-1</v>
       </c>
       <c r="C106" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="D106" s="7">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="E106" s="17">
+        <f t="shared" si="17"/>
+        <v>0.8</v>
+      </c>
+      <c r="F106" s="17">
+        <f t="shared" si="17"/>
+        <v>-0.8</v>
+      </c>
+      <c r="G106" s="7">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="I106" s="7">
+        <f t="shared" ref="I106" si="18">I95-I$100</f>
+        <v>2060</v>
+      </c>
+      <c r="M106">
+        <v>1</v>
+      </c>
+      <c r="N106">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="E106" s="17">
-        <f t="shared" si="16"/>
-        <v>0.8</v>
-      </c>
-      <c r="F106" s="17">
-        <f t="shared" si="16"/>
-        <v>-0.8</v>
-      </c>
-      <c r="G106" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I106" s="7">
-        <f t="shared" ref="I106" si="17">I95-I$100</f>
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M107">
+        <v>49</v>
+      </c>
+      <c r="N107">
+        <f t="shared" si="16"/>
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M108">
+        <v>1</v>
+      </c>
+      <c r="N108">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="V108">
+        <v>9020</v>
+      </c>
+      <c r="W108">
+        <v>25</v>
+      </c>
+      <c r="X108">
+        <f>V108/W108</f>
+        <v>360.8</v>
+      </c>
+      <c r="Y108">
+        <f>SQRT(X108)</f>
+        <v>18.994736112934024</v>
+      </c>
+    </row>
+    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B109">
         <f>(B102^2+B103^2+B104^2+B105^2+B106^2)^(1/2)</f>
         <v>2</v>
       </c>
       <c r="C109">
-        <f t="shared" ref="C109:I109" si="18">(C102^2+C103^2+C104^2+C105^2+C106^2)^(1/2)</f>
+        <f t="shared" ref="C109:I109" si="19">(C102^2+C103^2+C104^2+C105^2+C106^2)^(1/2)</f>
         <v>18.994736112934028</v>
       </c>
       <c r="D109">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="E109">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.89442719099991597</v>
       </c>
       <c r="F109">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.89442719099991586</v>
       </c>
       <c r="G109">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H109">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I109">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2343.5016535091245</v>
+      </c>
+      <c r="N109">
+        <f>SUM(N104:N108)</f>
+        <v>9020</v>
+      </c>
+      <c r="P109">
+        <v>2255</v>
+      </c>
+      <c r="Q109">
+        <v>4</v>
+      </c>
+      <c r="R109">
+        <f>Q109*P109</f>
+        <v>9020</v>
+      </c>
+      <c r="X109">
+        <v>441</v>
+      </c>
+      <c r="Y109">
+        <f>SQRT(X109)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>81</v>
+      </c>
+      <c r="X110" s="17">
+        <f>X109-X108</f>
+        <v>80.199999999999989</v>
+      </c>
+      <c r="Y110">
+        <f>SQRT(X110)</f>
+        <v>8.9554452708952432</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B111" s="18">
+        <f>B102/B$109</f>
+        <v>0.5</v>
+      </c>
+      <c r="C111" s="18">
+        <f t="shared" ref="C111:I111" si="20">C102/C$109</f>
+        <v>0.30534775347842924</v>
+      </c>
+      <c r="D111" s="18">
+        <f t="shared" si="20"/>
+        <v>0.5</v>
+      </c>
+      <c r="E111" s="18">
+        <f t="shared" si="20"/>
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="F111" s="18">
+        <f t="shared" si="20"/>
+        <v>0.22360679774997894</v>
+      </c>
+      <c r="G111" s="18"/>
+      <c r="H111" s="18"/>
+      <c r="I111" s="18">
+        <f t="shared" si="20"/>
+        <v>-0.10241085157359611</v>
+      </c>
+    </row>
+    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B112" s="18">
+        <f t="shared" ref="B112:I115" si="21">B103/B$109</f>
+        <v>-0.5</v>
+      </c>
+      <c r="C112" s="18">
+        <f t="shared" si="21"/>
+        <v>-0.80022169877105653</v>
+      </c>
+      <c r="D112" s="18">
+        <f t="shared" si="21"/>
+        <v>-0.5</v>
+      </c>
+      <c r="E112" s="18">
+        <f t="shared" si="21"/>
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="F112" s="18">
+        <f t="shared" si="21"/>
+        <v>0.22360679774997894</v>
+      </c>
+      <c r="G112" s="18"/>
+      <c r="H112" s="18"/>
+      <c r="I112" s="18">
+        <f t="shared" si="21"/>
+        <v>-0.35843798050758635</v>
+      </c>
+      <c r="N112" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="113" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B113" s="18">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="C113" s="18">
+        <f t="shared" si="21"/>
+        <v>-1.0529232878566681E-2</v>
+      </c>
+      <c r="D113" s="18">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="E113" s="18">
+        <f t="shared" si="21"/>
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="F113" s="18">
+        <f t="shared" si="21"/>
+        <v>0.22360679774997894</v>
+      </c>
+      <c r="G113" s="18"/>
+      <c r="H113" s="18"/>
+      <c r="I113" s="18">
+        <f t="shared" si="21"/>
+        <v>-0.23042441604059125</v>
+      </c>
+      <c r="O113">
+        <f>O114</f>
+        <v>2255</v>
+      </c>
+      <c r="R113">
+        <f>38^2</f>
+        <v>1444</v>
+      </c>
+      <c r="S113">
+        <f>R113-O113</f>
+        <v>-811</v>
+      </c>
+      <c r="T113">
+        <f>SQRT(-S113)</f>
+        <v>28.478061731796284</v>
+      </c>
+    </row>
+    <row r="114" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B114" s="18">
+        <f t="shared" si="21"/>
+        <v>0.5</v>
+      </c>
+      <c r="C114" s="18">
+        <f t="shared" si="21"/>
+        <v>0.51593241104975984</v>
+      </c>
+      <c r="D114" s="18">
+        <f t="shared" si="21"/>
+        <v>-0.5</v>
+      </c>
+      <c r="E114" s="18">
+        <f t="shared" si="21"/>
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="F114" s="18">
+        <f t="shared" si="21"/>
+        <v>0.22360679774997894</v>
+      </c>
+      <c r="G114" s="18"/>
+      <c r="H114" s="18"/>
+      <c r="I114" s="18">
+        <f t="shared" si="21"/>
+        <v>-0.18775322788492621</v>
+      </c>
+      <c r="N114">
+        <f>2/5</f>
+        <v>0.4</v>
+      </c>
+      <c r="O114">
+        <v>2255</v>
+      </c>
+      <c r="P114">
+        <f>SQRT(O114)</f>
+        <v>47.486840282335066</v>
+      </c>
+      <c r="R114">
+        <f>48^2</f>
+        <v>2304</v>
+      </c>
+      <c r="S114">
+        <f>R114-O114</f>
+        <v>49</v>
+      </c>
+      <c r="T114">
+        <f>SQRT(S114)</f>
+        <v>7</v>
+      </c>
+      <c r="U114">
+        <f>48^2-7^2</f>
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="115" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B115" s="18">
+        <f t="shared" si="21"/>
+        <v>-0.5</v>
+      </c>
+      <c r="C115" s="18">
+        <f t="shared" si="21"/>
+        <v>-1.0529232878566681E-2</v>
+      </c>
+      <c r="D115" s="18">
+        <f t="shared" si="21"/>
+        <v>0.5</v>
+      </c>
+      <c r="E115" s="18">
+        <f t="shared" si="21"/>
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="F115" s="18">
+        <f t="shared" si="21"/>
+        <v>-0.89442719099991597</v>
+      </c>
+      <c r="G115" s="18"/>
+      <c r="H115" s="18"/>
+      <c r="I115" s="18">
+        <f t="shared" si="21"/>
+        <v>0.87902647600669992</v>
+      </c>
+      <c r="P115">
+        <f>P114*2/5</f>
+        <v>18.994736112934028</v>
+      </c>
+      <c r="S115">
+        <f>R114-S114</f>
+        <v>2255</v>
+      </c>
+      <c r="W115">
+        <f>S115*4</f>
+        <v>9020</v>
+      </c>
+      <c r="X115">
+        <f>SQRT(W115)</f>
+        <v>94.973680564670133</v>
+      </c>
+      <c r="Z115">
+        <v>96</v>
+      </c>
+      <c r="AA115">
+        <f>Z115^2</f>
+        <v>9216</v>
+      </c>
+      <c r="AB115">
+        <f>AA115-W115</f>
+        <v>196</v>
+      </c>
+      <c r="AC115">
+        <f>SQRT(AB115)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="117" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="Z117" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA117">
+        <f>90-14</f>
+        <v>76</v>
+      </c>
+      <c r="AB117">
+        <f>SQRT(AA117)</f>
+        <v>8.717797887081348</v>
+      </c>
+    </row>
+    <row r="118" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="L118">
+        <f>51/5</f>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="N118">
+        <v>45.2</v>
+      </c>
+      <c r="O118">
+        <f>N118/5</f>
+        <v>9.0400000000000009</v>
+      </c>
+      <c r="Q118">
+        <f>9*25</f>
+        <v>225</v>
+      </c>
+      <c r="R118">
+        <v>25</v>
+      </c>
+      <c r="S118">
+        <f>Q118/R118</f>
+        <v>9</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA118">
+        <f>90+14</f>
+        <v>104</v>
+      </c>
+      <c r="AB118">
+        <f>SQRT(AA118)</f>
+        <v>10.198039027185569</v>
+      </c>
+    </row>
+    <row r="119" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="R119">
+        <f>Q118/5</f>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Edu/Linear_algebra/linal_session_task.xlsx
+++ b/Edu/Linear_algebra/linal_session_task.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LysogorA\DataScience\Edu\Linear_algebra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iTonyJah\DataScience\Edu\Linear_algebra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0538AAFC-DB83-4BFC-B05A-A9F8A28FD179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD744CE6-9E45-41B3-ACBB-F1C8780E04B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="1125" windowWidth="16455" windowHeight="12390" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="1" r:id="rId1"/>
@@ -392,7 +392,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -439,11 +439,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -479,6 +490,7 @@
     </xf>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3046,18 +3058,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472F5A48-0D57-45D1-AF67-58628EB4925B}">
-  <dimension ref="A1:AC119"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AD127"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="25" max="25" width="12.7109375" customWidth="1"/>
+    <col min="25" max="25" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3080,7 +3092,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -3103,7 +3115,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -3126,7 +3138,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -3149,7 +3161,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -3172,7 +3184,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -3195,32 +3207,32 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="23" x14ac:dyDescent="0.5">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -3228,7 +3240,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>3</v>
       </c>
@@ -3242,7 +3254,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
         <v>1</v>
       </c>
@@ -3256,7 +3268,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <v>2</v>
       </c>
@@ -3270,22 +3282,22 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -3293,12 +3305,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -3306,42 +3318,42 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="16" x14ac:dyDescent="0.4">
       <c r="A33" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
         <v>28</v>
       </c>
@@ -3352,7 +3364,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <f>F38*J$38+G38*J$39+H38*J$40</f>
         <v>93900</v>
@@ -3374,7 +3386,7 @@
       </c>
       <c r="L38" s="8"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="7">
         <f t="shared" ref="A39:A40" si="0">F39*J$38+G39*J$39+H39*J$40</f>
         <v>52100</v>
@@ -3396,7 +3408,7 @@
       </c>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <f t="shared" si="0"/>
         <v>80200</v>
@@ -3418,23 +3430,23 @@
       </c>
       <c r="L40" s="8"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B41" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="J43" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="12">
         <f>F44*J$44+G44*J$45+H44*J$46</f>
         <v>494200</v>
@@ -3456,7 +3468,7 @@
       </c>
       <c r="L44" s="8"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="12">
         <f t="shared" ref="A45:A46" si="1">F45*J$44+G45*J$45+H45*J$46</f>
         <v>9960900</v>
@@ -3478,7 +3490,7 @@
       </c>
       <c r="L45" s="8"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="12">
         <f t="shared" si="1"/>
         <v>494200</v>
@@ -3500,22 +3512,22 @@
       </c>
       <c r="L46" s="8"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B47" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B50" s="6" t="s">
         <v>43</v>
       </c>
@@ -3523,7 +3535,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -3555,7 +3567,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="12">
         <f t="shared" ref="A52:A53" si="4">$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -3587,7 +3599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="12">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -3619,12 +3631,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>38</v>
       </c>
@@ -3635,7 +3647,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -3658,7 +3670,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="12">
         <f>$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -3681,7 +3693,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="12">
         <f>$F53*J$51+$G53*J$52+$H53*J$53</f>
         <v>14</v>
@@ -3704,19 +3716,19 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B59" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>51</v>
       </c>
       <c r="B60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G61" s="6" t="s">
         <v>43</v>
       </c>
@@ -3724,7 +3736,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="12">
         <f>F62*J$62+G62*J$63+H62*J$64</f>
         <v>494200</v>
@@ -3745,7 +3757,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="12">
         <f t="shared" ref="A63:A64" si="5">F63*J$62+G63*J$63+H63*J$64</f>
         <v>9960900</v>
@@ -3766,7 +3778,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="12">
         <f t="shared" si="5"/>
         <v>494200</v>
@@ -3787,23 +3799,23 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B65" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B67" s="8"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C68" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="12">
         <v>494200</v>
       </c>
@@ -3811,7 +3823,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
         <v>9960900</v>
       </c>
@@ -3819,7 +3831,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="12">
         <v>494200</v>
       </c>
@@ -3827,77 +3839,77 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="23" x14ac:dyDescent="0.35">
       <c r="A74" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>1</v>
       </c>
@@ -3920,7 +3932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C90" s="16"/>
       <c r="D90" s="16"/>
       <c r="E90" s="16" t="s">
@@ -3932,7 +3944,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B91" s="7">
         <v>3</v>
       </c>
@@ -3955,7 +3967,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B92" s="7">
         <v>1</v>
       </c>
@@ -3978,7 +3990,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B93" s="7">
         <v>2</v>
       </c>
@@ -4001,7 +4013,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B94" s="7">
         <v>3</v>
       </c>
@@ -4024,7 +4036,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B95" s="7">
         <v>1</v>
       </c>
@@ -4047,17 +4059,17 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A97" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>76</v>
       </c>
@@ -4089,8 +4101,18 @@
         <f t="shared" si="6"/>
         <v>12200</v>
       </c>
-    </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AB99">
+        <v>95</v>
+      </c>
+      <c r="AC99">
+        <v>5</v>
+      </c>
+      <c r="AD99">
+        <f>AB99/AC99</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>77</v>
       </c>
@@ -4122,13 +4144,29 @@
         <f t="shared" si="7"/>
         <v>2440</v>
       </c>
-    </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="S100">
+        <f>1/5</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="S101">
+        <f>S100^2</f>
+        <v>4.0000000000000008E-2</v>
+      </c>
+      <c r="T101">
+        <f>S101*5</f>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="U101">
+        <f>SQRT(T101)</f>
+        <v>0.44721359549995798</v>
+      </c>
+    </row>
+    <row r="102" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B102" s="7">
         <f>B91-B$100</f>
         <v>1</v>
@@ -4157,6 +4195,14 @@
         <f t="shared" ref="I102" si="9">I91-I$100</f>
         <v>-240</v>
       </c>
+      <c r="J102" s="19">
+        <f>I102^2</f>
+        <v>57600</v>
+      </c>
+      <c r="K102">
+        <f>SQRT(ABS(I102))</f>
+        <v>15.491933384829668</v>
+      </c>
       <c r="M102" t="s">
         <v>83</v>
       </c>
@@ -4164,7 +4210,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B103" s="7">
         <f t="shared" ref="B103:G103" si="10">B92-B$100</f>
         <v>-1</v>
@@ -4193,35 +4239,63 @@
         <f t="shared" ref="I103" si="11">I92-I$100</f>
         <v>-840</v>
       </c>
-    </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="J103" s="19">
+        <f t="shared" ref="J103:J106" si="12">I103^2</f>
+        <v>705600</v>
+      </c>
+      <c r="K103">
+        <f t="shared" ref="K103:K107" si="13">SQRT(ABS(I103))</f>
+        <v>28.982753492378876</v>
+      </c>
+      <c r="S103">
+        <f>4/5</f>
+        <v>0.8</v>
+      </c>
+      <c r="T103">
+        <f>SQRT(S103)</f>
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="W103">
+        <f>W104*W105*W106</f>
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="104" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B104" s="7">
-        <f t="shared" ref="B104:G104" si="12">B93-B$100</f>
+        <f t="shared" ref="B104:G104" si="14">B93-B$100</f>
         <v>0</v>
       </c>
       <c r="C104" s="17">
+        <f t="shared" si="14"/>
+        <v>-0.20000000000000284</v>
+      </c>
+      <c r="D104" s="7">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="E104" s="17">
+        <f t="shared" si="14"/>
+        <v>-0.2</v>
+      </c>
+      <c r="F104" s="17">
+        <f t="shared" si="14"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="G104" s="7">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I104" s="7">
+        <f t="shared" ref="I104" si="15">I93-I$100</f>
+        <v>-540</v>
+      </c>
+      <c r="J104" s="19">
         <f t="shared" si="12"/>
-        <v>-0.20000000000000284</v>
-      </c>
-      <c r="D104" s="7">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="E104" s="17">
-        <f t="shared" si="12"/>
-        <v>-0.2</v>
-      </c>
-      <c r="F104" s="17">
-        <f t="shared" si="12"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="G104" s="7">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I104" s="7">
-        <f t="shared" ref="I104" si="13">I93-I$100</f>
-        <v>-540</v>
+        <v>291600</v>
+      </c>
+      <c r="K104">
+        <f t="shared" si="13"/>
+        <v>23.2379000772445</v>
       </c>
       <c r="M104">
         <v>29</v>
@@ -4230,98 +4304,161 @@
         <f>M104^2</f>
         <v>841</v>
       </c>
-    </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="T104">
+        <f>T103*2</f>
+        <v>1.7888543819998317</v>
+      </c>
+      <c r="W104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B105" s="7">
-        <f t="shared" ref="B105:G105" si="14">B94-B$100</f>
+        <f t="shared" ref="B105:G105" si="16">B94-B$100</f>
         <v>1</v>
       </c>
       <c r="C105" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>9.7999999999999972</v>
       </c>
       <c r="D105" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-1</v>
       </c>
       <c r="E105" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-0.2</v>
       </c>
       <c r="F105" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="G105" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I105" s="7">
-        <f t="shared" ref="I105" si="15">I94-I$100</f>
+        <f t="shared" ref="I105" si="17">I94-I$100</f>
         <v>-440</v>
+      </c>
+      <c r="J105" s="19">
+        <f t="shared" si="12"/>
+        <v>193600</v>
+      </c>
+      <c r="K105">
+        <f t="shared" si="13"/>
+        <v>20.976176963403031</v>
       </c>
       <c r="M105">
         <v>76</v>
       </c>
       <c r="N105">
-        <f t="shared" ref="N105:N108" si="16">M105^2</f>
+        <f t="shared" ref="N105:N108" si="18">M105^2</f>
         <v>5776</v>
       </c>
       <c r="R105">
         <f>5*451</f>
         <v>2255</v>
       </c>
-    </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="W105">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B106" s="7">
-        <f t="shared" ref="B106:G106" si="17">B95-B$100</f>
+        <f t="shared" ref="B106:G106" si="19">B95-B$100</f>
         <v>-1</v>
       </c>
       <c r="C106" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="D106" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E106" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.8</v>
       </c>
       <c r="F106" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-0.8</v>
       </c>
       <c r="G106" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I106" s="7">
-        <f t="shared" ref="I106" si="18">I95-I$100</f>
+        <f t="shared" ref="I106" si="20">I95-I$100</f>
         <v>2060</v>
+      </c>
+      <c r="J106" s="19">
+        <f t="shared" si="12"/>
+        <v>4243600</v>
+      </c>
+      <c r="K106">
+        <f t="shared" si="13"/>
+        <v>45.387222871640866</v>
       </c>
       <c r="M106">
         <v>1</v>
       </c>
       <c r="N106">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="W106">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>79</v>
       </c>
+      <c r="J107" s="19">
+        <f>SUM(J102:J106)</f>
+        <v>5492000</v>
+      </c>
+      <c r="K107">
+        <f>SQRT(ABS(J107))</f>
+        <v>2343.5016535091245</v>
+      </c>
       <c r="M107">
         <v>49</v>
       </c>
       <c r="N107">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>2401</v>
       </c>
-    </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="V107">
+        <v>95</v>
+      </c>
+      <c r="W107">
+        <f>V107*V107</f>
+        <v>9025</v>
+      </c>
+      <c r="Y107">
+        <f>V107*V107</f>
+        <v>9025</v>
+      </c>
+      <c r="Z107">
+        <f>Y107/5</f>
+        <v>1805</v>
+      </c>
+      <c r="AA107">
+        <v>1804</v>
+      </c>
+      <c r="AB107">
+        <f>AA107/Z107</f>
+        <v>0.99944598337950141</v>
+      </c>
+      <c r="AC107">
+        <f>SQRT(AB107)</f>
+        <v>0.99972295331231709</v>
+      </c>
+    </row>
+    <row r="108" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>80</v>
       </c>
@@ -4329,7 +4466,7 @@
         <v>1</v>
       </c>
       <c r="N108">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="V108">
@@ -4346,38 +4483,41 @@
         <f>SQRT(X108)</f>
         <v>18.994736112934024</v>
       </c>
-    </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AC108">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B109">
         <f>(B102^2+B103^2+B104^2+B105^2+B106^2)^(1/2)</f>
         <v>2</v>
       </c>
       <c r="C109">
-        <f t="shared" ref="C109:I109" si="19">(C102^2+C103^2+C104^2+C105^2+C106^2)^(1/2)</f>
+        <f t="shared" ref="C109:I109" si="21">(C102^2+C103^2+C104^2+C105^2+C106^2)^(1/2)</f>
         <v>18.994736112934028</v>
       </c>
       <c r="D109">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>2</v>
       </c>
       <c r="E109">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.89442719099991597</v>
       </c>
       <c r="F109">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.89442719099991586</v>
       </c>
       <c r="G109">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H109">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I109">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>2343.5016535091245</v>
       </c>
       <c r="N109">
@@ -4401,8 +4541,12 @@
         <f>SQRT(X109)</f>
         <v>21</v>
       </c>
-    </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AC109">
+        <f>AC108*AC107</f>
+        <v>18.994736112934024</v>
+      </c>
+    </row>
+    <row r="110" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>81</v>
       </c>
@@ -4415,90 +4559,105 @@
         <v>8.9554452708952432</v>
       </c>
     </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B111" s="18">
         <f>B102/B$109</f>
         <v>0.5</v>
       </c>
       <c r="C111" s="18">
-        <f t="shared" ref="C111:I111" si="20">C102/C$109</f>
+        <f t="shared" ref="C111:I111" si="22">C102/C$109</f>
         <v>0.30534775347842924</v>
       </c>
       <c r="D111" s="18">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.5</v>
       </c>
       <c r="E111" s="18">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-0.22360679774997896</v>
       </c>
       <c r="F111" s="18">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.22360679774997894</v>
       </c>
       <c r="G111" s="18"/>
       <c r="H111" s="18"/>
       <c r="I111" s="18">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-0.10241085157359611</v>
       </c>
     </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B112" s="18">
-        <f t="shared" ref="B112:I115" si="21">B103/B$109</f>
+        <f t="shared" ref="B112:I115" si="23">B103/B$109</f>
         <v>-0.5</v>
       </c>
       <c r="C112" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.80022169877105653</v>
       </c>
       <c r="D112" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.5</v>
       </c>
       <c r="E112" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.22360679774997896</v>
       </c>
       <c r="F112" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.22360679774997894</v>
       </c>
       <c r="G112" s="18"/>
       <c r="H112" s="18"/>
       <c r="I112" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.35843798050758635</v>
       </c>
       <c r="N112" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="113" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="Y112">
+        <v>4</v>
+      </c>
+      <c r="Z112">
+        <f>1/5</f>
+        <v>0.2</v>
+      </c>
+      <c r="AA112">
+        <f>SQRT(Z112)</f>
+        <v>0.44721359549995793</v>
+      </c>
+      <c r="AB112">
+        <f>Y112*AA112</f>
+        <v>1.7888543819998317</v>
+      </c>
+    </row>
+    <row r="113" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B113" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="C113" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-1.0529232878566681E-2</v>
       </c>
       <c r="D113" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="E113" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.22360679774997896</v>
       </c>
       <c r="F113" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.22360679774997894</v>
       </c>
       <c r="G113" s="18"/>
       <c r="H113" s="18"/>
       <c r="I113" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.23042441604059125</v>
       </c>
       <c r="O113">
@@ -4517,32 +4676,46 @@
         <f>SQRT(-S113)</f>
         <v>28.478061731796284</v>
       </c>
-    </row>
-    <row r="114" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="W113">
+        <v>4</v>
+      </c>
+      <c r="X113">
+        <v>5</v>
+      </c>
+      <c r="Y113">
+        <f>W113/X113</f>
+        <v>0.8</v>
+      </c>
+      <c r="Z113">
+        <f>SQRT(Y113)</f>
+        <v>0.89442719099991586</v>
+      </c>
+    </row>
+    <row r="114" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B114" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.5</v>
       </c>
       <c r="C114" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.51593241104975984</v>
       </c>
       <c r="D114" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.5</v>
       </c>
       <c r="E114" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.22360679774997896</v>
       </c>
       <c r="F114" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.22360679774997894</v>
       </c>
       <c r="G114" s="18"/>
       <c r="H114" s="18"/>
       <c r="I114" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.18775322788492621</v>
       </c>
       <c r="N114">
@@ -4572,32 +4745,40 @@
         <f>48^2-7^2</f>
         <v>2255</v>
       </c>
-    </row>
-    <row r="115" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="X114">
+        <f>SQRT(X113)</f>
+        <v>2.2360679774997898</v>
+      </c>
+      <c r="Y114">
+        <f>X114/5</f>
+        <v>0.44721359549995798</v>
+      </c>
+    </row>
+    <row r="115" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B115" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.5</v>
       </c>
       <c r="C115" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-1.0529232878566681E-2</v>
       </c>
       <c r="D115" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.5</v>
       </c>
       <c r="E115" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.89442719099991586</v>
       </c>
       <c r="F115" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.89442719099991597</v>
       </c>
       <c r="G115" s="18"/>
       <c r="H115" s="18"/>
       <c r="I115" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.87902647600669992</v>
       </c>
       <c r="P115">
@@ -4632,7 +4813,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="117" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:29" x14ac:dyDescent="0.35">
       <c r="Z117" t="s">
         <v>84</v>
       </c>
@@ -4645,7 +4826,7 @@
         <v>8.717797887081348</v>
       </c>
     </row>
-    <row r="118" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:29" x14ac:dyDescent="0.35">
       <c r="L118">
         <f>51/5</f>
         <v>10.199999999999999</v>
@@ -4668,6 +4849,21 @@
         <f>Q118/R118</f>
         <v>9</v>
       </c>
+      <c r="U118">
+        <v>2</v>
+      </c>
+      <c r="V118">
+        <f>4/5</f>
+        <v>0.8</v>
+      </c>
+      <c r="W118">
+        <f>SQRT(V118)</f>
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="X118">
+        <f>W118*U118</f>
+        <v>1.7888543819998317</v>
+      </c>
       <c r="Z118" t="s">
         <v>85</v>
       </c>
@@ -4680,10 +4876,146 @@
         <v>10.198039027185569</v>
       </c>
     </row>
-    <row r="119" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="R119">
+    <row r="120" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="H120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="H121">
+        <v>5</v>
+      </c>
+      <c r="R121">
         <f>Q118/5</f>
         <v>45</v>
+      </c>
+    </row>
+    <row r="122" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="H122">
+        <v>10</v>
+      </c>
+      <c r="I122">
+        <v>2</v>
+      </c>
+      <c r="J122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="F123">
+        <v>-240</v>
+      </c>
+      <c r="G123">
+        <f>ABS(F123)</f>
+        <v>240</v>
+      </c>
+      <c r="H123">
+        <f>$G123/H$122</f>
+        <v>24</v>
+      </c>
+      <c r="I123">
+        <f>$H123/I$122</f>
+        <v>12</v>
+      </c>
+      <c r="J123">
+        <f>I123/J$122</f>
+        <v>6</v>
+      </c>
+      <c r="L123">
+        <f>2^4*3*5</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="124" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="F124">
+        <v>-840</v>
+      </c>
+      <c r="G124">
+        <f t="shared" ref="G124:G127" si="24">ABS(F124)</f>
+        <v>840</v>
+      </c>
+      <c r="H124">
+        <f t="shared" ref="H124:H127" si="25">$G124/H$122</f>
+        <v>84</v>
+      </c>
+      <c r="I124">
+        <f t="shared" ref="I124:J127" si="26">$H124/I$122</f>
+        <v>42</v>
+      </c>
+      <c r="J124">
+        <f t="shared" ref="J124:J126" si="27">I124/J$122</f>
+        <v>21</v>
+      </c>
+      <c r="L124">
+        <f>7*5*3*2^3</f>
+        <v>840</v>
+      </c>
+    </row>
+    <row r="125" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="F125">
+        <v>-540</v>
+      </c>
+      <c r="G125">
+        <f t="shared" si="24"/>
+        <v>540</v>
+      </c>
+      <c r="H125">
+        <f t="shared" si="25"/>
+        <v>54</v>
+      </c>
+      <c r="I125">
+        <f t="shared" si="26"/>
+        <v>27</v>
+      </c>
+      <c r="L125">
+        <f>5*3^3*2^2</f>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="126" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="F126">
+        <v>-440</v>
+      </c>
+      <c r="G126">
+        <f t="shared" si="24"/>
+        <v>440</v>
+      </c>
+      <c r="H126">
+        <f t="shared" si="25"/>
+        <v>44</v>
+      </c>
+      <c r="I126">
+        <f t="shared" si="26"/>
+        <v>22</v>
+      </c>
+      <c r="J126">
+        <f t="shared" si="27"/>
+        <v>11</v>
+      </c>
+      <c r="L126">
+        <f>11*5*2^3</f>
+        <v>440</v>
+      </c>
+    </row>
+    <row r="127" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="F127">
+        <v>2060</v>
+      </c>
+      <c r="G127">
+        <f t="shared" si="24"/>
+        <v>2060</v>
+      </c>
+      <c r="H127">
+        <f t="shared" si="25"/>
+        <v>206</v>
+      </c>
+      <c r="I127">
+        <f t="shared" si="26"/>
+        <v>103</v>
+      </c>
+      <c r="L127">
+        <f>103*5*2^2</f>
+        <v>2060</v>
       </c>
     </row>
   </sheetData>

--- a/Edu/Linear_algebra/linal_session_task.xlsx
+++ b/Edu/Linear_algebra/linal_session_task.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iTonyJah\DataScience\Edu\Linear_algebra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LysogorA\DataScience\Edu\Linear_algebra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD744CE6-9E45-41B3-ACBB-F1C8780E04B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF331A3A-F6DE-41C8-BBD3-2261C83B749F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="91">
   <si>
     <t>Рабочая таблица с данными:</t>
   </si>
@@ -294,6 +294,21 @@
   </si>
   <si>
     <t>90+14</t>
+  </si>
+  <si>
+    <t>=2^4*3*5</t>
+  </si>
+  <si>
+    <t>=7*5*3*2^3</t>
+  </si>
+  <si>
+    <t>=5*3^3*2^2</t>
+  </si>
+  <si>
+    <t>=11*5*2^3</t>
+  </si>
+  <si>
+    <t>=103*5*2^2</t>
   </si>
 </sst>
 </file>
@@ -490,7 +505,7 @@
     </xf>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3058,18 +3073,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472F5A48-0D57-45D1-AF67-58628EB4925B}">
-  <dimension ref="A1:AD127"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AD136"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="25" max="25" width="12.7265625" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3092,7 +3107,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -3115,7 +3130,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -3138,7 +3153,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -3161,7 +3176,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -3184,7 +3199,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -3207,32 +3222,32 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="23" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -3240,7 +3255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>3</v>
       </c>
@@ -3254,7 +3269,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>1</v>
       </c>
@@ -3268,7 +3283,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>2</v>
       </c>
@@ -3282,22 +3297,22 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -3305,12 +3320,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -3318,42 +3333,42 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>28</v>
       </c>
@@ -3364,7 +3379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <f>F38*J$38+G38*J$39+H38*J$40</f>
         <v>93900</v>
@@ -3386,7 +3401,7 @@
       </c>
       <c r="L38" s="8"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <f t="shared" ref="A39:A40" si="0">F39*J$38+G39*J$39+H39*J$40</f>
         <v>52100</v>
@@ -3408,7 +3423,7 @@
       </c>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <f t="shared" si="0"/>
         <v>80200</v>
@@ -3430,23 +3445,23 @@
       </c>
       <c r="L40" s="8"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B41" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="J43" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
         <f>F44*J$44+G44*J$45+H44*J$46</f>
         <v>494200</v>
@@ -3468,7 +3483,7 @@
       </c>
       <c r="L44" s="8"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
         <f t="shared" ref="A45:A46" si="1">F45*J$44+G45*J$45+H45*J$46</f>
         <v>9960900</v>
@@ -3490,7 +3505,7 @@
       </c>
       <c r="L45" s="8"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
         <f t="shared" si="1"/>
         <v>494200</v>
@@ -3512,22 +3527,22 @@
       </c>
       <c r="L46" s="8"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B47" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B50" s="6" t="s">
         <v>43</v>
       </c>
@@ -3535,7 +3550,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -3567,7 +3582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="12">
         <f t="shared" ref="A52:A53" si="4">$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -3599,7 +3614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="12">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -3631,12 +3646,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>38</v>
       </c>
@@ -3647,7 +3662,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -3670,7 +3685,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
         <f>$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -3693,7 +3708,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="12">
         <f>$F53*J$51+$G53*J$52+$H53*J$53</f>
         <v>14</v>
@@ -3716,19 +3731,19 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B59" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>51</v>
       </c>
       <c r="B60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G61" s="6" t="s">
         <v>43</v>
       </c>
@@ -3736,7 +3751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="12">
         <f>F62*J$62+G62*J$63+H62*J$64</f>
         <v>494200</v>
@@ -3757,7 +3772,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="12">
         <f t="shared" ref="A63:A64" si="5">F63*J$62+G63*J$63+H63*J$64</f>
         <v>9960900</v>
@@ -3778,7 +3793,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="12">
         <f t="shared" si="5"/>
         <v>494200</v>
@@ -3799,23 +3814,23 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B65" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B67" s="8"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C68" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="12">
         <v>494200</v>
       </c>
@@ -3823,7 +3838,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="12">
         <v>9960900</v>
       </c>
@@ -3831,7 +3846,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="12">
         <v>494200</v>
       </c>
@@ -3839,77 +3854,77 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="23" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>1</v>
       </c>
@@ -3932,7 +3947,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C90" s="16"/>
       <c r="D90" s="16"/>
       <c r="E90" s="16" t="s">
@@ -3944,7 +3959,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B91" s="7">
         <v>3</v>
       </c>
@@ -3967,7 +3982,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B92" s="7">
         <v>1</v>
       </c>
@@ -3990,7 +4005,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B93" s="7">
         <v>2</v>
       </c>
@@ -4013,7 +4028,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B94" s="7">
         <v>3</v>
       </c>
@@ -4036,7 +4051,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B95" s="7">
         <v>1</v>
       </c>
@@ -4059,17 +4074,17 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>76</v>
       </c>
@@ -4112,7 +4127,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>77</v>
       </c>
@@ -4149,7 +4164,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>78</v>
       </c>
@@ -4166,7 +4181,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B102" s="7">
         <f>B91-B$100</f>
         <v>1</v>
@@ -4210,7 +4225,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B103" s="7">
         <f t="shared" ref="B103:G103" si="10">B92-B$100</f>
         <v>-1</v>
@@ -4244,7 +4259,7 @@
         <v>705600</v>
       </c>
       <c r="K103">
-        <f t="shared" ref="K103:K107" si="13">SQRT(ABS(I103))</f>
+        <f t="shared" ref="K103:K106" si="13">SQRT(ABS(I103))</f>
         <v>28.982753492378876</v>
       </c>
       <c r="S103">
@@ -4260,7 +4275,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B104" s="7">
         <f t="shared" ref="B104:G104" si="14">B93-B$100</f>
         <v>0</v>
@@ -4312,7 +4327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B105" s="7">
         <f t="shared" ref="B105:G105" si="16">B94-B$100</f>
         <v>1</v>
@@ -4364,7 +4379,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B106" s="7">
         <f t="shared" ref="B106:G106" si="19">B95-B$100</f>
         <v>-1</v>
@@ -4412,7 +4427,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>79</v>
       </c>
@@ -4458,7 +4473,7 @@
         <v>0.99972295331231709</v>
       </c>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>80</v>
       </c>
@@ -4487,7 +4502,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B109">
         <f>(B102^2+B103^2+B104^2+B105^2+B106^2)^(1/2)</f>
         <v>2</v>
@@ -4546,7 +4561,7 @@
         <v>18.994736112934024</v>
       </c>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>81</v>
       </c>
@@ -4559,7 +4574,7 @@
         <v>8.9554452708952432</v>
       </c>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B111" s="18">
         <f>B102/B$109</f>
         <v>0.5</v>
@@ -4587,7 +4602,7 @@
         <v>-0.10241085157359611</v>
       </c>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B112" s="18">
         <f t="shared" ref="B112:I115" si="23">B103/B$109</f>
         <v>-0.5</v>
@@ -4633,7 +4648,7 @@
         <v>1.7888543819998317</v>
       </c>
     </row>
-    <row r="113" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B113" s="18">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -4691,7 +4706,7 @@
         <v>0.89442719099991586</v>
       </c>
     </row>
-    <row r="114" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B114" s="18">
         <f t="shared" si="23"/>
         <v>0.5</v>
@@ -4754,7 +4769,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="115" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B115" s="18">
         <f t="shared" si="23"/>
         <v>-0.5</v>
@@ -4813,7 +4828,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="117" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:29" x14ac:dyDescent="0.25">
       <c r="Z117" t="s">
         <v>84</v>
       </c>
@@ -4826,7 +4841,7 @@
         <v>8.717797887081348</v>
       </c>
     </row>
-    <row r="118" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:29" x14ac:dyDescent="0.25">
       <c r="L118">
         <f>51/5</f>
         <v>10.199999999999999</v>
@@ -4876,12 +4891,12 @@
         <v>10.198039027185569</v>
       </c>
     </row>
-    <row r="120" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:29" x14ac:dyDescent="0.25">
       <c r="H120">
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:29" x14ac:dyDescent="0.25">
       <c r="H121">
         <v>5</v>
       </c>
@@ -4890,18 +4905,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="122" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:29" x14ac:dyDescent="0.25">
       <c r="H122">
         <v>10</v>
       </c>
       <c r="I122">
         <v>2</v>
       </c>
-      <c r="J122">
+      <c r="K122">
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F123">
         <v>-240</v>
       </c>
@@ -4918,15 +4933,26 @@
         <v>12</v>
       </c>
       <c r="J123">
-        <f>I123/J$122</f>
+        <f>I123^2</f>
+        <v>144</v>
+      </c>
+      <c r="K123">
+        <f>I123/K$122</f>
         <v>6</v>
       </c>
-      <c r="L123">
+      <c r="M123">
         <f>2^4*3*5</f>
         <v>240</v>
       </c>
-    </row>
-    <row r="124" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="N123" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="P123">
+        <f>G123/10/2</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F124">
         <v>-840</v>
       </c>
@@ -4939,19 +4965,30 @@
         <v>84</v>
       </c>
       <c r="I124">
-        <f t="shared" ref="I124:J127" si="26">$H124/I$122</f>
+        <f t="shared" ref="I124:I127" si="26">$H124/I$122</f>
         <v>42</v>
       </c>
       <c r="J124">
-        <f t="shared" ref="J124:J126" si="27">I124/J$122</f>
+        <f t="shared" ref="J124:J127" si="27">I124^2</f>
+        <v>1764</v>
+      </c>
+      <c r="K124">
+        <f>I124/K$122</f>
         <v>21</v>
       </c>
-      <c r="L124">
+      <c r="M124">
         <f>7*5*3*2^3</f>
         <v>840</v>
       </c>
-    </row>
-    <row r="125" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="N124" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="P124">
+        <f>G124/10/2</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="125" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F125">
         <v>-540</v>
       </c>
@@ -4967,12 +5004,23 @@
         <f t="shared" si="26"/>
         <v>27</v>
       </c>
-      <c r="L125">
+      <c r="J125">
+        <f t="shared" si="27"/>
+        <v>729</v>
+      </c>
+      <c r="M125">
         <f>5*3^3*2^2</f>
         <v>540</v>
       </c>
-    </row>
-    <row r="126" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="N125" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="P125">
+        <f>G125/10/2</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="126" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F126">
         <v>-440</v>
       </c>
@@ -4990,14 +5038,25 @@
       </c>
       <c r="J126">
         <f t="shared" si="27"/>
+        <v>484</v>
+      </c>
+      <c r="K126">
+        <f>I126/K$122</f>
         <v>11</v>
       </c>
-      <c r="L126">
+      <c r="M126">
         <f>11*5*2^3</f>
         <v>440</v>
       </c>
-    </row>
-    <row r="127" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="N126" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="P126">
+        <f>G126/10/2</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F127">
         <v>2060</v>
       </c>
@@ -5013,9 +5072,115 @@
         <f t="shared" si="26"/>
         <v>103</v>
       </c>
-      <c r="L127">
+      <c r="J127">
+        <f t="shared" si="27"/>
+        <v>10609</v>
+      </c>
+      <c r="M127">
         <f>103*5*2^2</f>
         <v>2060</v>
+      </c>
+      <c r="N127" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="P127">
+        <f>G127/10/2</f>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="129" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="J129">
+        <f>SUM(J123:J128)</f>
+        <v>13730</v>
+      </c>
+    </row>
+    <row r="130" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="J130">
+        <f>SQRT(J129)</f>
+        <v>117.17508267545622</v>
+      </c>
+    </row>
+    <row r="132" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F132">
+        <f>G132*H132</f>
+        <v>117</v>
+      </c>
+      <c r="G132">
+        <v>13</v>
+      </c>
+      <c r="H132">
+        <f>I132/13</f>
+        <v>9</v>
+      </c>
+      <c r="I132">
+        <v>117</v>
+      </c>
+      <c r="J132">
+        <f>I132^2</f>
+        <v>13689</v>
+      </c>
+      <c r="K132">
+        <v>41</v>
+      </c>
+      <c r="L132">
+        <f>K132+J132</f>
+        <v>13730</v>
+      </c>
+      <c r="M132">
+        <f>L132/J132</f>
+        <v>1.0029951055592081</v>
+      </c>
+      <c r="N132">
+        <f>SQRT(M132)</f>
+        <v>1.0014964331235574</v>
+      </c>
+      <c r="O132">
+        <v>2340</v>
+      </c>
+      <c r="P132">
+        <f>O132*N132</f>
+        <v>2343.5016535091245</v>
+      </c>
+    </row>
+    <row r="133" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="I133">
+        <f>I132*20</f>
+        <v>2340</v>
+      </c>
+      <c r="J133">
+        <f>J132-J129</f>
+        <v>-41</v>
+      </c>
+    </row>
+    <row r="135" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="H135">
+        <f>I135/2</f>
+        <v>59</v>
+      </c>
+      <c r="I135">
+        <v>118</v>
+      </c>
+      <c r="J135">
+        <f>I135^2</f>
+        <v>13924</v>
+      </c>
+      <c r="K135">
+        <f>J135-J129</f>
+        <v>194</v>
+      </c>
+      <c r="L135">
+        <f>K135/2</f>
+        <v>97</v>
+      </c>
+      <c r="M135">
+        <f>L135/7</f>
+        <v>13.857142857142858</v>
+      </c>
+    </row>
+    <row r="136" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="I136">
+        <f>I135*20</f>
+        <v>2360</v>
       </c>
     </row>
   </sheetData>

--- a/Edu/Linear_algebra/linal_session_task.xlsx
+++ b/Edu/Linear_algebra/linal_session_task.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LysogorA\DataScience\Edu\Linear_algebra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF331A3A-F6DE-41C8-BBD3-2261C83B749F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0555F8-23B6-481C-B23E-C8D5825E64DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
   </bookViews>
@@ -3073,7 +3073,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472F5A48-0D57-45D1-AF67-58628EB4925B}">
-  <dimension ref="A1:AD136"/>
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:AD142"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="25" max="25" width="12.7109375" customWidth="1"/>
@@ -4951,6 +4954,10 @@
         <f>G123/10/2</f>
         <v>12</v>
       </c>
+      <c r="Q123">
+        <f>P123^2</f>
+        <v>144</v>
+      </c>
     </row>
     <row r="124" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F124">
@@ -4987,6 +4994,10 @@
         <f>G124/10/2</f>
         <v>42</v>
       </c>
+      <c r="Q124">
+        <f t="shared" ref="Q124:Q127" si="28">P124^2</f>
+        <v>1764</v>
+      </c>
     </row>
     <row r="125" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F125">
@@ -5019,6 +5030,10 @@
         <f>G125/10/2</f>
         <v>27</v>
       </c>
+      <c r="Q125">
+        <f t="shared" si="28"/>
+        <v>729</v>
+      </c>
     </row>
     <row r="126" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F126">
@@ -5055,6 +5070,10 @@
         <f>G126/10/2</f>
         <v>22</v>
       </c>
+      <c r="Q126">
+        <f t="shared" si="28"/>
+        <v>484</v>
+      </c>
     </row>
     <row r="127" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F127">
@@ -5087,20 +5106,66 @@
         <f>G127/10/2</f>
         <v>103</v>
       </c>
-    </row>
-    <row r="129" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="Q127">
+        <f t="shared" si="28"/>
+        <v>10609</v>
+      </c>
+    </row>
+    <row r="128" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="W128">
+        <v>2</v>
+      </c>
+      <c r="X128">
+        <f>SQRT(W128)</f>
+        <v>1.4142135623730951</v>
+      </c>
+    </row>
+    <row r="129" spans="5:24" x14ac:dyDescent="0.25">
       <c r="J129">
         <f>SUM(J123:J128)</f>
         <v>13730</v>
       </c>
-    </row>
-    <row r="130" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="P129">
+        <f>SUM(P123:P128)</f>
+        <v>206</v>
+      </c>
+      <c r="Q129">
+        <f>SUM(Q123:Q128)</f>
+        <v>13730</v>
+      </c>
+      <c r="W129">
+        <v>3</v>
+      </c>
+      <c r="X129">
+        <f>SQRT(W129)</f>
+        <v>1.7320508075688772</v>
+      </c>
+    </row>
+    <row r="130" spans="5:24" x14ac:dyDescent="0.25">
       <c r="J130">
         <f>SQRT(J129)</f>
         <v>117.17508267545622</v>
       </c>
-    </row>
-    <row r="132" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="R130">
+        <f>2*5*1373</f>
+        <v>13730</v>
+      </c>
+      <c r="S130">
+        <f>SQRT(R130)</f>
+        <v>117.17508267545622</v>
+      </c>
+    </row>
+    <row r="131" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="W131">
+        <f>W128/W129</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="X131">
+        <f>X128/X129</f>
+        <v>0.81649658092772615</v>
+      </c>
+    </row>
+    <row r="132" spans="5:24" x14ac:dyDescent="0.25">
       <c r="F132">
         <f>G132*H132</f>
         <v>117</v>
@@ -5141,8 +5206,12 @@
         <f>O132*N132</f>
         <v>2343.5016535091245</v>
       </c>
-    </row>
-    <row r="133" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="W132">
+        <f>SQRT(W131)</f>
+        <v>0.81649658092772603</v>
+      </c>
+    </row>
+    <row r="133" spans="5:24" x14ac:dyDescent="0.25">
       <c r="I133">
         <f>I132*20</f>
         <v>2340</v>
@@ -5152,7 +5221,7 @@
         <v>-41</v>
       </c>
     </row>
-    <row r="135" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="5:24" x14ac:dyDescent="0.25">
       <c r="H135">
         <f>I135/2</f>
         <v>59</v>
@@ -5177,10 +5246,60 @@
         <v>13.857142857142858</v>
       </c>
     </row>
-    <row r="136" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="5:24" x14ac:dyDescent="0.25">
       <c r="I136">
         <f>I135*20</f>
         <v>2360</v>
+      </c>
+    </row>
+    <row r="139" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E139">
+        <v>19</v>
+      </c>
+      <c r="F139">
+        <v>1804</v>
+      </c>
+      <c r="H139">
+        <f>SQRT(F139/F140)*E139</f>
+        <v>18.994736112934024</v>
+      </c>
+      <c r="J139">
+        <v>9020</v>
+      </c>
+      <c r="K139">
+        <f>SQRT(J139)</f>
+        <v>94.973680564670133</v>
+      </c>
+    </row>
+    <row r="140" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="F140">
+        <v>1805</v>
+      </c>
+      <c r="J140">
+        <v>25</v>
+      </c>
+      <c r="N140">
+        <f>2 * 5 * 7 * 7 * 7 * 7</f>
+        <v>24010</v>
+      </c>
+    </row>
+    <row r="141" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="J141">
+        <f>J139/J140</f>
+        <v>360.8</v>
+      </c>
+    </row>
+    <row r="142" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="M142">
+        <v>7</v>
+      </c>
+      <c r="N142">
+        <f>M142^2</f>
+        <v>49</v>
+      </c>
+      <c r="O142">
+        <f>N142^2</f>
+        <v>2401</v>
       </c>
     </row>
   </sheetData>

--- a/Edu/Linear_algebra/linal_session_task.xlsx
+++ b/Edu/Linear_algebra/linal_session_task.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LysogorA\DataScience\Edu\Linear_algebra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iTonyJah\DataScience\Edu\Linear_algebra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0555F8-23B6-481C-B23E-C8D5825E64DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F698CE-2E4E-420F-9683-0F89304BC822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>Рабочая таблица с данными:</t>
   </si>
@@ -309,6 +310,9 @@
   </si>
   <si>
     <t>=103*5*2^2</t>
+  </si>
+  <si>
+    <t>меньше половины</t>
   </si>
 </sst>
 </file>
@@ -387,7 +391,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -403,6 +407,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF9F8FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -469,7 +485,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -506,6 +522,8 @@
     <xf numFmtId="12" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3077,17 +3095,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:AD142"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="25" max="25" width="12.7109375" customWidth="1"/>
+    <col min="25" max="25" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3110,7 +3128,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -3133,7 +3151,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -3156,7 +3174,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -3179,7 +3197,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -3202,7 +3220,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -3225,32 +3243,32 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="23" x14ac:dyDescent="0.5">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -3258,7 +3276,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>3</v>
       </c>
@@ -3272,7 +3290,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
         <v>1</v>
       </c>
@@ -3286,7 +3304,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <v>2</v>
       </c>
@@ -3300,22 +3318,22 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -3323,12 +3341,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -3336,42 +3354,42 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="16" x14ac:dyDescent="0.4">
       <c r="A33" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
         <v>28</v>
       </c>
@@ -3382,7 +3400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <f>F38*J$38+G38*J$39+H38*J$40</f>
         <v>93900</v>
@@ -3404,7 +3422,7 @@
       </c>
       <c r="L38" s="8"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="7">
         <f t="shared" ref="A39:A40" si="0">F39*J$38+G39*J$39+H39*J$40</f>
         <v>52100</v>
@@ -3426,7 +3444,7 @@
       </c>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <f t="shared" si="0"/>
         <v>80200</v>
@@ -3448,23 +3466,23 @@
       </c>
       <c r="L40" s="8"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B41" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="J43" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="12">
         <f>F44*J$44+G44*J$45+H44*J$46</f>
         <v>494200</v>
@@ -3486,7 +3504,7 @@
       </c>
       <c r="L44" s="8"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="12">
         <f t="shared" ref="A45:A46" si="1">F45*J$44+G45*J$45+H45*J$46</f>
         <v>9960900</v>
@@ -3508,7 +3526,7 @@
       </c>
       <c r="L45" s="8"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="12">
         <f t="shared" si="1"/>
         <v>494200</v>
@@ -3530,22 +3548,22 @@
       </c>
       <c r="L46" s="8"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B47" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B50" s="6" t="s">
         <v>43</v>
       </c>
@@ -3553,7 +3571,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -3585,7 +3603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="12">
         <f t="shared" ref="A52:A53" si="4">$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -3617,7 +3635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="12">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -3649,12 +3667,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>38</v>
       </c>
@@ -3665,7 +3683,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -3688,7 +3706,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="12">
         <f>$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -3711,7 +3729,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="12">
         <f>$F53*J$51+$G53*J$52+$H53*J$53</f>
         <v>14</v>
@@ -3734,19 +3752,19 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B59" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>51</v>
       </c>
       <c r="B60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G61" s="6" t="s">
         <v>43</v>
       </c>
@@ -3754,7 +3772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="12">
         <f>F62*J$62+G62*J$63+H62*J$64</f>
         <v>494200</v>
@@ -3775,7 +3793,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="12">
         <f t="shared" ref="A63:A64" si="5">F63*J$62+G63*J$63+H63*J$64</f>
         <v>9960900</v>
@@ -3796,7 +3814,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="12">
         <f t="shared" si="5"/>
         <v>494200</v>
@@ -3817,23 +3835,23 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B65" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B67" s="8"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C68" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="12">
         <v>494200</v>
       </c>
@@ -3841,7 +3859,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
         <v>9960900</v>
       </c>
@@ -3849,7 +3867,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="12">
         <v>494200</v>
       </c>
@@ -3857,77 +3875,77 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="23" x14ac:dyDescent="0.35">
       <c r="A74" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>1</v>
       </c>
@@ -3950,7 +3968,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C90" s="16"/>
       <c r="D90" s="16"/>
       <c r="E90" s="16" t="s">
@@ -3962,7 +3980,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B91" s="7">
         <v>3</v>
       </c>
@@ -3985,7 +4003,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B92" s="7">
         <v>1</v>
       </c>
@@ -4008,7 +4026,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B93" s="7">
         <v>2</v>
       </c>
@@ -4031,7 +4049,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B94" s="7">
         <v>3</v>
       </c>
@@ -4054,7 +4072,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B95" s="7">
         <v>1</v>
       </c>
@@ -4077,17 +4095,17 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A97" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>76</v>
       </c>
@@ -4130,7 +4148,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>77</v>
       </c>
@@ -4167,7 +4185,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>78</v>
       </c>
@@ -4184,7 +4202,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B102" s="7">
         <f>B91-B$100</f>
         <v>1</v>
@@ -4228,7 +4246,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B103" s="7">
         <f t="shared" ref="B103:G103" si="10">B92-B$100</f>
         <v>-1</v>
@@ -4278,7 +4296,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B104" s="7">
         <f t="shared" ref="B104:G104" si="14">B93-B$100</f>
         <v>0</v>
@@ -4330,7 +4348,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B105" s="7">
         <f t="shared" ref="B105:G105" si="16">B94-B$100</f>
         <v>1</v>
@@ -4382,7 +4400,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B106" s="7">
         <f t="shared" ref="B106:G106" si="19">B95-B$100</f>
         <v>-1</v>
@@ -4430,7 +4448,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>79</v>
       </c>
@@ -4476,7 +4494,7 @@
         <v>0.99972295331231709</v>
       </c>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>80</v>
       </c>
@@ -4505,7 +4523,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B109">
         <f>(B102^2+B103^2+B104^2+B105^2+B106^2)^(1/2)</f>
         <v>2</v>
@@ -4564,7 +4582,7 @@
         <v>18.994736112934024</v>
       </c>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>81</v>
       </c>
@@ -4577,7 +4595,7 @@
         <v>8.9554452708952432</v>
       </c>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B111" s="18">
         <f>B102/B$109</f>
         <v>0.5</v>
@@ -4605,7 +4623,7 @@
         <v>-0.10241085157359611</v>
       </c>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B112" s="18">
         <f t="shared" ref="B112:I115" si="23">B103/B$109</f>
         <v>-0.5</v>
@@ -4651,7 +4669,7 @@
         <v>1.7888543819998317</v>
       </c>
     </row>
-    <row r="113" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B113" s="18">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -4709,7 +4727,7 @@
         <v>0.89442719099991586</v>
       </c>
     </row>
-    <row r="114" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B114" s="18">
         <f t="shared" si="23"/>
         <v>0.5</v>
@@ -4772,7 +4790,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="115" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B115" s="18">
         <f t="shared" si="23"/>
         <v>-0.5</v>
@@ -4831,7 +4849,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="117" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:29" x14ac:dyDescent="0.35">
       <c r="Z117" t="s">
         <v>84</v>
       </c>
@@ -4844,7 +4862,7 @@
         <v>8.717797887081348</v>
       </c>
     </row>
-    <row r="118" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:29" x14ac:dyDescent="0.35">
       <c r="L118">
         <f>51/5</f>
         <v>10.199999999999999</v>
@@ -4894,12 +4912,12 @@
         <v>10.198039027185569</v>
       </c>
     </row>
-    <row r="120" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:29" x14ac:dyDescent="0.35">
       <c r="H120">
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:29" x14ac:dyDescent="0.35">
       <c r="H121">
         <v>5</v>
       </c>
@@ -4908,7 +4926,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="122" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:29" x14ac:dyDescent="0.35">
       <c r="H122">
         <v>10</v>
       </c>
@@ -4919,7 +4937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F123">
         <v>-240</v>
       </c>
@@ -4959,7 +4977,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="124" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F124">
         <v>-840</v>
       </c>
@@ -4999,7 +5017,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="125" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F125">
         <v>-540</v>
       </c>
@@ -5035,7 +5053,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="126" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F126">
         <v>-440</v>
       </c>
@@ -5075,7 +5093,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="127" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F127">
         <v>2060</v>
       </c>
@@ -5111,7 +5129,7 @@
         <v>10609</v>
       </c>
     </row>
-    <row r="128" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:29" x14ac:dyDescent="0.35">
       <c r="W128">
         <v>2</v>
       </c>
@@ -5120,7 +5138,7 @@
         <v>1.4142135623730951</v>
       </c>
     </row>
-    <row r="129" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="129" spans="5:24" x14ac:dyDescent="0.35">
       <c r="J129">
         <f>SUM(J123:J128)</f>
         <v>13730</v>
@@ -5141,7 +5159,7 @@
         <v>1.7320508075688772</v>
       </c>
     </row>
-    <row r="130" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="130" spans="5:24" x14ac:dyDescent="0.35">
       <c r="J130">
         <f>SQRT(J129)</f>
         <v>117.17508267545622</v>
@@ -5155,7 +5173,7 @@
         <v>117.17508267545622</v>
       </c>
     </row>
-    <row r="131" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="131" spans="5:24" x14ac:dyDescent="0.35">
       <c r="W131">
         <f>W128/W129</f>
         <v>0.66666666666666663</v>
@@ -5165,7 +5183,7 @@
         <v>0.81649658092772615</v>
       </c>
     </row>
-    <row r="132" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="132" spans="5:24" x14ac:dyDescent="0.35">
       <c r="F132">
         <f>G132*H132</f>
         <v>117</v>
@@ -5211,7 +5229,7 @@
         <v>0.81649658092772603</v>
       </c>
     </row>
-    <row r="133" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="133" spans="5:24" x14ac:dyDescent="0.35">
       <c r="I133">
         <f>I132*20</f>
         <v>2340</v>
@@ -5221,7 +5239,7 @@
         <v>-41</v>
       </c>
     </row>
-    <row r="135" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="135" spans="5:24" x14ac:dyDescent="0.35">
       <c r="H135">
         <f>I135/2</f>
         <v>59</v>
@@ -5246,13 +5264,13 @@
         <v>13.857142857142858</v>
       </c>
     </row>
-    <row r="136" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="136" spans="5:24" x14ac:dyDescent="0.35">
       <c r="I136">
         <f>I135*20</f>
         <v>2360</v>
       </c>
     </row>
-    <row r="139" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="139" spans="5:24" x14ac:dyDescent="0.35">
       <c r="E139">
         <v>19</v>
       </c>
@@ -5271,7 +5289,7 @@
         <v>94.973680564670133</v>
       </c>
     </row>
-    <row r="140" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="140" spans="5:24" x14ac:dyDescent="0.35">
       <c r="F140">
         <v>1805</v>
       </c>
@@ -5283,13 +5301,13 @@
         <v>24010</v>
       </c>
     </row>
-    <row r="141" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="141" spans="5:24" x14ac:dyDescent="0.35">
       <c r="J141">
         <f>J139/J140</f>
         <v>360.8</v>
       </c>
     </row>
-    <row r="142" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="142" spans="5:24" x14ac:dyDescent="0.35">
       <c r="M142">
         <v>7</v>
       </c>
@@ -5307,4 +5325,958 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{666D1E91-ED7C-475C-A636-9777A928839D}">
+  <dimension ref="A3:O72"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11">
+        <v>4</v>
+      </c>
+      <c r="C3" s="11">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <f>B3/C3</f>
+        <v>0.8</v>
+      </c>
+      <c r="E3">
+        <f>SQRT(D3)</f>
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="F3">
+        <f>E3*A3</f>
+        <v>1.7888543819998317</v>
+      </c>
+      <c r="G3">
+        <f>F3*D3</f>
+        <v>1.4310835055998654</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="11">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11">
+        <v>4</v>
+      </c>
+      <c r="C4" s="11">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4" si="0">B4/C4</f>
+        <v>0.8</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4" si="1">SQRT(D4)</f>
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="F4">
+        <f t="shared" ref="F4" si="2">E4*A4</f>
+        <v>1.7888543819998317</v>
+      </c>
+      <c r="G4">
+        <f t="shared" ref="G4" si="3">F4*D4</f>
+        <v>1.4310835055998654</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B13">
+        <f t="shared" ref="B13:B14" si="4">B14-1</f>
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <f t="shared" ref="C13:C16" si="5">SQRT(B13)</f>
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <f t="shared" ref="D13" si="6">C13/B13</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B14">
+        <f t="shared" ref="B14:B16" si="7">B15-1</f>
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="5"/>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="D14">
+        <f t="shared" ref="D14:D16" si="8">C14/B14</f>
+        <v>0.70710678118654757</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B15">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="5"/>
+        <v>1.7320508075688772</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="8"/>
+        <v>0.57735026918962573</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B16">
+        <f>B17-1</f>
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="8"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <f>SQRT(B17)</f>
+        <v>2.2360679774997898</v>
+      </c>
+      <c r="D17">
+        <f>C17/B17</f>
+        <v>0.44721359549995798</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18">
+        <f>B17+1</f>
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <f t="shared" ref="C18:C58" si="9">SQRT(B18)</f>
+        <v>2.4494897427831779</v>
+      </c>
+      <c r="D18">
+        <f t="shared" ref="D18:D27" si="10">C18/B18</f>
+        <v>0.40824829046386296</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B19">
+        <f t="shared" ref="B19:B27" si="11">B18+1</f>
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="9"/>
+        <v>2.6457513110645907</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="10"/>
+        <v>0.37796447300922725</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="9"/>
+        <v>2.8284271247461903</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="10"/>
+        <v>0.35355339059327379</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21">
+        <f t="shared" si="11"/>
+        <v>9</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="10"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B22">
+        <f t="shared" si="11"/>
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="9"/>
+        <v>3.1622776601683795</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="10"/>
+        <v>0.31622776601683794</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B23">
+        <f t="shared" si="11"/>
+        <v>11</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="9"/>
+        <v>3.3166247903553998</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="10"/>
+        <v>0.30151134457776363</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B24">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="9"/>
+        <v>3.4641016151377544</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="10"/>
+        <v>0.28867513459481287</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B25">
+        <f t="shared" si="11"/>
+        <v>13</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="9"/>
+        <v>3.6055512754639891</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="10"/>
+        <v>0.27735009811261457</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B26">
+        <f t="shared" si="11"/>
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="9"/>
+        <v>3.7416573867739413</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="10"/>
+        <v>0.2672612419124244</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B27">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="9"/>
+        <v>3.872983346207417</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="10"/>
+        <v>0.25819888974716115</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B28">
+        <f t="shared" ref="B28:B58" si="12">B27+1</f>
+        <v>16</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <f t="shared" ref="D28:D58" si="13">C28/B28</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B29">
+        <f t="shared" si="12"/>
+        <v>17</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="9"/>
+        <v>4.1231056256176606</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="13"/>
+        <v>0.24253562503633297</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B30">
+        <f t="shared" si="12"/>
+        <v>18</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="9"/>
+        <v>4.2426406871192848</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="13"/>
+        <v>0.23570226039551581</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B31">
+        <f t="shared" si="12"/>
+        <v>19</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="9"/>
+        <v>4.358898943540674</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="13"/>
+        <v>0.2294157338705618</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B32">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="9"/>
+        <v>4.4721359549995796</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="13"/>
+        <v>0.22360679774997899</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33">
+        <f t="shared" si="12"/>
+        <v>21</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="9"/>
+        <v>4.5825756949558398</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="13"/>
+        <v>0.21821789023599236</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34">
+        <f t="shared" si="12"/>
+        <v>22</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="9"/>
+        <v>4.6904157598234297</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="13"/>
+        <v>0.21320071635561044</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35">
+        <f t="shared" si="12"/>
+        <v>23</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="9"/>
+        <v>4.7958315233127191</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="13"/>
+        <v>0.20851441405707474</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B36">
+        <f t="shared" si="12"/>
+        <v>24</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="9"/>
+        <v>4.8989794855663558</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="13"/>
+        <v>0.20412414523193148</v>
+      </c>
+      <c r="F36">
+        <v>4</v>
+      </c>
+      <c r="G36">
+        <f>SQRT(F36)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37">
+        <f t="shared" si="12"/>
+        <v>25</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="13"/>
+        <v>0.2</v>
+      </c>
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="G37">
+        <f>SQRT(F37)</f>
+        <v>2.2360679774997898</v>
+      </c>
+      <c r="I37">
+        <f>F37/F36</f>
+        <v>1.25</v>
+      </c>
+      <c r="J37">
+        <f>G37/G36</f>
+        <v>1.1180339887498949</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38">
+        <f t="shared" si="12"/>
+        <v>26</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="9"/>
+        <v>5.0990195135927845</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="13"/>
+        <v>0.19611613513818402</v>
+      </c>
+      <c r="F38">
+        <f>F36/F37</f>
+        <v>0.8</v>
+      </c>
+      <c r="J38" t="b">
+        <f>J37=J39</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B39">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="9"/>
+        <v>5.196152422706632</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="13"/>
+        <v>0.19245008972987526</v>
+      </c>
+      <c r="F39">
+        <f>SQRT(F38)</f>
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="G39">
+        <f>G36/G37</f>
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="H39" t="b">
+        <f>G39=F39</f>
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <f>I39/G39</f>
+        <v>1.1180339887498949</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="9"/>
+        <v>5.2915026221291814</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="13"/>
+        <v>0.18898223650461363</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B41">
+        <f t="shared" si="12"/>
+        <v>29</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="9"/>
+        <v>5.3851648071345037</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="13"/>
+        <v>0.18569533817705186</v>
+      </c>
+      <c r="F41">
+        <f>F40*F39</f>
+        <v>1.7888543819998317</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <f>G41/F41</f>
+        <v>0.55901699437494745</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+      <c r="J41">
+        <f>I41*H41</f>
+        <v>1.1180339887498949</v>
+      </c>
+      <c r="K41">
+        <v>5</v>
+      </c>
+      <c r="L41">
+        <f>J41/K41</f>
+        <v>0.22360679774997899</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B42">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="9"/>
+        <v>5.4772255750516612</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="13"/>
+        <v>0.18257418583505539</v>
+      </c>
+      <c r="F42">
+        <f>F38*F41</f>
+        <v>1.4310835055998654</v>
+      </c>
+      <c r="H42">
+        <f>H41*I53</f>
+        <v>0.1118033988749895</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B43">
+        <f t="shared" si="12"/>
+        <v>31</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="9"/>
+        <v>5.5677643628300215</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="13"/>
+        <v>0.17960530202677488</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B44">
+        <f t="shared" si="12"/>
+        <v>32</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="9"/>
+        <v>5.6568542494923806</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="13"/>
+        <v>0.17677669529663689</v>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+      <c r="H44">
+        <v>2</v>
+      </c>
+      <c r="O44" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B45">
+        <f t="shared" si="12"/>
+        <v>33</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="9"/>
+        <v>5.7445626465380286</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="13"/>
+        <v>0.17407765595569782</v>
+      </c>
+      <c r="F45" s="20">
+        <f>SQRT(F44)/F44</f>
+        <v>0.44721359549995798</v>
+      </c>
+      <c r="G45" t="b">
+        <f>F45=O45</f>
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>5</v>
+      </c>
+      <c r="I45">
+        <f>H44/H45</f>
+        <v>0.4</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45">
+        <v>2</v>
+      </c>
+      <c r="M45">
+        <f>L45*F39</f>
+        <v>1.7888543819998317</v>
+      </c>
+      <c r="N45">
+        <f>K45/M45</f>
+        <v>0.55901699437494745</v>
+      </c>
+      <c r="O45" s="20">
+        <f>N45*F38</f>
+        <v>0.44721359549995798</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B46">
+        <f t="shared" si="12"/>
+        <v>34</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="9"/>
+        <v>5.8309518948453007</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="13"/>
+        <v>0.17149858514250885</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B47">
+        <f t="shared" si="12"/>
+        <v>35</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="9"/>
+        <v>5.9160797830996161</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="13"/>
+        <v>0.16903085094570333</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B48">
+        <f t="shared" si="12"/>
+        <v>36</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="9"/>
+        <v>6</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="13"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F48">
+        <f>SQRT(F47)</f>
+        <v>2.2360679774997898</v>
+      </c>
+      <c r="H48">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B49">
+        <f t="shared" si="12"/>
+        <v>37</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="9"/>
+        <v>6.0827625302982193</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="13"/>
+        <v>0.16439898730535729</v>
+      </c>
+      <c r="F49">
+        <v>4</v>
+      </c>
+      <c r="H49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B50">
+        <f t="shared" si="12"/>
+        <v>38</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="9"/>
+        <v>6.164414002968976</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="13"/>
+        <v>0.16222142113076252</v>
+      </c>
+      <c r="F50">
+        <f>SQRT(F49)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B51">
+        <f t="shared" si="12"/>
+        <v>39</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="9"/>
+        <v>6.2449979983983983</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="13"/>
+        <v>0.16012815380508713</v>
+      </c>
+      <c r="F51">
+        <f>F48/F50</f>
+        <v>1.1180339887498949</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B52">
+        <f t="shared" si="12"/>
+        <v>40</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="9"/>
+        <v>6.324555320336759</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="13"/>
+        <v>0.15811388300841897</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B53">
+        <f t="shared" si="12"/>
+        <v>41</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="9"/>
+        <v>6.4031242374328485</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="13"/>
+        <v>0.15617376188860607</v>
+      </c>
+      <c r="H53">
+        <v>5</v>
+      </c>
+      <c r="I53">
+        <f>H52/H53</f>
+        <v>0.2</v>
+      </c>
+      <c r="J53" s="21">
+        <f>I53*H41</f>
+        <v>0.1118033988749895</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B54">
+        <f t="shared" si="12"/>
+        <v>42</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="9"/>
+        <v>6.4807406984078604</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="13"/>
+        <v>0.15430334996209191</v>
+      </c>
+      <c r="F54">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B55">
+        <f t="shared" si="12"/>
+        <v>43</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="9"/>
+        <v>6.5574385243020004</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="13"/>
+        <v>0.15249857033260467</v>
+      </c>
+      <c r="F55">
+        <f>SQRT(F54)</f>
+        <v>22.360679774997898</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B56">
+        <f t="shared" si="12"/>
+        <v>44</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="9"/>
+        <v>6.6332495807107996</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="13"/>
+        <v>0.15075567228888181</v>
+      </c>
+      <c r="F56">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B57">
+        <f t="shared" si="12"/>
+        <v>45</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="9"/>
+        <v>6.7082039324993694</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="13"/>
+        <v>0.14907119849998599</v>
+      </c>
+      <c r="F57">
+        <f>SQRT(F56)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B58">
+        <f t="shared" si="12"/>
+        <v>46</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="9"/>
+        <v>6.7823299831252681</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="13"/>
+        <v>0.14744195615489714</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="F60">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="F61">
+        <f>SQRT(F60)</f>
+        <v>2.8284271247461903</v>
+      </c>
+    </row>
+    <row r="66" spans="6:10" x14ac:dyDescent="0.35">
+      <c r="G66">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="6:10" x14ac:dyDescent="0.35">
+      <c r="G67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="6:10" x14ac:dyDescent="0.35">
+      <c r="F68">
+        <v>2</v>
+      </c>
+      <c r="G68">
+        <f>F68*SQRT(G66/G67)</f>
+        <v>1.7888543819998317</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="6:10" x14ac:dyDescent="0.35">
+      <c r="H69">
+        <f>H68/G68</f>
+        <v>0.55901699437494745</v>
+      </c>
+      <c r="I69">
+        <f>H69*J69</f>
+        <v>0.1118033988749895</v>
+      </c>
+      <c r="J69">
+        <f>H68/I68</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="71" spans="6:10" x14ac:dyDescent="0.35">
+      <c r="F71">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" spans="6:10" x14ac:dyDescent="0.35">
+      <c r="F72">
+        <f>SQRT(F71)</f>
+        <v>8.9442719099991592</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <f>G72/F72</f>
+        <v>0.11180339887498948</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Edu/Linear_algebra/linal_session_task.xlsx
+++ b/Edu/Linear_algebra/linal_session_task.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iTonyJah\DataScience\Edu\Linear_algebra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LysogorA\DataScience\Edu\Linear_algebra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F698CE-2E4E-420F-9683-0F89304BC822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718BEFFB-9276-4255-8461-A2CDAF945A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="st" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="98">
   <si>
     <t>Рабочая таблица с данными:</t>
   </si>
@@ -313,13 +314,36 @@
   </si>
   <si>
     <t>меньше половины</t>
+  </si>
+  <si>
+    <t>x_1</t>
+  </si>
+  <si>
+    <t>x_2</t>
+  </si>
+  <si>
+    <t>x_3</t>
+  </si>
+  <si>
+    <t>x_4</t>
+  </si>
+  <si>
+    <t>x_5</t>
+  </si>
+  <si>
+    <t>y</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="9" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,8 +414,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -419,6 +450,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,7 +522,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -524,6 +561,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3094,18 +3137,18 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:AD142"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AD156"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="25" max="25" width="12.7265625" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3128,7 +3171,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -3151,7 +3194,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -3174,7 +3217,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -3197,7 +3240,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -3220,7 +3263,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -3243,32 +3286,32 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="23" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -3276,7 +3319,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>3</v>
       </c>
@@ -3290,7 +3333,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>1</v>
       </c>
@@ -3304,7 +3347,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>2</v>
       </c>
@@ -3318,22 +3361,22 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -3341,12 +3384,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -3354,42 +3397,42 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>28</v>
       </c>
@@ -3400,7 +3443,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <f>F38*J$38+G38*J$39+H38*J$40</f>
         <v>93900</v>
@@ -3422,7 +3465,7 @@
       </c>
       <c r="L38" s="8"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <f t="shared" ref="A39:A40" si="0">F39*J$38+G39*J$39+H39*J$40</f>
         <v>52100</v>
@@ -3444,7 +3487,7 @@
       </c>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <f t="shared" si="0"/>
         <v>80200</v>
@@ -3466,23 +3509,23 @@
       </c>
       <c r="L40" s="8"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B41" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="J43" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
         <f>F44*J$44+G44*J$45+H44*J$46</f>
         <v>494200</v>
@@ -3504,7 +3547,7 @@
       </c>
       <c r="L44" s="8"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
         <f t="shared" ref="A45:A46" si="1">F45*J$44+G45*J$45+H45*J$46</f>
         <v>9960900</v>
@@ -3526,7 +3569,7 @@
       </c>
       <c r="L45" s="8"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
         <f t="shared" si="1"/>
         <v>494200</v>
@@ -3548,22 +3591,22 @@
       </c>
       <c r="L46" s="8"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B47" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B50" s="6" t="s">
         <v>43</v>
       </c>
@@ -3571,7 +3614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -3603,7 +3646,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="12">
         <f t="shared" ref="A52:A53" si="4">$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -3635,7 +3678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="12">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -3667,12 +3710,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>38</v>
       </c>
@@ -3683,7 +3726,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -3706,7 +3749,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
         <f>$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -3729,7 +3772,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="12">
         <f>$F53*J$51+$G53*J$52+$H53*J$53</f>
         <v>14</v>
@@ -3752,19 +3795,19 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B59" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>51</v>
       </c>
       <c r="B60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G61" s="6" t="s">
         <v>43</v>
       </c>
@@ -3772,7 +3815,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="12">
         <f>F62*J$62+G62*J$63+H62*J$64</f>
         <v>494200</v>
@@ -3793,7 +3836,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="12">
         <f t="shared" ref="A63:A64" si="5">F63*J$62+G63*J$63+H63*J$64</f>
         <v>9960900</v>
@@ -3814,7 +3857,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="12">
         <f t="shared" si="5"/>
         <v>494200</v>
@@ -3835,23 +3878,23 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B65" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B67" s="8"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C68" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="12">
         <v>494200</v>
       </c>
@@ -3859,7 +3902,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="12">
         <v>9960900</v>
       </c>
@@ -3867,7 +3910,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="12">
         <v>494200</v>
       </c>
@@ -3875,77 +3918,77 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="23" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>1</v>
       </c>
@@ -3968,7 +4011,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C90" s="16"/>
       <c r="D90" s="16"/>
       <c r="E90" s="16" t="s">
@@ -3980,7 +4023,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B91" s="7">
         <v>3</v>
       </c>
@@ -4003,7 +4046,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B92" s="7">
         <v>1</v>
       </c>
@@ -4026,7 +4069,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B93" s="7">
         <v>2</v>
       </c>
@@ -4049,7 +4092,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B94" s="7">
         <v>3</v>
       </c>
@@ -4072,7 +4115,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B95" s="7">
         <v>1</v>
       </c>
@@ -4095,17 +4138,17 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>76</v>
       </c>
@@ -4148,7 +4191,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>77</v>
       </c>
@@ -4185,7 +4228,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>78</v>
       </c>
@@ -4202,7 +4245,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B102" s="7">
         <f>B91-B$100</f>
         <v>1</v>
@@ -4246,7 +4289,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B103" s="7">
         <f t="shared" ref="B103:G103" si="10">B92-B$100</f>
         <v>-1</v>
@@ -4296,7 +4339,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B104" s="7">
         <f t="shared" ref="B104:G104" si="14">B93-B$100</f>
         <v>0</v>
@@ -4348,7 +4391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B105" s="7">
         <f t="shared" ref="B105:G105" si="16">B94-B$100</f>
         <v>1</v>
@@ -4400,7 +4443,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B106" s="7">
         <f t="shared" ref="B106:G106" si="19">B95-B$100</f>
         <v>-1</v>
@@ -4448,7 +4491,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>79</v>
       </c>
@@ -4494,7 +4537,7 @@
         <v>0.99972295331231709</v>
       </c>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>80</v>
       </c>
@@ -4523,7 +4566,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B109">
         <f>(B102^2+B103^2+B104^2+B105^2+B106^2)^(1/2)</f>
         <v>2</v>
@@ -4582,7 +4625,7 @@
         <v>18.994736112934024</v>
       </c>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>81</v>
       </c>
@@ -4595,7 +4638,7 @@
         <v>8.9554452708952432</v>
       </c>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B111" s="18">
         <f>B102/B$109</f>
         <v>0.5</v>
@@ -4623,7 +4666,7 @@
         <v>-0.10241085157359611</v>
       </c>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B112" s="18">
         <f t="shared" ref="B112:I115" si="23">B103/B$109</f>
         <v>-0.5</v>
@@ -4669,7 +4712,7 @@
         <v>1.7888543819998317</v>
       </c>
     </row>
-    <row r="113" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B113" s="18">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -4727,7 +4770,7 @@
         <v>0.89442719099991586</v>
       </c>
     </row>
-    <row r="114" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B114" s="18">
         <f t="shared" si="23"/>
         <v>0.5</v>
@@ -4790,7 +4833,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="115" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B115" s="18">
         <f t="shared" si="23"/>
         <v>-0.5</v>
@@ -4849,7 +4892,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="117" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:29" x14ac:dyDescent="0.25">
       <c r="Z117" t="s">
         <v>84</v>
       </c>
@@ -4862,7 +4905,7 @@
         <v>8.717797887081348</v>
       </c>
     </row>
-    <row r="118" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:29" x14ac:dyDescent="0.25">
       <c r="L118">
         <f>51/5</f>
         <v>10.199999999999999</v>
@@ -4912,12 +4955,12 @@
         <v>10.198039027185569</v>
       </c>
     </row>
-    <row r="120" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:29" x14ac:dyDescent="0.25">
       <c r="H120">
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:29" x14ac:dyDescent="0.25">
       <c r="H121">
         <v>5</v>
       </c>
@@ -4926,7 +4969,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="122" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:29" x14ac:dyDescent="0.25">
       <c r="H122">
         <v>10</v>
       </c>
@@ -4937,7 +4980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F123">
         <v>-240</v>
       </c>
@@ -4977,7 +5020,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="124" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F124">
         <v>-840</v>
       </c>
@@ -5017,7 +5060,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="125" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F125">
         <v>-540</v>
       </c>
@@ -5053,7 +5096,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="126" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F126">
         <v>-440</v>
       </c>
@@ -5093,7 +5136,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="127" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F127">
         <v>2060</v>
       </c>
@@ -5129,7 +5172,7 @@
         <v>10609</v>
       </c>
     </row>
-    <row r="128" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:29" x14ac:dyDescent="0.25">
       <c r="W128">
         <v>2</v>
       </c>
@@ -5138,7 +5181,7 @@
         <v>1.4142135623730951</v>
       </c>
     </row>
-    <row r="129" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="129" spans="5:24" x14ac:dyDescent="0.25">
       <c r="J129">
         <f>SUM(J123:J128)</f>
         <v>13730</v>
@@ -5159,7 +5202,7 @@
         <v>1.7320508075688772</v>
       </c>
     </row>
-    <row r="130" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="130" spans="5:24" x14ac:dyDescent="0.25">
       <c r="J130">
         <f>SQRT(J129)</f>
         <v>117.17508267545622</v>
@@ -5173,7 +5216,7 @@
         <v>117.17508267545622</v>
       </c>
     </row>
-    <row r="131" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="131" spans="5:24" x14ac:dyDescent="0.25">
       <c r="W131">
         <f>W128/W129</f>
         <v>0.66666666666666663</v>
@@ -5183,7 +5226,7 @@
         <v>0.81649658092772615</v>
       </c>
     </row>
-    <row r="132" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="132" spans="5:24" x14ac:dyDescent="0.25">
       <c r="F132">
         <f>G132*H132</f>
         <v>117</v>
@@ -5229,7 +5272,7 @@
         <v>0.81649658092772603</v>
       </c>
     </row>
-    <row r="133" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="133" spans="5:24" x14ac:dyDescent="0.25">
       <c r="I133">
         <f>I132*20</f>
         <v>2340</v>
@@ -5239,7 +5282,7 @@
         <v>-41</v>
       </c>
     </row>
-    <row r="135" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="135" spans="5:24" x14ac:dyDescent="0.25">
       <c r="H135">
         <f>I135/2</f>
         <v>59</v>
@@ -5264,13 +5307,13 @@
         <v>13.857142857142858</v>
       </c>
     </row>
-    <row r="136" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="136" spans="5:24" x14ac:dyDescent="0.25">
       <c r="I136">
         <f>I135*20</f>
         <v>2360</v>
       </c>
     </row>
-    <row r="139" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="139" spans="5:24" x14ac:dyDescent="0.25">
       <c r="E139">
         <v>19</v>
       </c>
@@ -5289,7 +5332,7 @@
         <v>94.973680564670133</v>
       </c>
     </row>
-    <row r="140" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="140" spans="5:24" x14ac:dyDescent="0.25">
       <c r="F140">
         <v>1805</v>
       </c>
@@ -5301,13 +5344,13 @@
         <v>24010</v>
       </c>
     </row>
-    <row r="141" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="141" spans="5:24" x14ac:dyDescent="0.25">
       <c r="J141">
         <f>J139/J140</f>
         <v>360.8</v>
       </c>
     </row>
-    <row r="142" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="142" spans="5:24" x14ac:dyDescent="0.25">
       <c r="M142">
         <v>7</v>
       </c>
@@ -5318,6 +5361,70 @@
       <c r="O142">
         <f>N142^2</f>
         <v>2401</v>
+      </c>
+    </row>
+    <row r="148" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D149">
+        <v>5</v>
+      </c>
+      <c r="E149">
+        <f>SQRT(D149)</f>
+        <v>2.2360679774997898</v>
+      </c>
+    </row>
+    <row r="150" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D150">
+        <f>D148/D149</f>
+        <v>0.4</v>
+      </c>
+      <c r="E150">
+        <f>D150*E149</f>
+        <v>0.89442719099991597</v>
+      </c>
+    </row>
+    <row r="151" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C151">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C152">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C153">
+        <f>C151/C152</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="154" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C154">
+        <f>SQRT(C153)</f>
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="E154">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="155" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="E155">
+        <f>SQRT(E154)</f>
+        <v>4.4721359549995796</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="G156">
+        <f>G155/E155</f>
+        <v>0.22360679774997896</v>
       </c>
     </row>
   </sheetData>
@@ -5330,9 +5437,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{666D1E91-ED7C-475C-A636-9777A928839D}">
   <dimension ref="A3:O72"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -5359,7 +5466,7 @@
         <v>1.4310835055998654</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -5386,9 +5493,9 @@
         <v>1.4310835055998654</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13">
-        <f t="shared" ref="B13:B14" si="4">B14-1</f>
+        <f t="shared" ref="B13" si="4">B14-1</f>
         <v>1</v>
       </c>
       <c r="C13">
@@ -5400,9 +5507,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14">
-        <f t="shared" ref="B14:B16" si="7">B15-1</f>
+        <f t="shared" ref="B14:B15" si="7">B15-1</f>
         <v>2</v>
       </c>
       <c r="C14">
@@ -5414,7 +5521,7 @@
         <v>0.70710678118654757</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15">
         <f t="shared" si="7"/>
         <v>3</v>
@@ -5428,7 +5535,7 @@
         <v>0.57735026918962573</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16">
         <f>B17-1</f>
         <v>4</v>
@@ -5442,7 +5549,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>5</v>
       </c>
@@ -5455,7 +5562,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18">
         <f>B17+1</f>
         <v>6</v>
@@ -5469,7 +5576,7 @@
         <v>0.40824829046386296</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19">
         <f t="shared" ref="B19:B27" si="11">B18+1</f>
         <v>7</v>
@@ -5483,7 +5590,7 @@
         <v>0.37796447300922725</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20">
         <f t="shared" si="11"/>
         <v>8</v>
@@ -5497,7 +5604,7 @@
         <v>0.35355339059327379</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21">
         <f t="shared" si="11"/>
         <v>9</v>
@@ -5511,7 +5618,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22">
         <f t="shared" si="11"/>
         <v>10</v>
@@ -5525,7 +5632,7 @@
         <v>0.31622776601683794</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23">
         <f t="shared" si="11"/>
         <v>11</v>
@@ -5539,7 +5646,7 @@
         <v>0.30151134457776363</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24">
         <f t="shared" si="11"/>
         <v>12</v>
@@ -5553,7 +5660,7 @@
         <v>0.28867513459481287</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25">
         <f t="shared" si="11"/>
         <v>13</v>
@@ -5567,7 +5674,7 @@
         <v>0.27735009811261457</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26">
         <f t="shared" si="11"/>
         <v>14</v>
@@ -5581,7 +5688,7 @@
         <v>0.2672612419124244</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27">
         <f t="shared" si="11"/>
         <v>15</v>
@@ -5595,7 +5702,7 @@
         <v>0.25819888974716115</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28">
         <f t="shared" ref="B28:B58" si="12">B27+1</f>
         <v>16</v>
@@ -5609,7 +5716,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29">
         <f t="shared" si="12"/>
         <v>17</v>
@@ -5623,7 +5730,7 @@
         <v>0.24253562503633297</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30">
         <f t="shared" si="12"/>
         <v>18</v>
@@ -5637,7 +5744,7 @@
         <v>0.23570226039551581</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31">
         <f t="shared" si="12"/>
         <v>19</v>
@@ -5651,7 +5758,7 @@
         <v>0.2294157338705618</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32">
         <f t="shared" si="12"/>
         <v>20</v>
@@ -5665,7 +5772,7 @@
         <v>0.22360679774997899</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33">
         <f t="shared" si="12"/>
         <v>21</v>
@@ -5679,7 +5786,7 @@
         <v>0.21821789023599236</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34">
         <f t="shared" si="12"/>
         <v>22</v>
@@ -5693,7 +5800,7 @@
         <v>0.21320071635561044</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35">
         <f t="shared" si="12"/>
         <v>23</v>
@@ -5707,7 +5814,7 @@
         <v>0.20851441405707474</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36">
         <f t="shared" si="12"/>
         <v>24</v>
@@ -5728,7 +5835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B37">
         <f t="shared" si="12"/>
         <v>25</v>
@@ -5757,7 +5864,7 @@
         <v>1.1180339887498949</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B38">
         <f t="shared" si="12"/>
         <v>26</v>
@@ -5779,7 +5886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B39">
         <f t="shared" si="12"/>
         <v>27</v>
@@ -5812,7 +5919,7 @@
         <v>1.1180339887498949</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B40">
         <f t="shared" si="12"/>
         <v>28</v>
@@ -5829,7 +5936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B41">
         <f t="shared" si="12"/>
         <v>29</v>
@@ -5868,7 +5975,7 @@
         <v>0.22360679774997899</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B42">
         <f t="shared" si="12"/>
         <v>30</v>
@@ -5890,7 +5997,7 @@
         <v>0.1118033988749895</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43">
         <f t="shared" si="12"/>
         <v>31</v>
@@ -5904,7 +6011,7 @@
         <v>0.17960530202677488</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B44">
         <f t="shared" si="12"/>
         <v>32</v>
@@ -5927,7 +6034,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B45">
         <f t="shared" si="12"/>
         <v>33</v>
@@ -5974,7 +6081,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B46">
         <f t="shared" si="12"/>
         <v>34</v>
@@ -5988,7 +6095,7 @@
         <v>0.17149858514250885</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47">
         <f t="shared" si="12"/>
         <v>35</v>
@@ -6005,7 +6112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B48">
         <f t="shared" si="12"/>
         <v>36</v>
@@ -6026,7 +6133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49">
         <f t="shared" si="12"/>
         <v>37</v>
@@ -6046,7 +6153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50">
         <f t="shared" si="12"/>
         <v>38</v>
@@ -6064,7 +6171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51">
         <f t="shared" si="12"/>
         <v>39</v>
@@ -6082,7 +6189,7 @@
         <v>1.1180339887498949</v>
       </c>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52">
         <f t="shared" si="12"/>
         <v>40</v>
@@ -6099,7 +6206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53">
         <f t="shared" si="12"/>
         <v>41</v>
@@ -6124,7 +6231,7 @@
         <v>0.1118033988749895</v>
       </c>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54">
         <f t="shared" si="12"/>
         <v>42</v>
@@ -6141,7 +6248,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55">
         <f t="shared" si="12"/>
         <v>43</v>
@@ -6159,7 +6266,7 @@
         <v>22.360679774997898</v>
       </c>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56">
         <f t="shared" si="12"/>
         <v>44</v>
@@ -6176,7 +6283,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57">
         <f t="shared" si="12"/>
         <v>45</v>
@@ -6194,7 +6301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58">
         <f t="shared" si="12"/>
         <v>46</v>
@@ -6208,28 +6315,28 @@
         <v>0.14744195615489714</v>
       </c>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="F60">
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="F61">
         <f>SQRT(F60)</f>
         <v>2.8284271247461903</v>
       </c>
     </row>
-    <row r="66" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="6:10" x14ac:dyDescent="0.25">
       <c r="G66">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="6:10" x14ac:dyDescent="0.25">
       <c r="G67">
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F68">
         <v>2</v>
       </c>
@@ -6244,7 +6351,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="6:10" x14ac:dyDescent="0.25">
       <c r="H69">
         <f>H68/G68</f>
         <v>0.55901699437494745</v>
@@ -6258,12 +6365,12 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="71" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F71">
         <v>80</v>
       </c>
     </row>
-    <row r="72" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F72">
         <f>SQRT(F71)</f>
         <v>8.9442719099991592</v>
@@ -6279,4 +6386,794 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82BA3844-AF00-4659-9CA6-FDAA4D3C4028}">
+  <dimension ref="A2:T33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K4">
+        <f>K2/K3</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <f>SQRT(K4)</f>
+        <v>0.89442719099991586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <f>K5*J5</f>
+        <v>1.7888543819998317</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <f>K4</f>
+        <v>0.8</v>
+      </c>
+      <c r="K7">
+        <f>J6/K6</f>
+        <v>0.55901699437494745</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>1804</v>
+      </c>
+      <c r="K8">
+        <f>K7*J7</f>
+        <v>0.44721359549995798</v>
+      </c>
+      <c r="Q8">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B9" t="str">
+        <f>C17</f>
+        <v>x_1</v>
+      </c>
+      <c r="E9">
+        <v>1805</v>
+      </c>
+      <c r="F9" t="str">
+        <f>D17</f>
+        <v>x_2</v>
+      </c>
+      <c r="I9" t="str">
+        <f>E17</f>
+        <v>x_3</v>
+      </c>
+      <c r="L9" t="str">
+        <f>F17</f>
+        <v>x_4</v>
+      </c>
+      <c r="O9" t="str">
+        <f>G17</f>
+        <v>x_5</v>
+      </c>
+      <c r="Q9">
+        <v>13730</v>
+      </c>
+      <c r="R9" t="str">
+        <f>H17</f>
+        <v>y</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <f>SQRT(E8/E9)</f>
+        <v>0.99972295331231709</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>13689</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" s="7">
+        <v>1</v>
+      </c>
+      <c r="C11" s="23">
+        <f>B11*A$13</f>
+        <v>0.5</v>
+      </c>
+      <c r="E11">
+        <v>95</v>
+      </c>
+      <c r="F11" s="7">
+        <v>29</v>
+      </c>
+      <c r="G11" s="23">
+        <f>F11*E$13</f>
+        <v>0.30534775347842946</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" s="7">
+        <v>1</v>
+      </c>
+      <c r="J11" s="23">
+        <f>I11*H$13</f>
+        <v>0.5</v>
+      </c>
+      <c r="K11">
+        <v>20</v>
+      </c>
+      <c r="L11" s="7">
+        <v>-1</v>
+      </c>
+      <c r="M11" s="23">
+        <f>L11*K$13</f>
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="N11">
+        <v>80</v>
+      </c>
+      <c r="O11" s="7">
+        <v>1</v>
+      </c>
+      <c r="P11" s="23">
+        <f>O11*N$13</f>
+        <v>0.11180339887498948</v>
+      </c>
+      <c r="Q11">
+        <f>SQRT(Q9/Q10)</f>
+        <v>1.0014964331235574</v>
+      </c>
+      <c r="R11" s="7">
+        <v>-12</v>
+      </c>
+      <c r="S11" s="23">
+        <f>R11*Q$13</f>
+        <v>-0.10241085157359613</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12" s="7">
+        <v>-1</v>
+      </c>
+      <c r="C12" s="23">
+        <f t="shared" ref="C12:C15" si="0">B12*A$13</f>
+        <v>-0.5</v>
+      </c>
+      <c r="E12">
+        <f>E11*E10</f>
+        <v>94.973680564670119</v>
+      </c>
+      <c r="F12" s="7">
+        <v>-76</v>
+      </c>
+      <c r="G12" s="23">
+        <f t="shared" ref="G12:G15" si="1">F12*E$13</f>
+        <v>-0.80022169877105653</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12" s="7">
+        <v>-1</v>
+      </c>
+      <c r="J12" s="23">
+        <f t="shared" ref="J12:J15" si="2">I12*H$13</f>
+        <v>-0.5</v>
+      </c>
+      <c r="K12">
+        <f>SQRT(K11)</f>
+        <v>4.4721359549995796</v>
+      </c>
+      <c r="L12" s="7">
+        <v>-1</v>
+      </c>
+      <c r="M12" s="23">
+        <f t="shared" ref="M12:M15" si="3">L12*K$13</f>
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="N12">
+        <f>SQRT(N11)</f>
+        <v>8.9442719099991592</v>
+      </c>
+      <c r="O12" s="7">
+        <v>1</v>
+      </c>
+      <c r="P12" s="23">
+        <f t="shared" ref="P12:P15" si="4">O12*N$13</f>
+        <v>0.11180339887498948</v>
+      </c>
+      <c r="Q12">
+        <f>Q11*Q8</f>
+        <v>117.17508267545621</v>
+      </c>
+      <c r="R12" s="7">
+        <v>-42</v>
+      </c>
+      <c r="S12" s="23">
+        <f t="shared" ref="S12:S15" si="5">R12*Q$13</f>
+        <v>-0.35843798050758646</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="20">
+        <f>A11/A12</f>
+        <v>0.5</v>
+      </c>
+      <c r="B13" s="7">
+        <v>0</v>
+      </c>
+      <c r="C13" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E13" s="20">
+        <f>E7/E12</f>
+        <v>1.0529232878566533E-2</v>
+      </c>
+      <c r="F13" s="7">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="23">
+        <f t="shared" si="1"/>
+        <v>-1.0529232878566533E-2</v>
+      </c>
+      <c r="H13" s="20">
+        <f>H11/H12</f>
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="7">
+        <v>0</v>
+      </c>
+      <c r="J13" s="23">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="20">
+        <f>K10/K12</f>
+        <v>0.22360679774997896</v>
+      </c>
+      <c r="L13" s="7">
+        <v>-1</v>
+      </c>
+      <c r="M13" s="23">
+        <f t="shared" si="3"/>
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="N13" s="20">
+        <f>N10/N12</f>
+        <v>0.11180339887498948</v>
+      </c>
+      <c r="O13" s="7">
+        <v>1</v>
+      </c>
+      <c r="P13" s="23">
+        <f t="shared" si="4"/>
+        <v>0.11180339887498948</v>
+      </c>
+      <c r="Q13" s="20">
+        <f>Q7/Q12</f>
+        <v>8.5342376311330105E-3</v>
+      </c>
+      <c r="R13" s="7">
+        <v>-27</v>
+      </c>
+      <c r="S13" s="23">
+        <f t="shared" si="5"/>
+        <v>-0.23042441604059127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B14" s="7">
+        <v>1</v>
+      </c>
+      <c r="C14" s="23">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="7">
+        <v>49</v>
+      </c>
+      <c r="G14" s="23">
+        <f t="shared" si="1"/>
+        <v>0.51593241104976018</v>
+      </c>
+      <c r="I14" s="7">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="23">
+        <f t="shared" si="2"/>
+        <v>-0.5</v>
+      </c>
+      <c r="L14" s="7">
+        <v>-1</v>
+      </c>
+      <c r="M14" s="23">
+        <f t="shared" si="3"/>
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="O14" s="7">
+        <v>1</v>
+      </c>
+      <c r="P14" s="23">
+        <f t="shared" si="4"/>
+        <v>0.11180339887498948</v>
+      </c>
+      <c r="R14" s="7">
+        <v>-22</v>
+      </c>
+      <c r="S14" s="23">
+        <f t="shared" si="5"/>
+        <v>-0.18775322788492624</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B15" s="7">
+        <v>-1</v>
+      </c>
+      <c r="C15" s="23">
+        <f t="shared" si="0"/>
+        <v>-0.5</v>
+      </c>
+      <c r="F15" s="7">
+        <v>-1</v>
+      </c>
+      <c r="G15" s="23">
+        <f t="shared" si="1"/>
+        <v>-1.0529232878566533E-2</v>
+      </c>
+      <c r="I15" s="7">
+        <v>1</v>
+      </c>
+      <c r="J15" s="23">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="L15" s="7">
+        <v>4</v>
+      </c>
+      <c r="M15" s="23">
+        <f t="shared" si="3"/>
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="O15" s="7">
+        <v>-4</v>
+      </c>
+      <c r="P15" s="23">
+        <f t="shared" si="4"/>
+        <v>-0.44721359549995793</v>
+      </c>
+      <c r="R15" s="7">
+        <v>103</v>
+      </c>
+      <c r="S15" s="23">
+        <f t="shared" si="5"/>
+        <v>0.87902647600670003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C19" s="24">
+        <f>C11</f>
+        <v>0.5</v>
+      </c>
+      <c r="D19" s="24">
+        <f>G11</f>
+        <v>0.30534775347842946</v>
+      </c>
+      <c r="E19" s="24">
+        <f>J11</f>
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="24">
+        <f>M11</f>
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="G19" s="24">
+        <f>P11</f>
+        <v>0.11180339887498948</v>
+      </c>
+      <c r="H19" s="24">
+        <f>S11</f>
+        <v>-0.10241085157359613</v>
+      </c>
+      <c r="J19" t="str">
+        <f>C19&amp;" &amp; "&amp;D19</f>
+        <v>0.5 &amp; 0.305347753478429</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C20" s="24">
+        <f t="shared" ref="C20:C23" si="6">C12</f>
+        <v>-0.5</v>
+      </c>
+      <c r="D20" s="24">
+        <f t="shared" ref="D20:D23" si="7">G12</f>
+        <v>-0.80022169877105653</v>
+      </c>
+      <c r="E20" s="24">
+        <f t="shared" ref="E20:E23" si="8">J12</f>
+        <v>-0.5</v>
+      </c>
+      <c r="F20" s="24">
+        <f t="shared" ref="F20:F23" si="9">M12</f>
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="G20" s="24">
+        <f t="shared" ref="G20:G23" si="10">P12</f>
+        <v>0.11180339887498948</v>
+      </c>
+      <c r="H20" s="24">
+        <f t="shared" ref="H20:H23" si="11">S12</f>
+        <v>-0.35843798050758646</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C21" s="24">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="D21" s="24">
+        <f t="shared" si="7"/>
+        <v>-1.0529232878566533E-2</v>
+      </c>
+      <c r="E21" s="24">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="24">
+        <f t="shared" si="9"/>
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="G21" s="24">
+        <f t="shared" si="10"/>
+        <v>0.11180339887498948</v>
+      </c>
+      <c r="H21" s="24">
+        <f t="shared" si="11"/>
+        <v>-0.23042441604059127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C22" s="24">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="24">
+        <f t="shared" si="7"/>
+        <v>0.51593241104976018</v>
+      </c>
+      <c r="E22" s="24">
+        <f t="shared" si="8"/>
+        <v>-0.5</v>
+      </c>
+      <c r="F22" s="24">
+        <f t="shared" si="9"/>
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="G22" s="24">
+        <f t="shared" si="10"/>
+        <v>0.11180339887498948</v>
+      </c>
+      <c r="H22" s="24">
+        <f t="shared" si="11"/>
+        <v>-0.18775322788492624</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C23" s="24">
+        <f t="shared" si="6"/>
+        <v>-0.5</v>
+      </c>
+      <c r="D23" s="24">
+        <f t="shared" si="7"/>
+        <v>-1.0529232878566533E-2</v>
+      </c>
+      <c r="E23" s="24">
+        <f t="shared" si="8"/>
+        <v>0.5</v>
+      </c>
+      <c r="F23" s="24">
+        <f t="shared" si="9"/>
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="G23" s="24">
+        <f t="shared" si="10"/>
+        <v>-0.44721359549995793</v>
+      </c>
+      <c r="H23" s="24">
+        <f t="shared" si="11"/>
+        <v>0.87902647600670003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="S24">
+        <f>1/5</f>
+        <v>0.2</v>
+      </c>
+      <c r="T24">
+        <f>0-S24</f>
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C25" s="22">
+        <f>SUM(C19:C24)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="22">
+        <f t="shared" ref="D25:H25" si="12">SUM(D19:D24)</f>
+        <v>1.9081958235744878E-17</v>
+      </c>
+      <c r="E25" s="22">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="22">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="22">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="22">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R26">
+        <f>4/5</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="26">
+        <v>4</v>
+      </c>
+      <c r="C27" s="25">
+        <f>ROUND(C19,$A$27)</f>
+        <v>0.5</v>
+      </c>
+      <c r="D27" s="25">
+        <f t="shared" ref="D27:H27" si="13">ROUND(D19,$A$27)</f>
+        <v>0.30530000000000002</v>
+      </c>
+      <c r="E27" s="25">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="F27" s="25">
+        <f t="shared" si="13"/>
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="G27" s="25">
+        <f t="shared" si="13"/>
+        <v>0.1118</v>
+      </c>
+      <c r="H27" s="25">
+        <f t="shared" si="13"/>
+        <v>-0.1024</v>
+      </c>
+      <c r="J27" t="str">
+        <f>C27&amp;" &amp; "&amp;D27&amp;" &amp; "&amp;E27&amp;" &amp; "&amp;F27&amp;" &amp; "&amp;G27&amp;" &amp; "&amp;H27</f>
+        <v>0.5 &amp; 0.3053 &amp; 0.5 &amp; -0.2236 &amp; 0.1118 &amp; -0.1024</v>
+      </c>
+      <c r="R27">
+        <f>R26/S24</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C28" s="25">
+        <f t="shared" ref="C28:H28" si="14">ROUND(C20,$A$27)</f>
+        <v>-0.5</v>
+      </c>
+      <c r="D28" s="25">
+        <f t="shared" si="14"/>
+        <v>-0.80020000000000002</v>
+      </c>
+      <c r="E28" s="25">
+        <f t="shared" si="14"/>
+        <v>-0.5</v>
+      </c>
+      <c r="F28" s="25">
+        <f t="shared" si="14"/>
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="G28" s="25">
+        <f t="shared" si="14"/>
+        <v>0.1118</v>
+      </c>
+      <c r="H28" s="25">
+        <f t="shared" si="14"/>
+        <v>-0.3584</v>
+      </c>
+      <c r="J28" t="str">
+        <f t="shared" ref="J28:J31" si="15">C28&amp;" &amp; "&amp;D28&amp;" &amp; "&amp;E28&amp;" &amp; "&amp;F28&amp;" &amp; "&amp;G28&amp;" &amp; "&amp;H28</f>
+        <v>-0.5 &amp; -0.8002 &amp; -0.5 &amp; -0.2236 &amp; 0.1118 &amp; -0.3584</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C29" s="25">
+        <f t="shared" ref="C29:H29" si="16">ROUND(C21,$A$27)</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="25">
+        <f t="shared" si="16"/>
+        <v>-1.0500000000000001E-2</v>
+      </c>
+      <c r="E29" s="25">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="25">
+        <f t="shared" si="16"/>
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="G29" s="25">
+        <f t="shared" si="16"/>
+        <v>0.1118</v>
+      </c>
+      <c r="H29" s="25">
+        <f t="shared" si="16"/>
+        <v>-0.23039999999999999</v>
+      </c>
+      <c r="J29" t="str">
+        <f t="shared" si="15"/>
+        <v>0 &amp; -0.0105 &amp; 0 &amp; -0.2236 &amp; 0.1118 &amp; -0.2304</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C30" s="25">
+        <f t="shared" ref="C30:H30" si="17">ROUND(C22,$A$27)</f>
+        <v>0.5</v>
+      </c>
+      <c r="D30" s="25">
+        <f t="shared" si="17"/>
+        <v>0.51590000000000003</v>
+      </c>
+      <c r="E30" s="25">
+        <f t="shared" si="17"/>
+        <v>-0.5</v>
+      </c>
+      <c r="F30" s="25">
+        <f t="shared" si="17"/>
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="G30" s="25">
+        <f t="shared" si="17"/>
+        <v>0.1118</v>
+      </c>
+      <c r="H30" s="25">
+        <f t="shared" si="17"/>
+        <v>-0.18779999999999999</v>
+      </c>
+      <c r="J30" t="str">
+        <f t="shared" si="15"/>
+        <v>0.5 &amp; 0.5159 &amp; -0.5 &amp; -0.2236 &amp; 0.1118 &amp; -0.1878</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C31" s="25">
+        <f t="shared" ref="C31:H31" si="18">ROUND(C23,$A$27)</f>
+        <v>-0.5</v>
+      </c>
+      <c r="D31" s="25">
+        <f t="shared" si="18"/>
+        <v>-1.0500000000000001E-2</v>
+      </c>
+      <c r="E31" s="25">
+        <f t="shared" si="18"/>
+        <v>0.5</v>
+      </c>
+      <c r="F31" s="25">
+        <f t="shared" si="18"/>
+        <v>0.89439999999999997</v>
+      </c>
+      <c r="G31" s="25">
+        <f t="shared" si="18"/>
+        <v>-0.44719999999999999</v>
+      </c>
+      <c r="H31" s="25">
+        <f t="shared" si="18"/>
+        <v>0.879</v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" si="15"/>
+        <v>-0.5 &amp; -0.0105 &amp; 0.5 &amp; 0.8944 &amp; -0.4472 &amp; 0.879</v>
+      </c>
+    </row>
+    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C33" s="27">
+        <f>SUM(C27:C32)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="27">
+        <f t="shared" ref="D33:H33" si="19">SUM(D27:D32)</f>
+        <v>6.4184768611141862E-17</v>
+      </c>
+      <c r="E33" s="27">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="27">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="27">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="27">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Edu/Linear_algebra/linal_session_task.xlsx
+++ b/Edu/Linear_algebra/linal_session_task.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LysogorA\DataScience\Edu\Linear_algebra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iTonyJah\DataScience\Edu\Linear_algebra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718BEFFB-9276-4255-8461-A2CDAF945A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294ACA38-C795-465D-B34E-BA26A64B76FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="1" r:id="rId1"/>
@@ -343,7 +343,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,8 +421,25 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -456,6 +473,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -522,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -567,6 +590,10 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3138,17 +3165,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:AD156"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="25" max="25" width="12.7109375" customWidth="1"/>
+    <col min="25" max="25" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3171,7 +3198,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -3194,7 +3221,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -3217,7 +3244,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -3240,7 +3267,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -3263,7 +3290,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -3286,32 +3313,32 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="23" x14ac:dyDescent="0.5">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -3319,7 +3346,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>3</v>
       </c>
@@ -3333,7 +3360,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
         <v>1</v>
       </c>
@@ -3347,7 +3374,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <v>2</v>
       </c>
@@ -3361,22 +3388,22 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -3384,12 +3411,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -3397,42 +3424,42 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="16" x14ac:dyDescent="0.4">
       <c r="A33" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
         <v>28</v>
       </c>
@@ -3443,7 +3470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <f>F38*J$38+G38*J$39+H38*J$40</f>
         <v>93900</v>
@@ -3465,7 +3492,7 @@
       </c>
       <c r="L38" s="8"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="7">
         <f t="shared" ref="A39:A40" si="0">F39*J$38+G39*J$39+H39*J$40</f>
         <v>52100</v>
@@ -3487,7 +3514,7 @@
       </c>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <f t="shared" si="0"/>
         <v>80200</v>
@@ -3509,23 +3536,23 @@
       </c>
       <c r="L40" s="8"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B41" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="J43" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="12">
         <f>F44*J$44+G44*J$45+H44*J$46</f>
         <v>494200</v>
@@ -3547,7 +3574,7 @@
       </c>
       <c r="L44" s="8"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="12">
         <f t="shared" ref="A45:A46" si="1">F45*J$44+G45*J$45+H45*J$46</f>
         <v>9960900</v>
@@ -3569,7 +3596,7 @@
       </c>
       <c r="L45" s="8"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="12">
         <f t="shared" si="1"/>
         <v>494200</v>
@@ -3591,22 +3618,22 @@
       </c>
       <c r="L46" s="8"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B47" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B50" s="6" t="s">
         <v>43</v>
       </c>
@@ -3614,7 +3641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -3646,7 +3673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="12">
         <f t="shared" ref="A52:A53" si="4">$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -3678,7 +3705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="12">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -3710,12 +3737,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>38</v>
       </c>
@@ -3726,7 +3753,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -3749,7 +3776,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="12">
         <f>$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -3772,7 +3799,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="12">
         <f>$F53*J$51+$G53*J$52+$H53*J$53</f>
         <v>14</v>
@@ -3795,19 +3822,19 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B59" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>51</v>
       </c>
       <c r="B60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G61" s="6" t="s">
         <v>43</v>
       </c>
@@ -3815,7 +3842,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="12">
         <f>F62*J$62+G62*J$63+H62*J$64</f>
         <v>494200</v>
@@ -3836,7 +3863,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="12">
         <f t="shared" ref="A63:A64" si="5">F63*J$62+G63*J$63+H63*J$64</f>
         <v>9960900</v>
@@ -3857,7 +3884,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="12">
         <f t="shared" si="5"/>
         <v>494200</v>
@@ -3878,23 +3905,23 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B65" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B67" s="8"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C68" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="12">
         <v>494200</v>
       </c>
@@ -3902,7 +3929,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
         <v>9960900</v>
       </c>
@@ -3910,7 +3937,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="12">
         <v>494200</v>
       </c>
@@ -3918,77 +3945,77 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="23" x14ac:dyDescent="0.35">
       <c r="A74" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>1</v>
       </c>
@@ -4011,7 +4038,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C90" s="16"/>
       <c r="D90" s="16"/>
       <c r="E90" s="16" t="s">
@@ -4023,7 +4050,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B91" s="7">
         <v>3</v>
       </c>
@@ -4046,7 +4073,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B92" s="7">
         <v>1</v>
       </c>
@@ -4069,7 +4096,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B93" s="7">
         <v>2</v>
       </c>
@@ -4092,7 +4119,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B94" s="7">
         <v>3</v>
       </c>
@@ -4115,7 +4142,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B95" s="7">
         <v>1</v>
       </c>
@@ -4138,17 +4165,17 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A97" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>76</v>
       </c>
@@ -4191,7 +4218,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>77</v>
       </c>
@@ -4228,7 +4255,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>78</v>
       </c>
@@ -4245,7 +4272,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B102" s="7">
         <f>B91-B$100</f>
         <v>1</v>
@@ -4289,7 +4316,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B103" s="7">
         <f t="shared" ref="B103:G103" si="10">B92-B$100</f>
         <v>-1</v>
@@ -4339,7 +4366,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B104" s="7">
         <f t="shared" ref="B104:G104" si="14">B93-B$100</f>
         <v>0</v>
@@ -4391,7 +4418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B105" s="7">
         <f t="shared" ref="B105:G105" si="16">B94-B$100</f>
         <v>1</v>
@@ -4443,7 +4470,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B106" s="7">
         <f t="shared" ref="B106:G106" si="19">B95-B$100</f>
         <v>-1</v>
@@ -4491,7 +4518,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>79</v>
       </c>
@@ -4537,7 +4564,7 @@
         <v>0.99972295331231709</v>
       </c>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>80</v>
       </c>
@@ -4566,7 +4593,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B109">
         <f>(B102^2+B103^2+B104^2+B105^2+B106^2)^(1/2)</f>
         <v>2</v>
@@ -4625,7 +4652,7 @@
         <v>18.994736112934024</v>
       </c>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>81</v>
       </c>
@@ -4638,7 +4665,7 @@
         <v>8.9554452708952432</v>
       </c>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B111" s="18">
         <f>B102/B$109</f>
         <v>0.5</v>
@@ -4666,7 +4693,7 @@
         <v>-0.10241085157359611</v>
       </c>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B112" s="18">
         <f t="shared" ref="B112:I115" si="23">B103/B$109</f>
         <v>-0.5</v>
@@ -4712,7 +4739,7 @@
         <v>1.7888543819998317</v>
       </c>
     </row>
-    <row r="113" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B113" s="18">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -4770,7 +4797,7 @@
         <v>0.89442719099991586</v>
       </c>
     </row>
-    <row r="114" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B114" s="18">
         <f t="shared" si="23"/>
         <v>0.5</v>
@@ -4833,7 +4860,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="115" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B115" s="18">
         <f t="shared" si="23"/>
         <v>-0.5</v>
@@ -4892,7 +4919,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="117" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:29" x14ac:dyDescent="0.35">
       <c r="Z117" t="s">
         <v>84</v>
       </c>
@@ -4905,7 +4932,7 @@
         <v>8.717797887081348</v>
       </c>
     </row>
-    <row r="118" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:29" x14ac:dyDescent="0.35">
       <c r="L118">
         <f>51/5</f>
         <v>10.199999999999999</v>
@@ -4955,12 +4982,12 @@
         <v>10.198039027185569</v>
       </c>
     </row>
-    <row r="120" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:29" x14ac:dyDescent="0.35">
       <c r="H120">
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:29" x14ac:dyDescent="0.35">
       <c r="H121">
         <v>5</v>
       </c>
@@ -4969,7 +4996,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="122" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:29" x14ac:dyDescent="0.35">
       <c r="H122">
         <v>10</v>
       </c>
@@ -4980,7 +5007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F123">
         <v>-240</v>
       </c>
@@ -5020,7 +5047,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="124" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F124">
         <v>-840</v>
       </c>
@@ -5060,7 +5087,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="125" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F125">
         <v>-540</v>
       </c>
@@ -5096,7 +5123,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="126" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F126">
         <v>-440</v>
       </c>
@@ -5136,7 +5163,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="127" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F127">
         <v>2060</v>
       </c>
@@ -5172,7 +5199,7 @@
         <v>10609</v>
       </c>
     </row>
-    <row r="128" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:29" x14ac:dyDescent="0.35">
       <c r="W128">
         <v>2</v>
       </c>
@@ -5181,7 +5208,7 @@
         <v>1.4142135623730951</v>
       </c>
     </row>
-    <row r="129" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="129" spans="5:24" x14ac:dyDescent="0.35">
       <c r="J129">
         <f>SUM(J123:J128)</f>
         <v>13730</v>
@@ -5202,7 +5229,7 @@
         <v>1.7320508075688772</v>
       </c>
     </row>
-    <row r="130" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="130" spans="5:24" x14ac:dyDescent="0.35">
       <c r="J130">
         <f>SQRT(J129)</f>
         <v>117.17508267545622</v>
@@ -5216,7 +5243,7 @@
         <v>117.17508267545622</v>
       </c>
     </row>
-    <row r="131" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="131" spans="5:24" x14ac:dyDescent="0.35">
       <c r="W131">
         <f>W128/W129</f>
         <v>0.66666666666666663</v>
@@ -5226,7 +5253,7 @@
         <v>0.81649658092772615</v>
       </c>
     </row>
-    <row r="132" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="132" spans="5:24" x14ac:dyDescent="0.35">
       <c r="F132">
         <f>G132*H132</f>
         <v>117</v>
@@ -5272,7 +5299,7 @@
         <v>0.81649658092772603</v>
       </c>
     </row>
-    <row r="133" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="133" spans="5:24" x14ac:dyDescent="0.35">
       <c r="I133">
         <f>I132*20</f>
         <v>2340</v>
@@ -5282,7 +5309,7 @@
         <v>-41</v>
       </c>
     </row>
-    <row r="135" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="135" spans="5:24" x14ac:dyDescent="0.35">
       <c r="H135">
         <f>I135/2</f>
         <v>59</v>
@@ -5307,13 +5334,13 @@
         <v>13.857142857142858</v>
       </c>
     </row>
-    <row r="136" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="136" spans="5:24" x14ac:dyDescent="0.35">
       <c r="I136">
         <f>I135*20</f>
         <v>2360</v>
       </c>
     </row>
-    <row r="139" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="139" spans="5:24" x14ac:dyDescent="0.35">
       <c r="E139">
         <v>19</v>
       </c>
@@ -5332,7 +5359,7 @@
         <v>94.973680564670133</v>
       </c>
     </row>
-    <row r="140" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="140" spans="5:24" x14ac:dyDescent="0.35">
       <c r="F140">
         <v>1805</v>
       </c>
@@ -5344,13 +5371,13 @@
         <v>24010</v>
       </c>
     </row>
-    <row r="141" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="141" spans="5:24" x14ac:dyDescent="0.35">
       <c r="J141">
         <f>J139/J140</f>
         <v>360.8</v>
       </c>
     </row>
-    <row r="142" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="142" spans="5:24" x14ac:dyDescent="0.35">
       <c r="M142">
         <v>7</v>
       </c>
@@ -5363,12 +5390,12 @@
         <v>2401</v>
       </c>
     </row>
-    <row r="148" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:7" x14ac:dyDescent="0.35">
       <c r="D148">
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:7" x14ac:dyDescent="0.35">
       <c r="D149">
         <v>5</v>
       </c>
@@ -5377,7 +5404,7 @@
         <v>2.2360679774997898</v>
       </c>
     </row>
-    <row r="150" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:7" x14ac:dyDescent="0.35">
       <c r="D150">
         <f>D148/D149</f>
         <v>0.4</v>
@@ -5387,23 +5414,23 @@
         <v>0.89442719099991597</v>
       </c>
     </row>
-    <row r="151" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C151">
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C152">
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C153">
         <f>C151/C152</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="154" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C154">
         <f>SQRT(C153)</f>
         <v>0.89442719099991586</v>
@@ -5412,7 +5439,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="155" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:7" x14ac:dyDescent="0.35">
       <c r="E155">
         <f>SQRT(E154)</f>
         <v>4.4721359549995796</v>
@@ -5421,7 +5448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:7" x14ac:dyDescent="0.35">
       <c r="G156">
         <f>G155/E155</f>
         <v>0.22360679774997896</v>
@@ -5437,9 +5464,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{666D1E91-ED7C-475C-A636-9777A928839D}">
   <dimension ref="A3:O72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -5466,7 +5493,7 @@
         <v>1.4310835055998654</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -5493,7 +5520,7 @@
         <v>1.4310835055998654</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B13">
         <f t="shared" ref="B13" si="4">B14-1</f>
         <v>1</v>
@@ -5507,7 +5534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14">
         <f t="shared" ref="B14:B15" si="7">B15-1</f>
         <v>2</v>
@@ -5521,7 +5548,7 @@
         <v>0.70710678118654757</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15">
         <f t="shared" si="7"/>
         <v>3</v>
@@ -5535,7 +5562,7 @@
         <v>0.57735026918962573</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16">
         <f>B17-1</f>
         <v>4</v>
@@ -5549,7 +5576,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>5</v>
       </c>
@@ -5562,7 +5589,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18">
         <f>B17+1</f>
         <v>6</v>
@@ -5576,7 +5603,7 @@
         <v>0.40824829046386296</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19">
         <f t="shared" ref="B19:B27" si="11">B18+1</f>
         <v>7</v>
@@ -5590,7 +5617,7 @@
         <v>0.37796447300922725</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20">
         <f t="shared" si="11"/>
         <v>8</v>
@@ -5604,7 +5631,7 @@
         <v>0.35355339059327379</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21">
         <f t="shared" si="11"/>
         <v>9</v>
@@ -5618,7 +5645,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22">
         <f t="shared" si="11"/>
         <v>10</v>
@@ -5632,7 +5659,7 @@
         <v>0.31622776601683794</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23">
         <f t="shared" si="11"/>
         <v>11</v>
@@ -5646,7 +5673,7 @@
         <v>0.30151134457776363</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24">
         <f t="shared" si="11"/>
         <v>12</v>
@@ -5660,7 +5687,7 @@
         <v>0.28867513459481287</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25">
         <f t="shared" si="11"/>
         <v>13</v>
@@ -5674,7 +5701,7 @@
         <v>0.27735009811261457</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26">
         <f t="shared" si="11"/>
         <v>14</v>
@@ -5688,7 +5715,7 @@
         <v>0.2672612419124244</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27">
         <f t="shared" si="11"/>
         <v>15</v>
@@ -5702,7 +5729,7 @@
         <v>0.25819888974716115</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28">
         <f t="shared" ref="B28:B58" si="12">B27+1</f>
         <v>16</v>
@@ -5716,7 +5743,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29">
         <f t="shared" si="12"/>
         <v>17</v>
@@ -5730,7 +5757,7 @@
         <v>0.24253562503633297</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30">
         <f t="shared" si="12"/>
         <v>18</v>
@@ -5744,7 +5771,7 @@
         <v>0.23570226039551581</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31">
         <f t="shared" si="12"/>
         <v>19</v>
@@ -5758,7 +5785,7 @@
         <v>0.2294157338705618</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32">
         <f t="shared" si="12"/>
         <v>20</v>
@@ -5772,7 +5799,7 @@
         <v>0.22360679774997899</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33">
         <f t="shared" si="12"/>
         <v>21</v>
@@ -5786,7 +5813,7 @@
         <v>0.21821789023599236</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34">
         <f t="shared" si="12"/>
         <v>22</v>
@@ -5800,7 +5827,7 @@
         <v>0.21320071635561044</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35">
         <f t="shared" si="12"/>
         <v>23</v>
@@ -5814,7 +5841,7 @@
         <v>0.20851441405707474</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B36">
         <f t="shared" si="12"/>
         <v>24</v>
@@ -5835,7 +5862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B37">
         <f t="shared" si="12"/>
         <v>25</v>
@@ -5864,7 +5891,7 @@
         <v>1.1180339887498949</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B38">
         <f t="shared" si="12"/>
         <v>26</v>
@@ -5886,7 +5913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B39">
         <f t="shared" si="12"/>
         <v>27</v>
@@ -5919,7 +5946,7 @@
         <v>1.1180339887498949</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B40">
         <f t="shared" si="12"/>
         <v>28</v>
@@ -5936,7 +5963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B41">
         <f t="shared" si="12"/>
         <v>29</v>
@@ -5975,7 +6002,7 @@
         <v>0.22360679774997899</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B42">
         <f t="shared" si="12"/>
         <v>30</v>
@@ -5997,7 +6024,7 @@
         <v>0.1118033988749895</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43">
         <f t="shared" si="12"/>
         <v>31</v>
@@ -6011,7 +6038,7 @@
         <v>0.17960530202677488</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B44">
         <f t="shared" si="12"/>
         <v>32</v>
@@ -6034,7 +6061,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B45">
         <f t="shared" si="12"/>
         <v>33</v>
@@ -6081,7 +6108,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B46">
         <f t="shared" si="12"/>
         <v>34</v>
@@ -6095,7 +6122,7 @@
         <v>0.17149858514250885</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B47">
         <f t="shared" si="12"/>
         <v>35</v>
@@ -6112,7 +6139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B48">
         <f t="shared" si="12"/>
         <v>36</v>
@@ -6133,7 +6160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B49">
         <f t="shared" si="12"/>
         <v>37</v>
@@ -6153,7 +6180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B50">
         <f t="shared" si="12"/>
         <v>38</v>
@@ -6171,7 +6198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B51">
         <f t="shared" si="12"/>
         <v>39</v>
@@ -6189,7 +6216,7 @@
         <v>1.1180339887498949</v>
       </c>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B52">
         <f t="shared" si="12"/>
         <v>40</v>
@@ -6206,7 +6233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B53">
         <f t="shared" si="12"/>
         <v>41</v>
@@ -6231,7 +6258,7 @@
         <v>0.1118033988749895</v>
       </c>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B54">
         <f t="shared" si="12"/>
         <v>42</v>
@@ -6248,7 +6275,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B55">
         <f t="shared" si="12"/>
         <v>43</v>
@@ -6266,7 +6293,7 @@
         <v>22.360679774997898</v>
       </c>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B56">
         <f t="shared" si="12"/>
         <v>44</v>
@@ -6283,7 +6310,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B57">
         <f t="shared" si="12"/>
         <v>45</v>
@@ -6301,7 +6328,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B58">
         <f t="shared" si="12"/>
         <v>46</v>
@@ -6315,28 +6342,28 @@
         <v>0.14744195615489714</v>
       </c>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
       <c r="F60">
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
       <c r="F61">
         <f>SQRT(F60)</f>
         <v>2.8284271247461903</v>
       </c>
     </row>
-    <row r="66" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:10" x14ac:dyDescent="0.35">
       <c r="G66">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:10" x14ac:dyDescent="0.35">
       <c r="G67">
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F68">
         <v>2</v>
       </c>
@@ -6351,7 +6378,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:10" x14ac:dyDescent="0.35">
       <c r="H69">
         <f>H68/G68</f>
         <v>0.55901699437494745</v>
@@ -6365,12 +6392,12 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="71" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F71">
         <v>80</v>
       </c>
     </row>
-    <row r="72" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F72">
         <f>SQRT(F71)</f>
         <v>8.9442719099991592</v>
@@ -6390,26 +6417,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82BA3844-AF00-4659-9CA6-FDAA4D3C4028}">
-  <dimension ref="A2:T33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:T66"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K2">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K4">
         <f>K2/K3</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="J5">
         <v>2</v>
       </c>
@@ -6418,7 +6445,7 @@
         <v>0.89442719099991586</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="J6">
         <v>1</v>
       </c>
@@ -6427,7 +6454,7 @@
         <v>1.7888543819998317</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="E7">
         <v>1</v>
       </c>
@@ -6443,7 +6470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="E8">
         <v>1804</v>
       </c>
@@ -6455,7 +6482,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B9" t="str">
         <f>C17</f>
         <v>x_1</v>
@@ -6487,7 +6514,7 @@
         <v>y</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="E10">
         <f>SQRT(E8/E9)</f>
         <v>0.99972295331231709</v>
@@ -6502,7 +6529,7 @@
         <v>13689</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1</v>
       </c>
@@ -6565,7 +6592,7 @@
         <v>-0.10241085157359613</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2</v>
       </c>
@@ -6631,7 +6658,7 @@
         <v>-0.35843798050758646</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="20">
         <f>A11/A12</f>
         <v>0.5</v>
@@ -6699,7 +6726,7 @@
         <v>-0.23042441604059127</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B14" s="7">
         <v>1</v>
       </c>
@@ -6743,7 +6770,7 @@
         <v>-0.18775322788492624</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B15" s="7">
         <v>-1</v>
       </c>
@@ -6787,7 +6814,7 @@
         <v>0.87902647600670003</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
         <v>92</v>
       </c>
@@ -6807,7 +6834,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C19" s="24">
         <f>C11</f>
         <v>0.5</v>
@@ -6832,12 +6859,8 @@
         <f>S11</f>
         <v>-0.10241085157359613</v>
       </c>
-      <c r="J19" t="str">
-        <f>C19&amp;" &amp; "&amp;D19</f>
-        <v>0.5 &amp; 0.305347753478429</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C20" s="24">
         <f t="shared" ref="C20:C23" si="6">C12</f>
         <v>-0.5</v>
@@ -6863,7 +6886,7 @@
         <v>-0.35843798050758646</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C21" s="24">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -6889,7 +6912,7 @@
         <v>-0.23042441604059127</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C22" s="24">
         <f t="shared" si="6"/>
         <v>0.5</v>
@@ -6915,7 +6938,7 @@
         <v>-0.18775322788492624</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C23" s="24">
         <f t="shared" si="6"/>
         <v>-0.5</v>
@@ -6941,7 +6964,7 @@
         <v>0.87902647600670003</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C24" s="22"/>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -6957,7 +6980,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C25" s="22">
         <f>SUM(C19:C24)</f>
         <v>0</v>
@@ -6983,170 +7006,170 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="R26">
         <f>4/5</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" s="26">
         <v>4</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="28">
         <f>ROUND(C19,$A$27)</f>
         <v>0.5</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="28">
         <f t="shared" ref="D27:H27" si="13">ROUND(D19,$A$27)</f>
         <v>0.30530000000000002</v>
       </c>
-      <c r="E27" s="25">
+      <c r="E27" s="28">
         <f t="shared" si="13"/>
         <v>0.5</v>
       </c>
-      <c r="F27" s="25">
+      <c r="F27" s="28">
         <f t="shared" si="13"/>
         <v>-0.22359999999999999</v>
       </c>
-      <c r="G27" s="25">
+      <c r="G27" s="28">
         <f t="shared" si="13"/>
         <v>0.1118</v>
       </c>
-      <c r="H27" s="25">
+      <c r="H27" s="29">
         <f t="shared" si="13"/>
         <v>-0.1024</v>
       </c>
       <c r="J27" t="str">
-        <f>C27&amp;" &amp; "&amp;D27&amp;" &amp; "&amp;E27&amp;" &amp; "&amp;F27&amp;" &amp; "&amp;G27&amp;" &amp; "&amp;H27</f>
-        <v>0.5 &amp; 0.3053 &amp; 0.5 &amp; -0.2236 &amp; 0.1118 &amp; -0.1024</v>
+        <f>C27&amp;" &amp; "&amp;D27&amp;" &amp; "&amp;E27&amp;" &amp; "&amp;F27&amp;" &amp; "&amp;G27&amp;" &amp; "&amp;H27&amp;" \\"</f>
+        <v>0,5 &amp; 0,3053 &amp; 0,5 &amp; -0,2236 &amp; 0,1118 &amp; -0,1024 \\</v>
       </c>
       <c r="R27">
         <f>R26/S24</f>
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C28" s="25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C28" s="28">
         <f t="shared" ref="C28:H28" si="14">ROUND(C20,$A$27)</f>
         <v>-0.5</v>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="28">
         <f t="shared" si="14"/>
         <v>-0.80020000000000002</v>
       </c>
-      <c r="E28" s="25">
+      <c r="E28" s="28">
         <f t="shared" si="14"/>
         <v>-0.5</v>
       </c>
-      <c r="F28" s="25">
+      <c r="F28" s="28">
         <f t="shared" si="14"/>
         <v>-0.22359999999999999</v>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="28">
         <f t="shared" si="14"/>
         <v>0.1118</v>
       </c>
-      <c r="H28" s="25">
+      <c r="H28" s="29">
         <f t="shared" si="14"/>
         <v>-0.3584</v>
       </c>
       <c r="J28" t="str">
-        <f t="shared" ref="J28:J31" si="15">C28&amp;" &amp; "&amp;D28&amp;" &amp; "&amp;E28&amp;" &amp; "&amp;F28&amp;" &amp; "&amp;G28&amp;" &amp; "&amp;H28</f>
-        <v>-0.5 &amp; -0.8002 &amp; -0.5 &amp; -0.2236 &amp; 0.1118 &amp; -0.3584</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C29" s="25">
+        <f t="shared" ref="J28:J31" si="15">C28&amp;" &amp; "&amp;D28&amp;" &amp; "&amp;E28&amp;" &amp; "&amp;F28&amp;" &amp; "&amp;G28&amp;" &amp; "&amp;H28&amp;" \\"</f>
+        <v>-0,5 &amp; -0,8002 &amp; -0,5 &amp; -0,2236 &amp; 0,1118 &amp; -0,3584 \\</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C29" s="28">
         <f t="shared" ref="C29:H29" si="16">ROUND(C21,$A$27)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="28">
         <f t="shared" si="16"/>
         <v>-1.0500000000000001E-2</v>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="28">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F29" s="25">
+      <c r="F29" s="28">
         <f t="shared" si="16"/>
         <v>-0.22359999999999999</v>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="28">
         <f t="shared" si="16"/>
         <v>0.1118</v>
       </c>
-      <c r="H29" s="25">
+      <c r="H29" s="29">
         <f t="shared" si="16"/>
         <v>-0.23039999999999999</v>
       </c>
       <c r="J29" t="str">
         <f t="shared" si="15"/>
-        <v>0 &amp; -0.0105 &amp; 0 &amp; -0.2236 &amp; 0.1118 &amp; -0.2304</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C30" s="25">
+        <v>0 &amp; -0,0105 &amp; 0 &amp; -0,2236 &amp; 0,1118 &amp; -0,2304 \\</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C30" s="28">
         <f t="shared" ref="C30:H30" si="17">ROUND(C22,$A$27)</f>
         <v>0.5</v>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="28">
         <f t="shared" si="17"/>
         <v>0.51590000000000003</v>
       </c>
-      <c r="E30" s="25">
+      <c r="E30" s="28">
         <f t="shared" si="17"/>
         <v>-0.5</v>
       </c>
-      <c r="F30" s="25">
+      <c r="F30" s="28">
         <f t="shared" si="17"/>
         <v>-0.22359999999999999</v>
       </c>
-      <c r="G30" s="25">
+      <c r="G30" s="28">
         <f t="shared" si="17"/>
         <v>0.1118</v>
       </c>
-      <c r="H30" s="25">
+      <c r="H30" s="29">
         <f t="shared" si="17"/>
         <v>-0.18779999999999999</v>
       </c>
       <c r="J30" t="str">
         <f t="shared" si="15"/>
-        <v>0.5 &amp; 0.5159 &amp; -0.5 &amp; -0.2236 &amp; 0.1118 &amp; -0.1878</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C31" s="25">
+        <v>0,5 &amp; 0,5159 &amp; -0,5 &amp; -0,2236 &amp; 0,1118 &amp; -0,1878 \\</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C31" s="28">
         <f t="shared" ref="C31:H31" si="18">ROUND(C23,$A$27)</f>
         <v>-0.5</v>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="28">
         <f t="shared" si="18"/>
         <v>-1.0500000000000001E-2</v>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="28">
         <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
-      <c r="F31" s="25">
+      <c r="F31" s="28">
         <f t="shared" si="18"/>
         <v>0.89439999999999997</v>
       </c>
-      <c r="G31" s="25">
+      <c r="G31" s="28">
         <f t="shared" si="18"/>
         <v>-0.44719999999999999</v>
       </c>
-      <c r="H31" s="25">
+      <c r="H31" s="29">
         <f t="shared" si="18"/>
         <v>0.879</v>
       </c>
       <c r="J31" t="str">
         <f t="shared" si="15"/>
-        <v>-0.5 &amp; -0.0105 &amp; 0.5 &amp; 0.8944 &amp; -0.4472 &amp; 0.879</v>
-      </c>
-    </row>
-    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
+        <v>-0,5 &amp; -0,0105 &amp; 0,5 &amp; 0,8944 &amp; -0,4472 &amp; 0,879 \\</v>
+      </c>
+    </row>
+    <row r="33" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C33" s="27">
         <f>SUM(C27:C32)</f>
         <v>0</v>
@@ -7171,7 +7194,609 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-    </row>
+      <c r="Q33">
+        <v>1</v>
+      </c>
+      <c r="R33">
+        <f>Q33^2</f>
+        <v>1</v>
+      </c>
+      <c r="S33">
+        <f>Q33/$R$41</f>
+        <v>0.1889822365046136</v>
+      </c>
+      <c r="T33">
+        <f>S33^2</f>
+        <v>3.5714285714285705E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="Q34">
+        <v>2</v>
+      </c>
+      <c r="R34">
+        <f t="shared" ref="R34:R38" si="20">Q34^2</f>
+        <v>4</v>
+      </c>
+      <c r="S34">
+        <f>Q34/$R$41</f>
+        <v>0.3779644730092272</v>
+      </c>
+      <c r="T34">
+        <f t="shared" ref="T34:T38" si="21">S34^2</f>
+        <v>0.14285714285714282</v>
+      </c>
+    </row>
+    <row r="35" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C35" s="25"/>
+      <c r="I35" s="30">
+        <v>-0.1024</v>
+      </c>
+      <c r="J35" s="30">
+        <v>-0.3584</v>
+      </c>
+      <c r="K35" s="30">
+        <v>-0.23039999999999999</v>
+      </c>
+      <c r="L35" s="30">
+        <v>-0.18779999999999999</v>
+      </c>
+      <c r="M35" s="30">
+        <v>0.879</v>
+      </c>
+      <c r="Q35">
+        <v>3</v>
+      </c>
+      <c r="R35">
+        <f t="shared" si="20"/>
+        <v>9</v>
+      </c>
+      <c r="S35">
+        <f>Q35/$R$41</f>
+        <v>0.56694670951384085</v>
+      </c>
+      <c r="T35">
+        <f t="shared" si="21"/>
+        <v>0.32142857142857145</v>
+      </c>
+    </row>
+    <row r="36" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C36" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="D36" s="30">
+        <v>0.30530000000000002</v>
+      </c>
+      <c r="E36" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="F36" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="G36" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="H36" s="30">
+        <v>-0.1024</v>
+      </c>
+      <c r="I36">
+        <f>$C36*I$35</f>
+        <v>-5.1200000000000002E-2</v>
+      </c>
+      <c r="Q36">
+        <v>-1</v>
+      </c>
+      <c r="R36">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="S36">
+        <f>Q36/$R$41</f>
+        <v>-0.1889822365046136</v>
+      </c>
+      <c r="T36">
+        <f t="shared" si="21"/>
+        <v>3.5714285714285705E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C37" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="D37" s="30">
+        <v>-0.80020000000000002</v>
+      </c>
+      <c r="E37" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="F37" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="G37" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="H37" s="30">
+        <v>-0.3584</v>
+      </c>
+      <c r="J37">
+        <f>$C37*J$35</f>
+        <v>0.1792</v>
+      </c>
+      <c r="Q37">
+        <v>-2</v>
+      </c>
+      <c r="R37">
+        <f t="shared" si="20"/>
+        <v>4</v>
+      </c>
+      <c r="S37">
+        <f>Q37/$R$41</f>
+        <v>-0.3779644730092272</v>
+      </c>
+      <c r="T37">
+        <f t="shared" si="21"/>
+        <v>0.14285714285714282</v>
+      </c>
+    </row>
+    <row r="38" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C38" s="30">
+        <v>0</v>
+      </c>
+      <c r="D38" s="30">
+        <v>-1.0500000000000001E-2</v>
+      </c>
+      <c r="E38" s="30">
+        <v>0</v>
+      </c>
+      <c r="F38" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="G38" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="H38" s="30">
+        <v>-0.23039999999999999</v>
+      </c>
+      <c r="K38">
+        <f>$C38*K$35</f>
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>-3</v>
+      </c>
+      <c r="R38">
+        <f t="shared" si="20"/>
+        <v>9</v>
+      </c>
+      <c r="S38">
+        <f>Q38/$R$41</f>
+        <v>-0.56694670951384085</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="21"/>
+        <v>0.32142857142857145</v>
+      </c>
+    </row>
+    <row r="39" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C39" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="D39" s="30">
+        <v>0.51590000000000003</v>
+      </c>
+      <c r="E39" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="F39" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="G39" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="H39" s="30">
+        <v>-0.18779999999999999</v>
+      </c>
+      <c r="L39">
+        <f>$C39*L$35</f>
+        <v>-9.3899999999999997E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C40" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="D40" s="30">
+        <v>-1.0500000000000001E-2</v>
+      </c>
+      <c r="E40" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="F40" s="30">
+        <v>0.89439999999999997</v>
+      </c>
+      <c r="G40" s="30">
+        <v>-0.44719999999999999</v>
+      </c>
+      <c r="H40" s="30">
+        <v>0.879</v>
+      </c>
+      <c r="M40">
+        <f>$C40*M$35</f>
+        <v>-0.4395</v>
+      </c>
+      <c r="Q40">
+        <f>SUM(Q33:Q39)</f>
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <f>SUM(R33:R39)</f>
+        <v>28</v>
+      </c>
+      <c r="T40">
+        <f>SUM(T33:T39)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="R41">
+        <f>SQRT(R40)</f>
+        <v>5.2915026221291814</v>
+      </c>
+    </row>
+    <row r="43" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C43" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="D43" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="E43" s="30">
+        <v>0</v>
+      </c>
+      <c r="F43" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="G43" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="I43" t="str">
+        <f>C43&amp;" \\ "&amp;D43&amp;" \\ "&amp;E43&amp;" \\ "&amp;F43&amp;" \\ "&amp;G43</f>
+        <v>0,5 \\ -0,5 \\ 0 \\ 0,5 \\ -0,5</v>
+      </c>
+    </row>
+    <row r="44" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C44" s="30">
+        <v>0.30530000000000002</v>
+      </c>
+      <c r="D44" s="30">
+        <v>-0.80020000000000002</v>
+      </c>
+      <c r="E44" s="30">
+        <v>-1.0500000000000001E-2</v>
+      </c>
+      <c r="F44" s="30">
+        <v>0.51590000000000003</v>
+      </c>
+      <c r="G44" s="30">
+        <v>-1.0500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C45" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="D45" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="E45" s="30">
+        <v>0</v>
+      </c>
+      <c r="F45" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="G45" s="30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C46" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="D46" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="E46" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="F46" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="G46" s="30">
+        <v>0.89439999999999997</v>
+      </c>
+    </row>
+    <row r="47" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C47" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="D47" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="E47" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="F47" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="G47" s="30">
+        <v>-0.44719999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C48" s="30">
+        <v>-0.1024</v>
+      </c>
+      <c r="D48" s="30">
+        <v>-0.3584</v>
+      </c>
+      <c r="E48" s="30">
+        <v>-0.23039999999999999</v>
+      </c>
+      <c r="F48" s="30">
+        <v>-0.18779999999999999</v>
+      </c>
+      <c r="G48" s="30">
+        <v>0.879</v>
+      </c>
+      <c r="I48" t="str">
+        <f>C48&amp;" &amp; "&amp;D48&amp;" &amp; "&amp;E48&amp;" &amp; "&amp;F48&amp;" &amp; "&amp;G48</f>
+        <v>-0,1024 &amp; -0,3584 &amp; -0,2304 &amp; -0,1878 &amp; 0,879</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C51" s="25"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C52" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="D52" s="30">
+        <v>0.30530000000000002</v>
+      </c>
+      <c r="E52" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="F52" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="G52" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="H52" s="31">
+        <v>-0.1024</v>
+      </c>
+      <c r="J52" t="str">
+        <f>D52&amp;" &amp; "&amp;H52&amp;" \\"</f>
+        <v>0,3053 &amp; -0,1024 \\</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C53" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="D53" s="30">
+        <v>-0.80020000000000002</v>
+      </c>
+      <c r="E53" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="F53" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="G53" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="H53" s="31">
+        <v>-0.3584</v>
+      </c>
+      <c r="J53" t="str">
+        <f t="shared" ref="J53:J56" si="22">D53&amp;" &amp; "&amp;H53&amp;" \\"</f>
+        <v>-0,8002 &amp; -0,3584 \\</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C54" s="30">
+        <v>0</v>
+      </c>
+      <c r="D54" s="30">
+        <v>-1.0500000000000001E-2</v>
+      </c>
+      <c r="E54" s="30">
+        <v>0</v>
+      </c>
+      <c r="F54" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="G54" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="H54" s="31">
+        <v>-0.23039999999999999</v>
+      </c>
+      <c r="J54" t="str">
+        <f t="shared" si="22"/>
+        <v>-0,0105 &amp; -0,2304 \\</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C55" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="D55" s="30">
+        <v>0.51590000000000003</v>
+      </c>
+      <c r="E55" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="F55" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="G55" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="H55" s="31">
+        <v>-0.18779999999999999</v>
+      </c>
+      <c r="J55" t="str">
+        <f t="shared" si="22"/>
+        <v>0,5159 &amp; -0,1878 \\</v>
+      </c>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C56" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="D56" s="30">
+        <v>-1.0500000000000001E-2</v>
+      </c>
+      <c r="E56" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="F56" s="30">
+        <v>0.89439999999999997</v>
+      </c>
+      <c r="G56" s="30">
+        <v>-0.44719999999999999</v>
+      </c>
+      <c r="H56" s="31">
+        <v>0.879</v>
+      </c>
+      <c r="J56" t="str">
+        <f t="shared" si="22"/>
+        <v>-0,0105 &amp; 0,879 \\</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C59" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="D59" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="E59" s="30">
+        <v>0</v>
+      </c>
+      <c r="F59" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="G59" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="I59" t="str">
+        <f>C59&amp;" \\ "&amp;D59&amp;" \\ "&amp;E59&amp;" \\ "&amp;F59&amp;" \\ "&amp;G59</f>
+        <v>0,5 \\ -0,5 \\ 0 \\ 0,5 \\ -0,5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C60" s="30">
+        <v>0.30530000000000002</v>
+      </c>
+      <c r="D60" s="30">
+        <v>-0.80020000000000002</v>
+      </c>
+      <c r="E60" s="30">
+        <v>-1.0500000000000001E-2</v>
+      </c>
+      <c r="F60" s="30">
+        <v>0.51590000000000003</v>
+      </c>
+      <c r="G60" s="30">
+        <v>-1.0500000000000001E-2</v>
+      </c>
+      <c r="I60" t="str">
+        <f>C60&amp;" &amp; "&amp;D60&amp;" &amp; "&amp;E60&amp;" &amp; "&amp;F60&amp;" &amp; "&amp;G60</f>
+        <v>0,3053 &amp; -0,8002 &amp; -0,0105 &amp; 0,5159 &amp; -0,0105</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C61" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="D61" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="E61" s="30">
+        <v>0</v>
+      </c>
+      <c r="F61" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="G61" s="30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C62" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="D62" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="E62" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="F62" s="30">
+        <v>-0.22359999999999999</v>
+      </c>
+      <c r="G62" s="30">
+        <v>0.89439999999999997</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C63" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="D63" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="E63" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="F63" s="30">
+        <v>0.1118</v>
+      </c>
+      <c r="G63" s="30">
+        <v>-0.44719999999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C64" s="30">
+        <v>-0.1024</v>
+      </c>
+      <c r="D64" s="30">
+        <v>-0.3584</v>
+      </c>
+      <c r="E64" s="30">
+        <v>-0.23039999999999999</v>
+      </c>
+      <c r="F64" s="30">
+        <v>-0.18779999999999999</v>
+      </c>
+      <c r="G64" s="30">
+        <v>0.879</v>
+      </c>
+      <c r="I64" t="str">
+        <f>C64&amp;" &amp; "&amp;D64&amp;" &amp; "&amp;E64&amp;" &amp; "&amp;F64&amp;" &amp; "&amp;G64</f>
+        <v>-0,1024 &amp; -0,3584 &amp; -0,2304 &amp; -0,1878 &amp; 0,879</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="66" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Edu/Linear_algebra/linal_session_task.xlsx
+++ b/Edu/Linear_algebra/linal_session_task.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iTonyJah\DataScience\Edu\Linear_algebra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LysogorA\DataScience\Edu\Linear_algebra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294ACA38-C795-465D-B34E-BA26A64B76FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D03A45-8DE2-4F8B-AB00-D5DDE8DC62E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="1" r:id="rId1"/>
@@ -3165,17 +3165,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:AD156"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="25" max="25" width="12.7265625" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -3313,32 +3313,32 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="23" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>3</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>1</v>
       </c>
@@ -3374,7 +3374,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>2</v>
       </c>
@@ -3388,22 +3388,22 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -3411,12 +3411,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -3424,42 +3424,42 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>28</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <f>F38*J$38+G38*J$39+H38*J$40</f>
         <v>93900</v>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L38" s="8"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <f t="shared" ref="A39:A40" si="0">F39*J$38+G39*J$39+H39*J$40</f>
         <v>52100</v>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <f t="shared" si="0"/>
         <v>80200</v>
@@ -3536,23 +3536,23 @@
       </c>
       <c r="L40" s="8"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B41" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="J43" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
         <f>F44*J$44+G44*J$45+H44*J$46</f>
         <v>494200</v>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L44" s="8"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
         <f t="shared" ref="A45:A46" si="1">F45*J$44+G45*J$45+H45*J$46</f>
         <v>9960900</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="L45" s="8"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
         <f t="shared" si="1"/>
         <v>494200</v>
@@ -3618,22 +3618,22 @@
       </c>
       <c r="L46" s="8"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B47" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B50" s="6" t="s">
         <v>43</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -3673,7 +3673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="12">
         <f t="shared" ref="A52:A53" si="4">$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -3705,7 +3705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="12">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -3737,12 +3737,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>38</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -3776,7 +3776,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
         <f>$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -3799,7 +3799,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="12">
         <f>$F53*J$51+$G53*J$52+$H53*J$53</f>
         <v>14</v>
@@ -3822,19 +3822,19 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B59" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>51</v>
       </c>
       <c r="B60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G61" s="6" t="s">
         <v>43</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="12">
         <f>F62*J$62+G62*J$63+H62*J$64</f>
         <v>494200</v>
@@ -3863,7 +3863,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="12">
         <f t="shared" ref="A63:A64" si="5">F63*J$62+G63*J$63+H63*J$64</f>
         <v>9960900</v>
@@ -3884,7 +3884,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="12">
         <f t="shared" si="5"/>
         <v>494200</v>
@@ -3905,23 +3905,23 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B65" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B67" s="8"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C68" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="12">
         <v>494200</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="12">
         <v>9960900</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="12">
         <v>494200</v>
       </c>
@@ -3945,77 +3945,77 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="23" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>1</v>
       </c>
@@ -4038,7 +4038,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C90" s="16"/>
       <c r="D90" s="16"/>
       <c r="E90" s="16" t="s">
@@ -4050,7 +4050,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B91" s="7">
         <v>3</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B92" s="7">
         <v>1</v>
       </c>
@@ -4096,7 +4096,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B93" s="7">
         <v>2</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B94" s="7">
         <v>3</v>
       </c>
@@ -4142,7 +4142,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B95" s="7">
         <v>1</v>
       </c>
@@ -4165,17 +4165,17 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>76</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>77</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>78</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B102" s="7">
         <f>B91-B$100</f>
         <v>1</v>
@@ -4316,7 +4316,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B103" s="7">
         <f t="shared" ref="B103:G103" si="10">B92-B$100</f>
         <v>-1</v>
@@ -4366,7 +4366,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B104" s="7">
         <f t="shared" ref="B104:G104" si="14">B93-B$100</f>
         <v>0</v>
@@ -4418,7 +4418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B105" s="7">
         <f t="shared" ref="B105:G105" si="16">B94-B$100</f>
         <v>1</v>
@@ -4470,7 +4470,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B106" s="7">
         <f t="shared" ref="B106:G106" si="19">B95-B$100</f>
         <v>-1</v>
@@ -4518,7 +4518,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>79</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>0.99972295331231709</v>
       </c>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>80</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B109">
         <f>(B102^2+B103^2+B104^2+B105^2+B106^2)^(1/2)</f>
         <v>2</v>
@@ -4652,7 +4652,7 @@
         <v>18.994736112934024</v>
       </c>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>81</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>8.9554452708952432</v>
       </c>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B111" s="18">
         <f>B102/B$109</f>
         <v>0.5</v>
@@ -4693,7 +4693,7 @@
         <v>-0.10241085157359611</v>
       </c>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B112" s="18">
         <f t="shared" ref="B112:I115" si="23">B103/B$109</f>
         <v>-0.5</v>
@@ -4739,7 +4739,7 @@
         <v>1.7888543819998317</v>
       </c>
     </row>
-    <row r="113" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B113" s="18">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -4797,7 +4797,7 @@
         <v>0.89442719099991586</v>
       </c>
     </row>
-    <row r="114" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B114" s="18">
         <f t="shared" si="23"/>
         <v>0.5</v>
@@ -4860,7 +4860,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="115" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B115" s="18">
         <f t="shared" si="23"/>
         <v>-0.5</v>
@@ -4919,7 +4919,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="117" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:29" x14ac:dyDescent="0.25">
       <c r="Z117" t="s">
         <v>84</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>8.717797887081348</v>
       </c>
     </row>
-    <row r="118" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:29" x14ac:dyDescent="0.25">
       <c r="L118">
         <f>51/5</f>
         <v>10.199999999999999</v>
@@ -4982,12 +4982,12 @@
         <v>10.198039027185569</v>
       </c>
     </row>
-    <row r="120" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:29" x14ac:dyDescent="0.25">
       <c r="H120">
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:29" x14ac:dyDescent="0.25">
       <c r="H121">
         <v>5</v>
       </c>
@@ -4996,7 +4996,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="122" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:29" x14ac:dyDescent="0.25">
       <c r="H122">
         <v>10</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F123">
         <v>-240</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="124" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F124">
         <v>-840</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="125" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F125">
         <v>-540</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="126" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F126">
         <v>-440</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="127" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:29" x14ac:dyDescent="0.25">
       <c r="F127">
         <v>2060</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>10609</v>
       </c>
     </row>
-    <row r="128" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:29" x14ac:dyDescent="0.25">
       <c r="W128">
         <v>2</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>1.4142135623730951</v>
       </c>
     </row>
-    <row r="129" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="129" spans="5:24" x14ac:dyDescent="0.25">
       <c r="J129">
         <f>SUM(J123:J128)</f>
         <v>13730</v>
@@ -5229,7 +5229,7 @@
         <v>1.7320508075688772</v>
       </c>
     </row>
-    <row r="130" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="130" spans="5:24" x14ac:dyDescent="0.25">
       <c r="J130">
         <f>SQRT(J129)</f>
         <v>117.17508267545622</v>
@@ -5243,7 +5243,7 @@
         <v>117.17508267545622</v>
       </c>
     </row>
-    <row r="131" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="131" spans="5:24" x14ac:dyDescent="0.25">
       <c r="W131">
         <f>W128/W129</f>
         <v>0.66666666666666663</v>
@@ -5253,7 +5253,7 @@
         <v>0.81649658092772615</v>
       </c>
     </row>
-    <row r="132" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="132" spans="5:24" x14ac:dyDescent="0.25">
       <c r="F132">
         <f>G132*H132</f>
         <v>117</v>
@@ -5299,7 +5299,7 @@
         <v>0.81649658092772603</v>
       </c>
     </row>
-    <row r="133" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="133" spans="5:24" x14ac:dyDescent="0.25">
       <c r="I133">
         <f>I132*20</f>
         <v>2340</v>
@@ -5309,7 +5309,7 @@
         <v>-41</v>
       </c>
     </row>
-    <row r="135" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="135" spans="5:24" x14ac:dyDescent="0.25">
       <c r="H135">
         <f>I135/2</f>
         <v>59</v>
@@ -5334,13 +5334,13 @@
         <v>13.857142857142858</v>
       </c>
     </row>
-    <row r="136" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="136" spans="5:24" x14ac:dyDescent="0.25">
       <c r="I136">
         <f>I135*20</f>
         <v>2360</v>
       </c>
     </row>
-    <row r="139" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="139" spans="5:24" x14ac:dyDescent="0.25">
       <c r="E139">
         <v>19</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>94.973680564670133</v>
       </c>
     </row>
-    <row r="140" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="140" spans="5:24" x14ac:dyDescent="0.25">
       <c r="F140">
         <v>1805</v>
       </c>
@@ -5371,13 +5371,13 @@
         <v>24010</v>
       </c>
     </row>
-    <row r="141" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="141" spans="5:24" x14ac:dyDescent="0.25">
       <c r="J141">
         <f>J139/J140</f>
         <v>360.8</v>
       </c>
     </row>
-    <row r="142" spans="5:24" x14ac:dyDescent="0.35">
+    <row r="142" spans="5:24" x14ac:dyDescent="0.25">
       <c r="M142">
         <v>7</v>
       </c>
@@ -5390,12 +5390,12 @@
         <v>2401</v>
       </c>
     </row>
-    <row r="148" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="148" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D148">
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D149">
         <v>5</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>2.2360679774997898</v>
       </c>
     </row>
-    <row r="150" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D150">
         <f>D148/D149</f>
         <v>0.4</v>
@@ -5414,23 +5414,23 @@
         <v>0.89442719099991597</v>
       </c>
     </row>
-    <row r="151" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C151">
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="152" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C152">
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="153" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C153">
         <f>C151/C152</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="154" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="154" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C154">
         <f>SQRT(C153)</f>
         <v>0.89442719099991586</v>
@@ -5439,7 +5439,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="155" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="155" spans="3:7" x14ac:dyDescent="0.25">
       <c r="E155">
         <f>SQRT(E154)</f>
         <v>4.4721359549995796</v>
@@ -5448,7 +5448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="156" spans="3:7" x14ac:dyDescent="0.25">
       <c r="G156">
         <f>G155/E155</f>
         <v>0.22360679774997896</v>
@@ -5464,9 +5464,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{666D1E91-ED7C-475C-A636-9777A928839D}">
   <dimension ref="A3:O72"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -5493,7 +5493,7 @@
         <v>1.4310835055998654</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>1.4310835055998654</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13">
         <f t="shared" ref="B13" si="4">B14-1</f>
         <v>1</v>
@@ -5534,7 +5534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14">
         <f t="shared" ref="B14:B15" si="7">B15-1</f>
         <v>2</v>
@@ -5548,7 +5548,7 @@
         <v>0.70710678118654757</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15">
         <f t="shared" si="7"/>
         <v>3</v>
@@ -5562,7 +5562,7 @@
         <v>0.57735026918962573</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16">
         <f>B17-1</f>
         <v>4</v>
@@ -5576,7 +5576,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>5</v>
       </c>
@@ -5589,7 +5589,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18">
         <f>B17+1</f>
         <v>6</v>
@@ -5603,7 +5603,7 @@
         <v>0.40824829046386296</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19">
         <f t="shared" ref="B19:B27" si="11">B18+1</f>
         <v>7</v>
@@ -5617,7 +5617,7 @@
         <v>0.37796447300922725</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20">
         <f t="shared" si="11"/>
         <v>8</v>
@@ -5631,7 +5631,7 @@
         <v>0.35355339059327379</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21">
         <f t="shared" si="11"/>
         <v>9</v>
@@ -5645,7 +5645,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22">
         <f t="shared" si="11"/>
         <v>10</v>
@@ -5659,7 +5659,7 @@
         <v>0.31622776601683794</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23">
         <f t="shared" si="11"/>
         <v>11</v>
@@ -5673,7 +5673,7 @@
         <v>0.30151134457776363</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24">
         <f t="shared" si="11"/>
         <v>12</v>
@@ -5687,7 +5687,7 @@
         <v>0.28867513459481287</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25">
         <f t="shared" si="11"/>
         <v>13</v>
@@ -5701,7 +5701,7 @@
         <v>0.27735009811261457</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26">
         <f t="shared" si="11"/>
         <v>14</v>
@@ -5715,7 +5715,7 @@
         <v>0.2672612419124244</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27">
         <f t="shared" si="11"/>
         <v>15</v>
@@ -5729,7 +5729,7 @@
         <v>0.25819888974716115</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28">
         <f t="shared" ref="B28:B58" si="12">B27+1</f>
         <v>16</v>
@@ -5743,7 +5743,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29">
         <f t="shared" si="12"/>
         <v>17</v>
@@ -5757,7 +5757,7 @@
         <v>0.24253562503633297</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30">
         <f t="shared" si="12"/>
         <v>18</v>
@@ -5771,7 +5771,7 @@
         <v>0.23570226039551581</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31">
         <f t="shared" si="12"/>
         <v>19</v>
@@ -5785,7 +5785,7 @@
         <v>0.2294157338705618</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32">
         <f t="shared" si="12"/>
         <v>20</v>
@@ -5799,7 +5799,7 @@
         <v>0.22360679774997899</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33">
         <f t="shared" si="12"/>
         <v>21</v>
@@ -5813,7 +5813,7 @@
         <v>0.21821789023599236</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34">
         <f t="shared" si="12"/>
         <v>22</v>
@@ -5827,7 +5827,7 @@
         <v>0.21320071635561044</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35">
         <f t="shared" si="12"/>
         <v>23</v>
@@ -5841,7 +5841,7 @@
         <v>0.20851441405707474</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36">
         <f t="shared" si="12"/>
         <v>24</v>
@@ -5862,7 +5862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B37">
         <f t="shared" si="12"/>
         <v>25</v>
@@ -5891,7 +5891,7 @@
         <v>1.1180339887498949</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B38">
         <f t="shared" si="12"/>
         <v>26</v>
@@ -5913,7 +5913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B39">
         <f t="shared" si="12"/>
         <v>27</v>
@@ -5946,7 +5946,7 @@
         <v>1.1180339887498949</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B40">
         <f t="shared" si="12"/>
         <v>28</v>
@@ -5963,7 +5963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B41">
         <f t="shared" si="12"/>
         <v>29</v>
@@ -6002,7 +6002,7 @@
         <v>0.22360679774997899</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B42">
         <f t="shared" si="12"/>
         <v>30</v>
@@ -6024,7 +6024,7 @@
         <v>0.1118033988749895</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43">
         <f t="shared" si="12"/>
         <v>31</v>
@@ -6038,7 +6038,7 @@
         <v>0.17960530202677488</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B44">
         <f t="shared" si="12"/>
         <v>32</v>
@@ -6061,7 +6061,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B45">
         <f t="shared" si="12"/>
         <v>33</v>
@@ -6108,7 +6108,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B46">
         <f t="shared" si="12"/>
         <v>34</v>
@@ -6122,7 +6122,7 @@
         <v>0.17149858514250885</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47">
         <f t="shared" si="12"/>
         <v>35</v>
@@ -6139,7 +6139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B48">
         <f t="shared" si="12"/>
         <v>36</v>
@@ -6160,7 +6160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49">
         <f t="shared" si="12"/>
         <v>37</v>
@@ -6180,7 +6180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50">
         <f t="shared" si="12"/>
         <v>38</v>
@@ -6198,7 +6198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51">
         <f t="shared" si="12"/>
         <v>39</v>
@@ -6216,7 +6216,7 @@
         <v>1.1180339887498949</v>
       </c>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52">
         <f t="shared" si="12"/>
         <v>40</v>
@@ -6233,7 +6233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53">
         <f t="shared" si="12"/>
         <v>41</v>
@@ -6258,7 +6258,7 @@
         <v>0.1118033988749895</v>
       </c>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54">
         <f t="shared" si="12"/>
         <v>42</v>
@@ -6275,7 +6275,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55">
         <f t="shared" si="12"/>
         <v>43</v>
@@ -6293,7 +6293,7 @@
         <v>22.360679774997898</v>
       </c>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56">
         <f t="shared" si="12"/>
         <v>44</v>
@@ -6310,7 +6310,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57">
         <f t="shared" si="12"/>
         <v>45</v>
@@ -6328,7 +6328,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58">
         <f t="shared" si="12"/>
         <v>46</v>
@@ -6342,28 +6342,28 @@
         <v>0.14744195615489714</v>
       </c>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="F60">
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="F61">
         <f>SQRT(F60)</f>
         <v>2.8284271247461903</v>
       </c>
     </row>
-    <row r="66" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="6:10" x14ac:dyDescent="0.25">
       <c r="G66">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="6:10" x14ac:dyDescent="0.25">
       <c r="G67">
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F68">
         <v>2</v>
       </c>
@@ -6378,7 +6378,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="6:10" x14ac:dyDescent="0.25">
       <c r="H69">
         <f>H68/G68</f>
         <v>0.55901699437494745</v>
@@ -6392,12 +6392,12 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="71" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F71">
         <v>80</v>
       </c>
     </row>
-    <row r="72" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F72">
         <f>SQRT(F71)</f>
         <v>8.9442719099991592</v>
@@ -6417,26 +6417,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82BA3844-AF00-4659-9CA6-FDAA4D3C4028}">
-  <dimension ref="A2:T66"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:T83"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="K2">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="K3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="K4">
         <f>K2/K3</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="J5">
         <v>2</v>
       </c>
@@ -6445,7 +6445,7 @@
         <v>0.89442719099991586</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="J6">
         <v>1</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>1.7888543819998317</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="E7">
         <v>1</v>
       </c>
@@ -6470,7 +6470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="E8">
         <v>1804</v>
       </c>
@@ -6482,7 +6482,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B9" t="str">
         <f>C17</f>
         <v>x_1</v>
@@ -6514,7 +6514,7 @@
         <v>y</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="E10">
         <f>SQRT(E8/E9)</f>
         <v>0.99972295331231709</v>
@@ -6529,7 +6529,7 @@
         <v>13689</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>-0.10241085157359613</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>-0.35843798050758646</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="20">
         <f>A11/A12</f>
         <v>0.5</v>
@@ -6726,7 +6726,7 @@
         <v>-0.23042441604059127</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B14" s="7">
         <v>1</v>
       </c>
@@ -6770,7 +6770,7 @@
         <v>-0.18775322788492624</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B15" s="7">
         <v>-1</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>0.87902647600670003</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>92</v>
       </c>
@@ -6834,7 +6834,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C19" s="24">
         <f>C11</f>
         <v>0.5</v>
@@ -6860,7 +6860,7 @@
         <v>-0.10241085157359613</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C20" s="24">
         <f t="shared" ref="C20:C23" si="6">C12</f>
         <v>-0.5</v>
@@ -6886,7 +6886,7 @@
         <v>-0.35843798050758646</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C21" s="24">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -6912,7 +6912,7 @@
         <v>-0.23042441604059127</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C22" s="24">
         <f t="shared" si="6"/>
         <v>0.5</v>
@@ -6938,7 +6938,7 @@
         <v>-0.18775322788492624</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C23" s="24">
         <f t="shared" si="6"/>
         <v>-0.5</v>
@@ -6964,7 +6964,7 @@
         <v>0.87902647600670003</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C24" s="22"/>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -6980,7 +6980,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C25" s="22">
         <f>SUM(C19:C24)</f>
         <v>0</v>
@@ -7006,13 +7006,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="R26">
         <f>4/5</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="26">
         <v>4</v>
       </c>
@@ -7049,7 +7049,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C28" s="28">
         <f t="shared" ref="C28:H28" si="14">ROUND(C20,$A$27)</f>
         <v>-0.5</v>
@@ -7079,7 +7079,7 @@
         <v>-0,5 &amp; -0,8002 &amp; -0,5 &amp; -0,2236 &amp; 0,1118 &amp; -0,3584 \\</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C29" s="28">
         <f t="shared" ref="C29:H29" si="16">ROUND(C21,$A$27)</f>
         <v>0</v>
@@ -7109,7 +7109,7 @@
         <v>0 &amp; -0,0105 &amp; 0 &amp; -0,2236 &amp; 0,1118 &amp; -0,2304 \\</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C30" s="28">
         <f t="shared" ref="C30:H30" si="17">ROUND(C22,$A$27)</f>
         <v>0.5</v>
@@ -7139,7 +7139,7 @@
         <v>0,5 &amp; 0,5159 &amp; -0,5 &amp; -0,2236 &amp; 0,1118 &amp; -0,1878 \\</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C31" s="28">
         <f t="shared" ref="C31:H31" si="18">ROUND(C23,$A$27)</f>
         <v>-0.5</v>
@@ -7169,7 +7169,7 @@
         <v>-0,5 &amp; -0,0105 &amp; 0,5 &amp; 0,8944 &amp; -0,4472 &amp; 0,879 \\</v>
       </c>
     </row>
-    <row r="33" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C33" s="27">
         <f>SUM(C27:C32)</f>
         <v>0</v>
@@ -7202,7 +7202,7 @@
         <v>1</v>
       </c>
       <c r="S33">
-        <f>Q33/$R$41</f>
+        <f t="shared" ref="S33:S38" si="20">Q33/$R$41</f>
         <v>0.1889822365046136</v>
       </c>
       <c r="T33">
@@ -7210,24 +7210,24 @@
         <v>3.5714285714285705E-2</v>
       </c>
     </row>
-    <row r="34" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:20" x14ac:dyDescent="0.25">
       <c r="Q34">
         <v>2</v>
       </c>
       <c r="R34">
-        <f t="shared" ref="R34:R38" si="20">Q34^2</f>
+        <f t="shared" ref="R34:R38" si="21">Q34^2</f>
         <v>4</v>
       </c>
       <c r="S34">
-        <f>Q34/$R$41</f>
+        <f t="shared" si="20"/>
         <v>0.3779644730092272</v>
       </c>
       <c r="T34">
-        <f t="shared" ref="T34:T38" si="21">S34^2</f>
+        <f t="shared" ref="T34:T38" si="22">S34^2</f>
         <v>0.14285714285714282</v>
       </c>
     </row>
-    <row r="35" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C35" s="25"/>
       <c r="I35" s="30">
         <v>-0.1024</v>
@@ -7248,19 +7248,19 @@
         <v>3</v>
       </c>
       <c r="R35">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="S35">
         <f t="shared" si="20"/>
-        <v>9</v>
-      </c>
-      <c r="S35">
-        <f>Q35/$R$41</f>
         <v>0.56694670951384085</v>
       </c>
       <c r="T35">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.32142857142857145</v>
       </c>
     </row>
-    <row r="36" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C36" s="30">
         <v>0.5</v>
       </c>
@@ -7287,19 +7287,19 @@
         <v>-1</v>
       </c>
       <c r="R36">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="S36">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="S36">
-        <f>Q36/$R$41</f>
         <v>-0.1889822365046136</v>
       </c>
       <c r="T36">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3.5714285714285705E-2</v>
       </c>
     </row>
-    <row r="37" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C37" s="30">
         <v>-0.5</v>
       </c>
@@ -7326,19 +7326,19 @@
         <v>-2</v>
       </c>
       <c r="R37">
+        <f t="shared" si="21"/>
+        <v>4</v>
+      </c>
+      <c r="S37">
         <f t="shared" si="20"/>
-        <v>4</v>
-      </c>
-      <c r="S37">
-        <f>Q37/$R$41</f>
         <v>-0.3779644730092272</v>
       </c>
       <c r="T37">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.14285714285714282</v>
       </c>
     </row>
-    <row r="38" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C38" s="30">
         <v>0</v>
       </c>
@@ -7365,19 +7365,19 @@
         <v>-3</v>
       </c>
       <c r="R38">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="S38">
         <f t="shared" si="20"/>
-        <v>9</v>
-      </c>
-      <c r="S38">
-        <f>Q38/$R$41</f>
         <v>-0.56694670951384085</v>
       </c>
       <c r="T38">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.32142857142857145</v>
       </c>
     </row>
-    <row r="39" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C39" s="30">
         <v>0.5</v>
       </c>
@@ -7401,7 +7401,7 @@
         <v>-9.3899999999999997E-2</v>
       </c>
     </row>
-    <row r="40" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C40" s="30">
         <v>-0.5</v>
       </c>
@@ -7437,13 +7437,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:20" x14ac:dyDescent="0.25">
       <c r="R41">
         <f>SQRT(R40)</f>
         <v>5.2915026221291814</v>
       </c>
     </row>
-    <row r="43" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C43" s="30">
         <v>0.5</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>0,5 \\ -0,5 \\ 0 \\ 0,5 \\ -0,5</v>
       </c>
     </row>
-    <row r="44" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C44" s="30">
         <v>0.30530000000000002</v>
       </c>
@@ -7481,7 +7481,7 @@
         <v>-1.0500000000000001E-2</v>
       </c>
     </row>
-    <row r="45" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="45" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C45" s="30">
         <v>0.5</v>
       </c>
@@ -7498,7 +7498,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="46" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C46" s="30">
         <v>-0.22359999999999999</v>
       </c>
@@ -7515,7 +7515,7 @@
         <v>0.89439999999999997</v>
       </c>
     </row>
-    <row r="47" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="47" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C47" s="30">
         <v>0.1118</v>
       </c>
@@ -7532,7 +7532,7 @@
         <v>-0.44719999999999999</v>
       </c>
     </row>
-    <row r="48" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="48" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C48" s="30">
         <v>-0.1024</v>
       </c>
@@ -7553,7 +7553,7 @@
         <v>-0,1024 &amp; -0,3584 &amp; -0,2304 &amp; -0,1878 &amp; 0,879</v>
       </c>
     </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C51" s="25"/>
       <c r="I51" s="30"/>
       <c r="J51" s="30"/>
@@ -7561,7 +7561,7 @@
       <c r="L51" s="30"/>
       <c r="M51" s="30"/>
     </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C52" s="30">
         <v>0.5</v>
       </c>
@@ -7585,7 +7585,7 @@
         <v>0,3053 &amp; -0,1024 \\</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C53" s="30">
         <v>-0.5</v>
       </c>
@@ -7605,11 +7605,11 @@
         <v>-0.3584</v>
       </c>
       <c r="J53" t="str">
-        <f t="shared" ref="J53:J56" si="22">D53&amp;" &amp; "&amp;H53&amp;" \\"</f>
+        <f t="shared" ref="J53:J56" si="23">D53&amp;" &amp; "&amp;H53&amp;" \\"</f>
         <v>-0,8002 &amp; -0,3584 \\</v>
       </c>
     </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C54" s="30">
         <v>0</v>
       </c>
@@ -7629,11 +7629,11 @@
         <v>-0.23039999999999999</v>
       </c>
       <c r="J54" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-0,0105 &amp; -0,2304 \\</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C55" s="30">
         <v>0.5</v>
       </c>
@@ -7653,11 +7653,11 @@
         <v>-0.18779999999999999</v>
       </c>
       <c r="J55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0,5159 &amp; -0,1878 \\</v>
       </c>
     </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C56" s="30">
         <v>-0.5</v>
       </c>
@@ -7677,11 +7677,11 @@
         <v>0.879</v>
       </c>
       <c r="J56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-0,0105 &amp; 0,879 \\</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C59" s="30">
         <v>0.5</v>
       </c>
@@ -7702,7 +7702,7 @@
         <v>0,5 \\ -0,5 \\ 0 \\ 0,5 \\ -0,5</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C60" s="30">
         <v>0.30530000000000002</v>
       </c>
@@ -7723,7 +7723,7 @@
         <v>0,3053 &amp; -0,8002 &amp; -0,0105 &amp; 0,5159 &amp; -0,0105</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C61" s="30">
         <v>0.5</v>
       </c>
@@ -7740,7 +7740,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C62" s="30">
         <v>-0.22359999999999999</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>0.89439999999999997</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C63" s="30">
         <v>0.1118</v>
       </c>
@@ -7774,7 +7774,7 @@
         <v>-0.44719999999999999</v>
       </c>
     </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C64" s="30">
         <v>-0.1024</v>
       </c>
@@ -7795,8 +7795,455 @@
         <v>-0,1024 &amp; -0,3584 &amp; -0,2304 &amp; -0,1878 &amp; 0,879</v>
       </c>
     </row>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="69" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C69" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D69" s="11">
+        <v>0.30534775347842946</v>
+      </c>
+      <c r="E69" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F69" s="11">
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="G69" s="11">
+        <v>0.11180339887498948</v>
+      </c>
+      <c r="H69" s="11">
+        <v>-0.10241085157359613</v>
+      </c>
+      <c r="J69">
+        <f>C69*$H69</f>
+        <v>-5.1205425786798063E-2</v>
+      </c>
+      <c r="K69">
+        <f t="shared" ref="K69:O69" si="24">D69*$H69</f>
+        <v>-3.127092345981046E-2</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="24"/>
+        <v>-5.1205425786798063E-2</v>
+      </c>
+      <c r="M69">
+        <f t="shared" si="24"/>
+        <v>2.2899762575220223E-2</v>
+      </c>
+      <c r="N69">
+        <f t="shared" si="24"/>
+        <v>-1.1449881287610111E-2</v>
+      </c>
+      <c r="O69">
+        <f t="shared" si="24"/>
+        <v>1.0487982520029136E-2</v>
+      </c>
+      <c r="Q69" t="str">
+        <f>J69&amp;" &amp; "&amp;K69&amp;" &amp; "&amp;L69&amp;" &amp; "&amp;M69&amp;" &amp; "&amp;N69&amp;" &amp; "&amp;O69</f>
+        <v>-0.0512054257867981 &amp; -0.0312709234598105 &amp; -0.0512054257867981 &amp; 0.0228997625752202 &amp; -0.0114498812876101 &amp; 0.0104879825200291</v>
+      </c>
+    </row>
+    <row r="70" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C70" s="11">
+        <v>-0.5</v>
+      </c>
+      <c r="D70" s="11">
+        <v>-0.80022169877105653</v>
+      </c>
+      <c r="E70" s="11">
+        <v>-0.5</v>
+      </c>
+      <c r="F70" s="11">
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="G70" s="11">
+        <v>0.11180339887498948</v>
+      </c>
+      <c r="H70" s="11">
+        <v>-0.35843798050758646</v>
+      </c>
+      <c r="J70">
+        <f t="shared" ref="J70:J73" si="25">C70*$H70</f>
+        <v>0.17921899025379323</v>
+      </c>
+      <c r="K70">
+        <f t="shared" ref="K70:K73" si="26">D70*$H70</f>
+        <v>0.28682984966584768</v>
+      </c>
+      <c r="L70">
+        <f t="shared" ref="L70:L73" si="27">E70*$H70</f>
+        <v>0.17921899025379323</v>
+      </c>
+      <c r="M70">
+        <f t="shared" ref="M70:M73" si="28">F70*$H70</f>
+        <v>8.0149169013270793E-2</v>
+      </c>
+      <c r="N70">
+        <f t="shared" ref="N70:N73" si="29">G70*$H70</f>
+        <v>-4.0074584506635397E-2</v>
+      </c>
+      <c r="O70">
+        <f t="shared" ref="O70:O73" si="30">H70*$H70</f>
+        <v>0.12847778587035694</v>
+      </c>
+      <c r="Q70" t="str">
+        <f t="shared" ref="Q70:Q73" si="31">J70&amp;" &amp; "&amp;K70&amp;" &amp; "&amp;L70&amp;" &amp; "&amp;M70&amp;" &amp; "&amp;N70&amp;" &amp; "&amp;O70</f>
+        <v>0.179218990253793 &amp; 0.286829849665848 &amp; 0.179218990253793 &amp; 0.0801491690132708 &amp; -0.0400745845066354 &amp; 0.128477785870357</v>
+      </c>
+    </row>
+    <row r="71" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C71" s="11">
+        <v>0</v>
+      </c>
+      <c r="D71" s="11">
+        <v>-1.0529232878566533E-2</v>
+      </c>
+      <c r="E71" s="11">
+        <v>0</v>
+      </c>
+      <c r="F71" s="11">
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="G71" s="11">
+        <v>0.11180339887498948</v>
+      </c>
+      <c r="H71" s="11">
+        <v>-0.23042441604059127</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="26"/>
+        <v>2.4261923373990872E-3</v>
+      </c>
+      <c r="L71">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <f t="shared" si="28"/>
+        <v>5.1524465794245501E-2</v>
+      </c>
+      <c r="N71">
+        <f t="shared" si="29"/>
+        <v>-2.5762232897122751E-2</v>
+      </c>
+      <c r="O71">
+        <f t="shared" si="30"/>
+        <v>5.3095411507647496E-2</v>
+      </c>
+      <c r="Q71" t="str">
+        <f t="shared" si="31"/>
+        <v>0 &amp; 0.00242619233739909 &amp; 0 &amp; 0.0515244657942455 &amp; -0.0257622328971228 &amp; 0.0530954115076475</v>
+      </c>
+    </row>
+    <row r="72" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C72" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D72" s="11">
+        <v>0.51593241104976018</v>
+      </c>
+      <c r="E72" s="11">
+        <v>-0.5</v>
+      </c>
+      <c r="F72" s="11">
+        <v>-0.22360679774997896</v>
+      </c>
+      <c r="G72" s="11">
+        <v>0.11180339887498948</v>
+      </c>
+      <c r="H72" s="11">
+        <v>-0.18775322788492624</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="25"/>
+        <v>-9.3876613942463119E-2</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="26"/>
+        <v>-9.686797554504506E-2</v>
+      </c>
+      <c r="L72">
+        <f t="shared" si="27"/>
+        <v>9.3876613942463119E-2</v>
+      </c>
+      <c r="M72">
+        <f t="shared" si="28"/>
+        <v>4.1982898054570415E-2</v>
+      </c>
+      <c r="N72">
+        <f t="shared" si="29"/>
+        <v>-2.0991449027285208E-2</v>
+      </c>
+      <c r="O72">
+        <f t="shared" si="30"/>
+        <v>3.5251274581209045E-2</v>
+      </c>
+      <c r="Q72" t="str">
+        <f t="shared" si="31"/>
+        <v>-0.0938766139424631 &amp; -0.0968679755450451 &amp; 0.0938766139424631 &amp; 0.0419828980545704 &amp; -0.0209914490272852 &amp; 0.035251274581209</v>
+      </c>
+    </row>
+    <row r="73" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C73" s="11">
+        <v>-0.5</v>
+      </c>
+      <c r="D73" s="11">
+        <v>-1.0529232878566533E-2</v>
+      </c>
+      <c r="E73" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F73" s="11">
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="G73" s="11">
+        <v>-0.44721359549995793</v>
+      </c>
+      <c r="H73" s="11">
+        <v>0.87902647600670003</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="25"/>
+        <v>-0.43951323800335002</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="26"/>
+        <v>-9.2554744723002211E-3</v>
+      </c>
+      <c r="L73">
+        <f t="shared" si="27"/>
+        <v>0.43951323800335002</v>
+      </c>
+      <c r="M73">
+        <f t="shared" si="28"/>
+        <v>0.78622518174922762</v>
+      </c>
+      <c r="N73">
+        <f t="shared" si="29"/>
+        <v>-0.39311259087461381</v>
+      </c>
+      <c r="O73">
+        <f t="shared" si="30"/>
+        <v>0.77268754552075758</v>
+      </c>
+      <c r="Q73" t="str">
+        <f t="shared" si="31"/>
+        <v>-0.43951323800335 &amp; -0.00925547447230022 &amp; 0.43951323800335 &amp; 0.786225181749228 &amp; -0.393112590874614 &amp; 0.772687545520758</v>
+      </c>
+    </row>
+    <row r="75" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="J75">
+        <f>SUM(J69:J74)</f>
+        <v>-0.40537628747881799</v>
+      </c>
+      <c r="K75">
+        <f t="shared" ref="K75:O75" si="32">SUM(K69:K74)</f>
+        <v>0.15186166852609104</v>
+      </c>
+      <c r="L75">
+        <f t="shared" si="32"/>
+        <v>0.66140341641280831</v>
+      </c>
+      <c r="M75">
+        <f t="shared" si="32"/>
+        <v>0.98278147718653452</v>
+      </c>
+      <c r="N75">
+        <f t="shared" si="32"/>
+        <v>-0.49139073859326726</v>
+      </c>
+      <c r="O75">
+        <f t="shared" si="32"/>
+        <v>1.0000000000000002</v>
+      </c>
+    </row>
+    <row r="77" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="I77" s="26">
+        <v>2</v>
+      </c>
+      <c r="J77">
+        <f>ROUND(J69,$I$77)</f>
+        <v>-0.05</v>
+      </c>
+      <c r="K77">
+        <f t="shared" ref="K77:O77" si="33">ROUND(K69,$I$77)</f>
+        <v>-0.03</v>
+      </c>
+      <c r="L77">
+        <f t="shared" si="33"/>
+        <v>-0.05</v>
+      </c>
+      <c r="M77">
+        <f t="shared" si="33"/>
+        <v>0.02</v>
+      </c>
+      <c r="N77">
+        <f t="shared" si="33"/>
+        <v>-0.01</v>
+      </c>
+      <c r="O77">
+        <f t="shared" si="33"/>
+        <v>0.01</v>
+      </c>
+      <c r="Q77" t="str">
+        <f t="shared" ref="Q77:Q83" si="34">J77&amp;" &amp; "&amp;K77&amp;" &amp; "&amp;L77&amp;" &amp; "&amp;M77&amp;" &amp; "&amp;N77&amp;" &amp; "&amp;O77</f>
+        <v>-0.05 &amp; -0.03 &amp; -0.05 &amp; 0.02 &amp; -0.01 &amp; 0.01</v>
+      </c>
+    </row>
+    <row r="78" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="J78">
+        <f t="shared" ref="J78:O78" si="35">ROUND(J70,$I$77)</f>
+        <v>0.18</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="35"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L78">
+        <f t="shared" si="35"/>
+        <v>0.18</v>
+      </c>
+      <c r="M78">
+        <f t="shared" si="35"/>
+        <v>0.08</v>
+      </c>
+      <c r="N78">
+        <f t="shared" si="35"/>
+        <v>-0.04</v>
+      </c>
+      <c r="O78">
+        <f t="shared" si="35"/>
+        <v>0.13</v>
+      </c>
+      <c r="Q78" t="str">
+        <f t="shared" si="34"/>
+        <v>0.18 &amp; 0.29 &amp; 0.18 &amp; 0.08 &amp; -0.04 &amp; 0.13</v>
+      </c>
+    </row>
+    <row r="79" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="J79">
+        <f t="shared" ref="J79:O79" si="36">ROUND(J71,$I$77)</f>
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <f t="shared" si="36"/>
+        <v>0.05</v>
+      </c>
+      <c r="N79">
+        <f t="shared" si="36"/>
+        <v>-0.03</v>
+      </c>
+      <c r="O79">
+        <f t="shared" si="36"/>
+        <v>0.05</v>
+      </c>
+      <c r="Q79" t="str">
+        <f t="shared" si="34"/>
+        <v>0 &amp; 0 &amp; 0 &amp; 0.05 &amp; -0.03 &amp; 0.05</v>
+      </c>
+    </row>
+    <row r="80" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="J80">
+        <f t="shared" ref="J80:O80" si="37">ROUND(J72,$I$77)</f>
+        <v>-0.09</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="37"/>
+        <v>-0.1</v>
+      </c>
+      <c r="L80">
+        <f t="shared" si="37"/>
+        <v>0.09</v>
+      </c>
+      <c r="M80">
+        <f t="shared" si="37"/>
+        <v>0.04</v>
+      </c>
+      <c r="N80">
+        <f t="shared" si="37"/>
+        <v>-0.02</v>
+      </c>
+      <c r="O80">
+        <f t="shared" si="37"/>
+        <v>0.04</v>
+      </c>
+      <c r="Q80" t="str">
+        <f t="shared" si="34"/>
+        <v>-0.09 &amp; -0.1 &amp; 0.09 &amp; 0.04 &amp; -0.02 &amp; 0.04</v>
+      </c>
+    </row>
+    <row r="81" spans="10:17" x14ac:dyDescent="0.25">
+      <c r="J81">
+        <f t="shared" ref="J81:O81" si="38">ROUND(J73,$I$77)</f>
+        <v>-0.44</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="38"/>
+        <v>-0.01</v>
+      </c>
+      <c r="L81">
+        <f t="shared" si="38"/>
+        <v>0.44</v>
+      </c>
+      <c r="M81">
+        <f t="shared" si="38"/>
+        <v>0.79</v>
+      </c>
+      <c r="N81">
+        <f t="shared" si="38"/>
+        <v>-0.39</v>
+      </c>
+      <c r="O81">
+        <f t="shared" si="38"/>
+        <v>0.77</v>
+      </c>
+      <c r="Q81" t="str">
+        <f t="shared" si="34"/>
+        <v>-0.44 &amp; -0.01 &amp; 0.44 &amp; 0.79 &amp; -0.39 &amp; 0.77</v>
+      </c>
+    </row>
+    <row r="83" spans="10:17" x14ac:dyDescent="0.25">
+      <c r="J83">
+        <f>SUM(J77:J82)</f>
+        <v>-0.4</v>
+      </c>
+      <c r="K83">
+        <f t="shared" ref="K83" si="39">SUM(K77:K82)</f>
+        <v>0.15</v>
+      </c>
+      <c r="L83">
+        <f t="shared" ref="L83" si="40">SUM(L77:L82)</f>
+        <v>0.66</v>
+      </c>
+      <c r="M83">
+        <f t="shared" ref="M83" si="41">SUM(M77:M82)</f>
+        <v>0.98000000000000009</v>
+      </c>
+      <c r="N83">
+        <f t="shared" ref="N83" si="42">SUM(N77:N82)</f>
+        <v>-0.49</v>
+      </c>
+      <c r="O83">
+        <f t="shared" ref="O83" si="43">SUM(O77:O82)</f>
+        <v>1</v>
+      </c>
+      <c r="Q83" t="str">
+        <f>J83&amp;" &amp; "&amp;K83&amp;" &amp; "&amp;L83&amp;" &amp; "&amp;M83&amp;" &amp; "&amp;N83&amp;" &amp; "&amp;O83&amp;" \\"</f>
+        <v>-0.4 &amp; 0.15 &amp; 0.66 &amp; 0.98 &amp; -0.49 &amp; 1 \\</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Edu/Linear_algebra/linal_session_task.xlsx
+++ b/Edu/Linear_algebra/linal_session_task.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LysogorA\DataScience\Edu\Linear_algebra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D03A45-8DE2-4F8B-AB00-D5DDE8DC62E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A692C3-DADE-4900-B0BC-8FD14E0A5956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <sheet name="st" sheetId="3" r:id="rId3"/>
+    <sheet name="split1" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
+    <sheet name="st" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="105">
   <si>
     <t>Рабочая таблица с данными:</t>
   </si>
@@ -332,6 +333,27 @@
   </si>
   <si>
     <t>y</t>
+  </si>
+  <si>
+    <t>среднее</t>
+  </si>
+  <si>
+    <t>центрированые</t>
+  </si>
+  <si>
+    <t>длина ц.в.</t>
+  </si>
+  <si>
+    <t>standart</t>
+  </si>
+  <si>
+    <t>check</t>
+  </si>
+  <si>
+    <t>Спальный</t>
+  </si>
+  <si>
+    <t>Центральный</t>
   </si>
 </sst>
 </file>
@@ -545,7 +567,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -594,6 +616,7 @@
     <xf numFmtId="165" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5462,6 +5485,556 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{187E156B-4495-4400-8873-A45B82A27CF2}">
+  <dimension ref="B1:L28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C3" s="7">
+        <v>3</v>
+      </c>
+      <c r="D3" s="7">
+        <v>51</v>
+      </c>
+      <c r="E3" s="7">
+        <v>3</v>
+      </c>
+      <c r="F3" s="7">
+        <v>2200</v>
+      </c>
+      <c r="H3" s="7">
+        <v>1</v>
+      </c>
+      <c r="I3" s="7">
+        <v>45</v>
+      </c>
+      <c r="J3" s="7">
+        <v>3</v>
+      </c>
+      <c r="K3" s="7">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7">
+        <v>30</v>
+      </c>
+      <c r="E4" s="7">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C5" s="7">
+        <v>2</v>
+      </c>
+      <c r="D5" s="7">
+        <v>45</v>
+      </c>
+      <c r="E5" s="7">
+        <v>2</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C6" s="7">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7">
+        <v>55</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8">
+        <f>AVERAGE(C3:C6)</f>
+        <v>2.25</v>
+      </c>
+      <c r="D8">
+        <f t="shared" ref="D8:F8" si="0">AVERAGE(D3:D6)</f>
+        <v>45.25</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>1.75</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>1925</v>
+      </c>
+      <c r="H8">
+        <f>AVERAGE(H3:H6)</f>
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <f t="shared" ref="I8:K8" si="1">AVERAGE(I3:I6)</f>
+        <v>45</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10">
+        <f>C3-C$8</f>
+        <v>0.75</v>
+      </c>
+      <c r="D10">
+        <f t="shared" ref="D10:F10" si="2">D3-D$8</f>
+        <v>5.75</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="2"/>
+        <v>1.25</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="2"/>
+        <v>275</v>
+      </c>
+      <c r="H10">
+        <f>H3-H$8</f>
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <f t="shared" ref="I10:K10" si="3">I3-I$8</f>
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <f t="shared" ref="C11:F11" si="4">C4-C$8</f>
+        <v>-1.25</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="4"/>
+        <v>-15.25</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="4"/>
+        <v>-0.75</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="4"/>
+        <v>-325</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C12">
+        <f t="shared" ref="C12:F12" si="5">C5-C$8</f>
+        <v>-0.25</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="5"/>
+        <v>-0.25</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="5"/>
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C13">
+        <f t="shared" ref="C13:F13" si="6">C6-C$8</f>
+        <v>0.75</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="6"/>
+        <v>9.75</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="6"/>
+        <v>-0.75</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="6"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C15">
+        <f>C10^2</f>
+        <v>0.5625</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ref="D15:F15" si="7">D10^2</f>
+        <v>33.0625</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="7"/>
+        <v>1.5625</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="7"/>
+        <v>75625</v>
+      </c>
+      <c r="H15">
+        <f>H10^2</f>
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <f t="shared" ref="I15:K15" si="8">I10^2</f>
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C16">
+        <f t="shared" ref="C16:F16" si="9">C11^2</f>
+        <v>1.5625</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="9"/>
+        <v>232.5625</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="9"/>
+        <v>0.5625</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="9"/>
+        <v>105625</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C17">
+        <f t="shared" ref="C17:F17" si="10">C12^2</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="10"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="10"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="10"/>
+        <v>625</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C18">
+        <f t="shared" ref="C18:F18" si="11">C13^2</f>
+        <v>0.5625</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="11"/>
+        <v>95.0625</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="11"/>
+        <v>0.5625</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="11"/>
+        <v>5625</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C20">
+        <f>SUM(C15:C19)</f>
+        <v>2.75</v>
+      </c>
+      <c r="D20">
+        <f t="shared" ref="D20:F20" si="12">SUM(D15:D19)</f>
+        <v>360.75</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="12"/>
+        <v>2.75</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="12"/>
+        <v>187500</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21">
+        <f>SQRT(C20)</f>
+        <v>1.6583123951776999</v>
+      </c>
+      <c r="D21">
+        <f t="shared" ref="D21:F21" si="13">SQRT(D20)</f>
+        <v>18.993419913222578</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="13"/>
+        <v>1.6583123951776999</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="13"/>
+        <v>433.0127018922193</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="32">
+        <f>C10/C$21</f>
+        <v>0.45226701686664544</v>
+      </c>
+      <c r="D23" s="32">
+        <f t="shared" ref="D23:F23" si="14">D10/D$21</f>
+        <v>0.30273642273327744</v>
+      </c>
+      <c r="E23" s="32">
+        <f t="shared" si="14"/>
+        <v>0.75377836144440902</v>
+      </c>
+      <c r="F23" s="32">
+        <f t="shared" si="14"/>
+        <v>0.63508529610858833</v>
+      </c>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32">
+        <f>C23*$F23</f>
+        <v>0.28722813232690142</v>
+      </c>
+      <c r="I23" s="32">
+        <f t="shared" ref="I23:K23" si="15">D23*$F23</f>
+        <v>0.19226345067441827</v>
+      </c>
+      <c r="J23" s="32">
+        <f t="shared" si="15"/>
+        <v>0.478713553878169</v>
+      </c>
+      <c r="K23" s="32">
+        <f t="shared" si="15"/>
+        <v>0.40333333333333332</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C24" s="32">
+        <f t="shared" ref="C24:F26" si="16">C11/C$21</f>
+        <v>-0.75377836144440902</v>
+      </c>
+      <c r="D24" s="32">
+        <f t="shared" si="16"/>
+        <v>-0.80290964290130107</v>
+      </c>
+      <c r="E24" s="32">
+        <f t="shared" si="16"/>
+        <v>-0.45226701686664544</v>
+      </c>
+      <c r="F24" s="32">
+        <f t="shared" si="16"/>
+        <v>-0.75055534994651352</v>
+      </c>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32">
+        <f t="shared" ref="H24:H26" si="17">C24*$F24</f>
+        <v>0.56575238185601795</v>
+      </c>
+      <c r="I24" s="32">
+        <f t="shared" ref="I24:I26" si="18">D24*$F24</f>
+        <v>0.60262812800321619</v>
+      </c>
+      <c r="J24" s="32">
+        <f t="shared" ref="J24:J26" si="19">E24*$F24</f>
+        <v>0.33945142911361081</v>
+      </c>
+      <c r="K24" s="32">
+        <f t="shared" ref="K24:K26" si="20">F24*$F24</f>
+        <v>0.56333333333333335</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C25" s="32">
+        <f t="shared" si="16"/>
+        <v>-0.15075567228888181</v>
+      </c>
+      <c r="D25" s="32">
+        <f t="shared" si="16"/>
+        <v>-1.316245316231641E-2</v>
+      </c>
+      <c r="E25" s="32">
+        <f t="shared" si="16"/>
+        <v>0.15075567228888181</v>
+      </c>
+      <c r="F25" s="32">
+        <f t="shared" si="16"/>
+        <v>-5.7735026918962581E-2</v>
+      </c>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32">
+        <f t="shared" si="17"/>
+        <v>8.7038827977848933E-3</v>
+      </c>
+      <c r="I25" s="32">
+        <f t="shared" si="18"/>
+        <v>7.5993458764592203E-4</v>
+      </c>
+      <c r="J25" s="32">
+        <f t="shared" si="19"/>
+        <v>-8.7038827977848933E-3</v>
+      </c>
+      <c r="K25" s="32">
+        <f t="shared" si="20"/>
+        <v>3.333333333333334E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C26" s="32">
+        <f t="shared" si="16"/>
+        <v>0.45226701686664544</v>
+      </c>
+      <c r="D26" s="32">
+        <f t="shared" si="16"/>
+        <v>0.51333567333034003</v>
+      </c>
+      <c r="E26" s="32">
+        <f t="shared" si="16"/>
+        <v>-0.45226701686664544</v>
+      </c>
+      <c r="F26" s="32">
+        <f t="shared" si="16"/>
+        <v>0.17320508075688773</v>
+      </c>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32">
+        <f t="shared" si="17"/>
+        <v>7.8334945180064036E-2</v>
+      </c>
+      <c r="I26" s="32">
+        <f t="shared" si="18"/>
+        <v>8.891234675457288E-2</v>
+      </c>
+      <c r="J26" s="32">
+        <f t="shared" si="19"/>
+        <v>-7.8334945180064036E-2</v>
+      </c>
+      <c r="K26" s="32">
+        <f t="shared" si="20"/>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="32">
+        <f>SUM(C23:C27)</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="32">
+        <f t="shared" ref="D28:F28" si="21">SUM(D23:D27)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="32">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="32">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32">
+        <f t="shared" ref="H28" si="22">SUM(H23:H27)</f>
+        <v>0.94001934216076832</v>
+      </c>
+      <c r="I28" s="32">
+        <f t="shared" ref="I28" si="23">SUM(I23:I27)</f>
+        <v>0.88456386001985332</v>
+      </c>
+      <c r="J28" s="32">
+        <f t="shared" ref="J28" si="24">SUM(J23:J27)</f>
+        <v>0.73112615501393097</v>
+      </c>
+      <c r="K28" s="32">
+        <f t="shared" ref="K28" si="25">SUM(K23:K27)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{666D1E91-ED7C-475C-A636-9777A928839D}">
   <dimension ref="A3:O72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6415,7 +6988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82BA3844-AF00-4659-9CA6-FDAA4D3C4028}">
   <dimension ref="A2:T83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8090,7 +8663,7 @@
         <v>0.01</v>
       </c>
       <c r="Q77" t="str">
-        <f t="shared" ref="Q77:Q83" si="34">J77&amp;" &amp; "&amp;K77&amp;" &amp; "&amp;L77&amp;" &amp; "&amp;M77&amp;" &amp; "&amp;N77&amp;" &amp; "&amp;O77</f>
+        <f t="shared" ref="Q77:Q81" si="34">J77&amp;" &amp; "&amp;K77&amp;" &amp; "&amp;L77&amp;" &amp; "&amp;M77&amp;" &amp; "&amp;N77&amp;" &amp; "&amp;O77</f>
         <v>-0.05 &amp; -0.03 &amp; -0.05 &amp; 0.02 &amp; -0.01 &amp; 0.01</v>
       </c>
     </row>

--- a/Edu/Linear_algebra/linal_session_task.xlsx
+++ b/Edu/Linear_algebra/linal_session_task.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LysogorA\DataScience\Edu\Linear_algebra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iTonyJah\DataScience\Edu\Linear_algebra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A692C3-DADE-4900-B0BC-8FD14E0A5956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06E4F92-B9B9-494B-8D85-BF9BD368D0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="1" r:id="rId1"/>
     <sheet name="split1" sheetId="4" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
     <sheet name="st" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="117">
   <si>
     <t>Рабочая таблица с данными:</t>
   </si>
@@ -149,9 +150,6 @@
     <t xml:space="preserve">   =51*93900 + 30*52100 + 45*80200</t>
   </si>
   <si>
-    <t>Итого еще 15 операций или всего 30 операций.</t>
-  </si>
-  <si>
     <t>Способ 2</t>
   </si>
   <si>
@@ -203,9 +201,6 @@
     <t xml:space="preserve">   = 14*2200 + 273*1600 + 14*1900</t>
   </si>
   <si>
-    <t>Итого 15 операций. Всего 60 операций (15+45).</t>
-  </si>
-  <si>
     <t>Первый и второй спсоб перемножения дают нам один и тот же ветор столбец.</t>
   </si>
   <si>
@@ -354,6 +349,98 @@
   </si>
   <si>
     <t>Центральный</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Итого еще 15 операций или </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>всего 30 операций</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Итого 15 операций. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Всего 60 операций</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (15+45).</t>
+    </r>
+  </si>
+  <si>
+    <t>cent</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>cent^2</t>
+  </si>
+  <si>
+    <t>sum</t>
+  </si>
+  <si>
+    <t>sqrt(sum)</t>
+  </si>
+  <si>
+    <t>st1</t>
+  </si>
+  <si>
+    <t>st2</t>
+  </si>
+  <si>
+    <t>sqrt</t>
+  </si>
+  <si>
+    <t>sent_2025_1015_2200</t>
+  </si>
+  <si>
+    <t>sqrt(2)</t>
+  </si>
+  <si>
+    <t>round</t>
+  </si>
+  <si>
+    <t>st1+st2=st_n</t>
   </si>
 </sst>
 </file>
@@ -461,7 +548,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -501,6 +588,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,7 +666,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -617,6 +716,12 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3188,17 +3293,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:AD156"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="25" max="25" width="12.7109375" customWidth="1"/>
+    <col min="25" max="25" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3221,7 +3326,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -3244,7 +3349,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -3267,7 +3372,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -3290,7 +3395,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -3313,7 +3418,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -3336,32 +3441,32 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="23" x14ac:dyDescent="0.5">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -3369,7 +3474,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>3</v>
       </c>
@@ -3383,7 +3488,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
         <v>1</v>
       </c>
@@ -3397,7 +3502,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <v>2</v>
       </c>
@@ -3411,22 +3516,22 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -3434,12 +3539,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -3447,42 +3552,42 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="16" x14ac:dyDescent="0.4">
       <c r="A33" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
         <v>28</v>
       </c>
@@ -3493,7 +3598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <f>F38*J$38+G38*J$39+H38*J$40</f>
         <v>93900</v>
@@ -3515,7 +3620,7 @@
       </c>
       <c r="L38" s="8"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="7">
         <f t="shared" ref="A39:A40" si="0">F39*J$38+G39*J$39+H39*J$40</f>
         <v>52100</v>
@@ -3537,7 +3642,7 @@
       </c>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <f t="shared" si="0"/>
         <v>80200</v>
@@ -3559,23 +3664,23 @@
       </c>
       <c r="L40" s="8"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B41" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="J43" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="12">
         <f>F44*J$44+G44*J$45+H44*J$46</f>
         <v>494200</v>
@@ -3597,7 +3702,7 @@
       </c>
       <c r="L44" s="8"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="12">
         <f t="shared" ref="A45:A46" si="1">F45*J$44+G45*J$45+H45*J$46</f>
         <v>9960900</v>
@@ -3619,7 +3724,7 @@
       </c>
       <c r="L45" s="8"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="12">
         <f t="shared" si="1"/>
         <v>494200</v>
@@ -3641,30 +3746,30 @@
       </c>
       <c r="L46" s="8"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B47" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A48" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B50" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
@@ -3696,7 +3801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="12">
         <f t="shared" ref="A52:A53" si="4">$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
@@ -3728,7 +3833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="12">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -3760,118 +3865,118 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>37</v>
+      </c>
+      <c r="E55" t="s">
         <v>38</v>
       </c>
-      <c r="E55" t="s">
-        <v>39</v>
-      </c>
       <c r="I55" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="12">
         <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
         <v>14</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E56" s="12">
         <f>$F51*K$51+$G51*K$52+$H51*K$53</f>
         <v>273</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I56" s="12">
         <f>$F51*L$51+$G51*L$52+$H51*L$53</f>
         <v>14</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="12">
         <f>$F52*J$51+$G52*J$52+$H52*J$53</f>
         <v>273</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E57" s="12">
         <f>$F52*K$51+$G52*K$52+$H52*K$53</f>
         <v>5526</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I57" s="12">
         <f>$F52*L$51+$G52*L$52+$H52*L$53</f>
         <v>273</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="12">
         <f>$F53*J$51+$G53*J$52+$H53*J$53</f>
         <v>14</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E58" s="12">
         <f>$F53*K$51+$G53*K$52+$H53*K$53</f>
         <v>273</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I58" s="12">
         <f>$F53*L$51+$G53*L$52+$H53*L$53</f>
         <v>14</v>
       </c>
       <c r="J58" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B59" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B59" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G61" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J61" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="12">
         <f>F62*J$62+G62*J$63+H62*J$64</f>
         <v>494200</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F62" s="12">
         <v>14</v>
@@ -3886,13 +3991,13 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="12">
         <f t="shared" ref="A63:A64" si="5">F63*J$62+G63*J$63+H63*J$64</f>
         <v>9960900</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F63" s="12">
         <v>273</v>
@@ -3907,13 +4012,13 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="12">
         <f t="shared" si="5"/>
         <v>494200</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F64" s="12">
         <v>14</v>
@@ -3928,117 +4033,117 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B65" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B67" s="8"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C68" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="12">
         <v>494200</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
         <v>9960900</v>
       </c>
       <c r="C70" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="12">
         <v>494200</v>
       </c>
       <c r="C71" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="23.25" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="23" x14ac:dyDescent="0.35">
       <c r="A74" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>1</v>
       </c>
@@ -4061,19 +4166,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C90" s="16"/>
       <c r="D90" s="16"/>
       <c r="E90" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F90" s="16"/>
       <c r="G90" s="16"/>
       <c r="I90" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B91" s="7">
         <v>3</v>
       </c>
@@ -4096,7 +4201,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B92" s="7">
         <v>1</v>
       </c>
@@ -4119,7 +4224,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B93" s="7">
         <v>2</v>
       </c>
@@ -4142,7 +4247,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B94" s="7">
         <v>3</v>
       </c>
@@ -4165,7 +4270,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B95" s="7">
         <v>1</v>
       </c>
@@ -4188,19 +4293,19 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A97" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="98" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="99" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>76</v>
       </c>
       <c r="B99">
         <f>SUM(B91:B95)</f>
@@ -4241,9 +4346,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B100">
         <f>B99/5</f>
@@ -4278,9 +4383,9 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="S101">
         <f>S100^2</f>
@@ -4295,7 +4400,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B102" s="7">
         <f>B91-B$100</f>
         <v>1</v>
@@ -4333,13 +4438,13 @@
         <v>15.491933384829668</v>
       </c>
       <c r="M102" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Z102">
         <v>2255</v>
       </c>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B103" s="7">
         <f t="shared" ref="B103:G103" si="10">B92-B$100</f>
         <v>-1</v>
@@ -4389,7 +4494,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B104" s="7">
         <f t="shared" ref="B104:G104" si="14">B93-B$100</f>
         <v>0</v>
@@ -4441,7 +4546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B105" s="7">
         <f t="shared" ref="B105:G105" si="16">B94-B$100</f>
         <v>1</v>
@@ -4493,7 +4598,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B106" s="7">
         <f t="shared" ref="B106:G106" si="19">B95-B$100</f>
         <v>-1</v>
@@ -4541,9 +4646,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J107" s="19">
         <f>SUM(J102:J106)</f>
@@ -4587,9 +4692,9 @@
         <v>0.99972295331231709</v>
       </c>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M108">
         <v>1</v>
@@ -4616,7 +4721,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B109">
         <f>(B102^2+B103^2+B104^2+B105^2+B106^2)^(1/2)</f>
         <v>2</v>
@@ -4675,9 +4780,9 @@
         <v>18.994736112934024</v>
       </c>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="X110" s="17">
         <f>X109-X108</f>
@@ -4688,7 +4793,7 @@
         <v>8.9554452708952432</v>
       </c>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B111" s="18">
         <f>B102/B$109</f>
         <v>0.5</v>
@@ -4716,7 +4821,7 @@
         <v>-0.10241085157359611</v>
       </c>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B112" s="18">
         <f t="shared" ref="B112:I115" si="23">B103/B$109</f>
         <v>-0.5</v>
@@ -4744,7 +4849,7 @@
         <v>-0.35843798050758635</v>
       </c>
       <c r="N112" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="Y112">
         <v>4</v>
@@ -4762,7 +4867,7 @@
         <v>1.7888543819998317</v>
       </c>
     </row>
-    <row r="113" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B113" s="18">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -4820,7 +4925,7 @@
         <v>0.89442719099991586</v>
       </c>
     </row>
-    <row r="114" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B114" s="18">
         <f t="shared" si="23"/>
         <v>0.5</v>
@@ -4883,7 +4988,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="115" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B115" s="18">
         <f t="shared" si="23"/>
         <v>-0.5</v>
@@ -4942,9 +5047,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="117" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:29" x14ac:dyDescent="0.35">
       <c r="Z117" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AA117">
         <f>90-14</f>
@@ -4955,7 +5060,7 @@
         <v>8.717797887081348</v>
       </c>
     </row>
-    <row r="118" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:29" x14ac:dyDescent="0.35">
       <c r="L118">
         <f>51/5</f>
         <v>10.199999999999999</v>
@@ -4994,7 +5099,7 @@
         <v>1.7888543819998317</v>
       </c>
       <c r="Z118" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AA118">
         <f>90+14</f>
@@ -5005,12 +5110,12 @@
         <v>10.198039027185569</v>
       </c>
     </row>
-    <row r="120" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:29" x14ac:dyDescent="0.35">
       <c r="H120">
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:29" x14ac:dyDescent="0.35">
       <c r="H121">
         <v>5</v>
       </c>
@@ -5019,7 +5124,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="122" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:29" x14ac:dyDescent="0.35">
       <c r="H122">
         <v>10</v>
       </c>
@@ -5030,7 +5135,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F123">
         <v>-240</v>
       </c>
@@ -5059,7 +5164,7 @@
         <v>240</v>
       </c>
       <c r="N123" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="P123">
         <f>G123/10/2</f>
@@ -5070,7 +5175,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="124" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F124">
         <v>-840</v>
       </c>
@@ -5099,7 +5204,7 @@
         <v>840</v>
       </c>
       <c r="N124" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P124">
         <f>G124/10/2</f>
@@ -5110,7 +5215,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="125" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F125">
         <v>-540</v>
       </c>
@@ -5135,7 +5240,7 @@
         <v>540</v>
       </c>
       <c r="N125" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="P125">
         <f>G125/10/2</f>
@@ -5146,7 +5251,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="126" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F126">
         <v>-440</v>
       </c>
@@ -5175,7 +5280,7 @@
         <v>440</v>
       </c>
       <c r="N126" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="P126">
         <f>G126/10/2</f>
@@ -5186,7 +5291,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="127" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:29" x14ac:dyDescent="0.35">
       <c r="F127">
         <v>2060</v>
       </c>
@@ -5211,7 +5316,7 @@
         <v>2060</v>
       </c>
       <c r="N127" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P127">
         <f>G127/10/2</f>
@@ -5222,7 +5327,7 @@
         <v>10609</v>
       </c>
     </row>
-    <row r="128" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:29" x14ac:dyDescent="0.35">
       <c r="W128">
         <v>2</v>
       </c>
@@ -5231,7 +5336,7 @@
         <v>1.4142135623730951</v>
       </c>
     </row>
-    <row r="129" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="129" spans="5:24" x14ac:dyDescent="0.35">
       <c r="J129">
         <f>SUM(J123:J128)</f>
         <v>13730</v>
@@ -5252,7 +5357,7 @@
         <v>1.7320508075688772</v>
       </c>
     </row>
-    <row r="130" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="130" spans="5:24" x14ac:dyDescent="0.35">
       <c r="J130">
         <f>SQRT(J129)</f>
         <v>117.17508267545622</v>
@@ -5266,7 +5371,7 @@
         <v>117.17508267545622</v>
       </c>
     </row>
-    <row r="131" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="131" spans="5:24" x14ac:dyDescent="0.35">
       <c r="W131">
         <f>W128/W129</f>
         <v>0.66666666666666663</v>
@@ -5276,7 +5381,7 @@
         <v>0.81649658092772615</v>
       </c>
     </row>
-    <row r="132" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="132" spans="5:24" x14ac:dyDescent="0.35">
       <c r="F132">
         <f>G132*H132</f>
         <v>117</v>
@@ -5322,7 +5427,7 @@
         <v>0.81649658092772603</v>
       </c>
     </row>
-    <row r="133" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="133" spans="5:24" x14ac:dyDescent="0.35">
       <c r="I133">
         <f>I132*20</f>
         <v>2340</v>
@@ -5332,7 +5437,7 @@
         <v>-41</v>
       </c>
     </row>
-    <row r="135" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="135" spans="5:24" x14ac:dyDescent="0.35">
       <c r="H135">
         <f>I135/2</f>
         <v>59</v>
@@ -5357,13 +5462,13 @@
         <v>13.857142857142858</v>
       </c>
     </row>
-    <row r="136" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="136" spans="5:24" x14ac:dyDescent="0.35">
       <c r="I136">
         <f>I135*20</f>
         <v>2360</v>
       </c>
     </row>
-    <row r="139" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="139" spans="5:24" x14ac:dyDescent="0.35">
       <c r="E139">
         <v>19</v>
       </c>
@@ -5382,7 +5487,7 @@
         <v>94.973680564670133</v>
       </c>
     </row>
-    <row r="140" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="140" spans="5:24" x14ac:dyDescent="0.35">
       <c r="F140">
         <v>1805</v>
       </c>
@@ -5394,13 +5499,13 @@
         <v>24010</v>
       </c>
     </row>
-    <row r="141" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="141" spans="5:24" x14ac:dyDescent="0.35">
       <c r="J141">
         <f>J139/J140</f>
         <v>360.8</v>
       </c>
     </row>
-    <row r="142" spans="5:24" x14ac:dyDescent="0.25">
+    <row r="142" spans="5:24" x14ac:dyDescent="0.35">
       <c r="M142">
         <v>7</v>
       </c>
@@ -5413,12 +5518,12 @@
         <v>2401</v>
       </c>
     </row>
-    <row r="148" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:7" x14ac:dyDescent="0.35">
       <c r="D148">
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:7" x14ac:dyDescent="0.35">
       <c r="D149">
         <v>5</v>
       </c>
@@ -5427,7 +5532,7 @@
         <v>2.2360679774997898</v>
       </c>
     </row>
-    <row r="150" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:7" x14ac:dyDescent="0.35">
       <c r="D150">
         <f>D148/D149</f>
         <v>0.4</v>
@@ -5437,23 +5542,23 @@
         <v>0.89442719099991597</v>
       </c>
     </row>
-    <row r="151" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C151">
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C152">
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C153">
         <f>C151/C152</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="154" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C154">
         <f>SQRT(C153)</f>
         <v>0.89442719099991586</v>
@@ -5462,7 +5567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="155" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:7" x14ac:dyDescent="0.35">
       <c r="E155">
         <f>SQRT(E154)</f>
         <v>4.4721359549995796</v>
@@ -5471,7 +5576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:7" x14ac:dyDescent="0.35">
       <c r="G156">
         <f>G155/E155</f>
         <v>0.22360679774997896</v>
@@ -5487,11 +5592,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{187E156B-4495-4400-8873-A45B82A27CF2}">
   <dimension ref="B1:L28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -5506,15 +5611,15 @@
         <v>7</v>
       </c>
       <c r="L1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
       <c r="D2" s="16"/>
       <c r="E2" s="16"/>
       <c r="F2" s="9"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C3" s="7">
         <v>3</v>
       </c>
@@ -5540,7 +5645,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C4" s="7">
         <v>1</v>
       </c>
@@ -5554,7 +5659,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C5" s="7">
         <v>2</v>
       </c>
@@ -5568,7 +5673,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C6" s="7">
         <v>3</v>
       </c>
@@ -5582,9 +5687,9 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C8">
         <f>AVERAGE(C3:C6)</f>
@@ -5619,9 +5724,9 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C10">
         <f>C3-C$8</f>
@@ -5656,7 +5761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C11">
         <f t="shared" ref="C11:F11" si="4">C4-C$8</f>
         <v>-1.25</v>
@@ -5674,7 +5779,7 @@
         <v>-325</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C12">
         <f t="shared" ref="C12:F12" si="5">C5-C$8</f>
         <v>-0.25</v>
@@ -5692,7 +5797,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C13">
         <f t="shared" ref="C13:F13" si="6">C6-C$8</f>
         <v>0.75</v>
@@ -5710,7 +5815,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C15">
         <f>C10^2</f>
         <v>0.5625</v>
@@ -5744,7 +5849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C16">
         <f t="shared" ref="C16:F16" si="9">C11^2</f>
         <v>1.5625</v>
@@ -5762,7 +5867,7 @@
         <v>105625</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="C17">
         <f t="shared" ref="C17:F17" si="10">C12^2</f>
         <v>6.25E-2</v>
@@ -5780,7 +5885,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
       <c r="C18">
         <f t="shared" ref="C18:F18" si="11">C13^2</f>
         <v>0.5625</v>
@@ -5798,7 +5903,7 @@
         <v>5625</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
       <c r="C20">
         <f>SUM(C15:C19)</f>
         <v>2.75</v>
@@ -5816,9 +5921,9 @@
         <v>187500</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C21">
         <f>SQRT(C20)</f>
@@ -5837,9 +5942,9 @@
         <v>433.0127018922193</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C23" s="32">
         <f>C10/C$21</f>
@@ -5875,7 +5980,7 @@
         <v>0.40333333333333332</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
       <c r="C24" s="32">
         <f t="shared" ref="C24:F26" si="16">C11/C$21</f>
         <v>-0.75377836144440902</v>
@@ -5910,7 +6015,7 @@
         <v>0.56333333333333335</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.35">
       <c r="C25" s="32">
         <f t="shared" si="16"/>
         <v>-0.15075567228888181</v>
@@ -5945,7 +6050,7 @@
         <v>3.333333333333334E-3</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.35">
       <c r="C26" s="32">
         <f t="shared" si="16"/>
         <v>0.45226701686664544</v>
@@ -5980,7 +6085,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
       <c r="C27" s="32"/>
       <c r="D27" s="32"/>
       <c r="E27" s="32"/>
@@ -5991,9 +6096,9 @@
       <c r="J27" s="32"/>
       <c r="K27" s="32"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C28" s="32">
         <f>SUM(C23:C27)</f>
@@ -6037,9 +6142,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{666D1E91-ED7C-475C-A636-9777A928839D}">
   <dimension ref="A3:O72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -6066,7 +6171,7 @@
         <v>1.4310835055998654</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -6093,7 +6198,7 @@
         <v>1.4310835055998654</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B13">
         <f t="shared" ref="B13" si="4">B14-1</f>
         <v>1</v>
@@ -6107,7 +6212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14">
         <f t="shared" ref="B14:B15" si="7">B15-1</f>
         <v>2</v>
@@ -6121,7 +6226,7 @@
         <v>0.70710678118654757</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15">
         <f t="shared" si="7"/>
         <v>3</v>
@@ -6135,7 +6240,7 @@
         <v>0.57735026918962573</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16">
         <f>B17-1</f>
         <v>4</v>
@@ -6149,7 +6254,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>5</v>
       </c>
@@ -6162,7 +6267,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18">
         <f>B17+1</f>
         <v>6</v>
@@ -6176,7 +6281,7 @@
         <v>0.40824829046386296</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19">
         <f t="shared" ref="B19:B27" si="11">B18+1</f>
         <v>7</v>
@@ -6190,7 +6295,7 @@
         <v>0.37796447300922725</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20">
         <f t="shared" si="11"/>
         <v>8</v>
@@ -6204,7 +6309,7 @@
         <v>0.35355339059327379</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21">
         <f t="shared" si="11"/>
         <v>9</v>
@@ -6218,7 +6323,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22">
         <f t="shared" si="11"/>
         <v>10</v>
@@ -6232,7 +6337,7 @@
         <v>0.31622776601683794</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23">
         <f t="shared" si="11"/>
         <v>11</v>
@@ -6246,7 +6351,7 @@
         <v>0.30151134457776363</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24">
         <f t="shared" si="11"/>
         <v>12</v>
@@ -6260,7 +6365,7 @@
         <v>0.28867513459481287</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25">
         <f t="shared" si="11"/>
         <v>13</v>
@@ -6274,7 +6379,7 @@
         <v>0.27735009811261457</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26">
         <f t="shared" si="11"/>
         <v>14</v>
@@ -6288,7 +6393,7 @@
         <v>0.2672612419124244</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27">
         <f t="shared" si="11"/>
         <v>15</v>
@@ -6302,7 +6407,7 @@
         <v>0.25819888974716115</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28">
         <f t="shared" ref="B28:B58" si="12">B27+1</f>
         <v>16</v>
@@ -6316,7 +6421,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29">
         <f t="shared" si="12"/>
         <v>17</v>
@@ -6330,7 +6435,7 @@
         <v>0.24253562503633297</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30">
         <f t="shared" si="12"/>
         <v>18</v>
@@ -6344,7 +6449,7 @@
         <v>0.23570226039551581</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31">
         <f t="shared" si="12"/>
         <v>19</v>
@@ -6358,7 +6463,7 @@
         <v>0.2294157338705618</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32">
         <f t="shared" si="12"/>
         <v>20</v>
@@ -6372,7 +6477,7 @@
         <v>0.22360679774997899</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33">
         <f t="shared" si="12"/>
         <v>21</v>
@@ -6386,7 +6491,7 @@
         <v>0.21821789023599236</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34">
         <f t="shared" si="12"/>
         <v>22</v>
@@ -6400,7 +6505,7 @@
         <v>0.21320071635561044</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35">
         <f t="shared" si="12"/>
         <v>23</v>
@@ -6414,7 +6519,7 @@
         <v>0.20851441405707474</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B36">
         <f t="shared" si="12"/>
         <v>24</v>
@@ -6435,7 +6540,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B37">
         <f t="shared" si="12"/>
         <v>25</v>
@@ -6464,7 +6569,7 @@
         <v>1.1180339887498949</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B38">
         <f t="shared" si="12"/>
         <v>26</v>
@@ -6486,7 +6591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B39">
         <f t="shared" si="12"/>
         <v>27</v>
@@ -6519,7 +6624,7 @@
         <v>1.1180339887498949</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B40">
         <f t="shared" si="12"/>
         <v>28</v>
@@ -6536,7 +6641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B41">
         <f t="shared" si="12"/>
         <v>29</v>
@@ -6575,7 +6680,7 @@
         <v>0.22360679774997899</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B42">
         <f t="shared" si="12"/>
         <v>30</v>
@@ -6597,7 +6702,7 @@
         <v>0.1118033988749895</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43">
         <f t="shared" si="12"/>
         <v>31</v>
@@ -6611,7 +6716,7 @@
         <v>0.17960530202677488</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B44">
         <f t="shared" si="12"/>
         <v>32</v>
@@ -6631,10 +6736,10 @@
         <v>2</v>
       </c>
       <c r="O44" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B45">
         <f t="shared" si="12"/>
         <v>33</v>
@@ -6681,7 +6786,7 @@
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B46">
         <f t="shared" si="12"/>
         <v>34</v>
@@ -6695,7 +6800,7 @@
         <v>0.17149858514250885</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B47">
         <f t="shared" si="12"/>
         <v>35</v>
@@ -6712,7 +6817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B48">
         <f t="shared" si="12"/>
         <v>36</v>
@@ -6733,7 +6838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B49">
         <f t="shared" si="12"/>
         <v>37</v>
@@ -6753,7 +6858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B50">
         <f t="shared" si="12"/>
         <v>38</v>
@@ -6771,7 +6876,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B51">
         <f t="shared" si="12"/>
         <v>39</v>
@@ -6789,7 +6894,7 @@
         <v>1.1180339887498949</v>
       </c>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B52">
         <f t="shared" si="12"/>
         <v>40</v>
@@ -6806,7 +6911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B53">
         <f t="shared" si="12"/>
         <v>41</v>
@@ -6831,7 +6936,7 @@
         <v>0.1118033988749895</v>
       </c>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B54">
         <f t="shared" si="12"/>
         <v>42</v>
@@ -6848,7 +6953,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B55">
         <f t="shared" si="12"/>
         <v>43</v>
@@ -6866,7 +6971,7 @@
         <v>22.360679774997898</v>
       </c>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B56">
         <f t="shared" si="12"/>
         <v>44</v>
@@ -6883,7 +6988,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B57">
         <f t="shared" si="12"/>
         <v>45</v>
@@ -6901,7 +7006,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B58">
         <f t="shared" si="12"/>
         <v>46</v>
@@ -6915,28 +7020,28 @@
         <v>0.14744195615489714</v>
       </c>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
       <c r="F60">
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
       <c r="F61">
         <f>SQRT(F60)</f>
         <v>2.8284271247461903</v>
       </c>
     </row>
-    <row r="66" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:10" x14ac:dyDescent="0.35">
       <c r="G66">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:10" x14ac:dyDescent="0.35">
       <c r="G67">
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F68">
         <v>2</v>
       </c>
@@ -6951,7 +7056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:10" x14ac:dyDescent="0.35">
       <c r="H69">
         <f>H68/G68</f>
         <v>0.55901699437494745</v>
@@ -6965,12 +7070,12 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="71" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F71">
         <v>80</v>
       </c>
     </row>
-    <row r="72" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F72">
         <f>SQRT(F71)</f>
         <v>8.9442719099991592</v>
@@ -6991,25 +7096,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82BA3844-AF00-4659-9CA6-FDAA4D3C4028}">
   <dimension ref="A2:T83"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K2">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K4">
         <f>K2/K3</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="J5">
         <v>2</v>
       </c>
@@ -7018,7 +7123,7 @@
         <v>0.89442719099991586</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="J6">
         <v>1</v>
       </c>
@@ -7027,7 +7132,7 @@
         <v>1.7888543819998317</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="E7">
         <v>1</v>
       </c>
@@ -7043,7 +7148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="E8">
         <v>1804</v>
       </c>
@@ -7055,7 +7160,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B9" t="str">
         <f>C17</f>
         <v>x_1</v>
@@ -7087,7 +7192,7 @@
         <v>y</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="E10">
         <f>SQRT(E8/E9)</f>
         <v>0.99972295331231709</v>
@@ -7102,7 +7207,7 @@
         <v>13689</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1</v>
       </c>
@@ -7165,7 +7270,7 @@
         <v>-0.10241085157359613</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2</v>
       </c>
@@ -7231,7 +7336,7 @@
         <v>-0.35843798050758646</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="20">
         <f>A11/A12</f>
         <v>0.5</v>
@@ -7299,7 +7404,7 @@
         <v>-0.23042441604059127</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B14" s="7">
         <v>1</v>
       </c>
@@ -7343,7 +7448,7 @@
         <v>-0.18775322788492624</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B15" s="7">
         <v>-1</v>
       </c>
@@ -7387,27 +7492,27 @@
         <v>0.87902647600670003</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" t="s">
         <v>92</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>93</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>94</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" t="s">
         <v>95</v>
       </c>
-      <c r="G17" t="s">
-        <v>96</v>
-      </c>
-      <c r="H17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C19" s="24">
         <f>C11</f>
         <v>0.5</v>
@@ -7433,7 +7538,7 @@
         <v>-0.10241085157359613</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C20" s="24">
         <f t="shared" ref="C20:C23" si="6">C12</f>
         <v>-0.5</v>
@@ -7459,7 +7564,7 @@
         <v>-0.35843798050758646</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C21" s="24">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -7485,7 +7590,7 @@
         <v>-0.23042441604059127</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C22" s="24">
         <f t="shared" si="6"/>
         <v>0.5</v>
@@ -7511,7 +7616,7 @@
         <v>-0.18775322788492624</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C23" s="24">
         <f t="shared" si="6"/>
         <v>-0.5</v>
@@ -7537,7 +7642,7 @@
         <v>0.87902647600670003</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C24" s="22"/>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -7553,7 +7658,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C25" s="22">
         <f>SUM(C19:C24)</f>
         <v>0</v>
@@ -7579,13 +7684,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="R26">
         <f>4/5</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" s="26">
         <v>4</v>
       </c>
@@ -7622,7 +7727,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C28" s="28">
         <f t="shared" ref="C28:H28" si="14">ROUND(C20,$A$27)</f>
         <v>-0.5</v>
@@ -7652,7 +7757,7 @@
         <v>-0,5 &amp; -0,8002 &amp; -0,5 &amp; -0,2236 &amp; 0,1118 &amp; -0,3584 \\</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C29" s="28">
         <f t="shared" ref="C29:H29" si="16">ROUND(C21,$A$27)</f>
         <v>0</v>
@@ -7682,7 +7787,7 @@
         <v>0 &amp; -0,0105 &amp; 0 &amp; -0,2236 &amp; 0,1118 &amp; -0,2304 \\</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C30" s="28">
         <f t="shared" ref="C30:H30" si="17">ROUND(C22,$A$27)</f>
         <v>0.5</v>
@@ -7712,7 +7817,7 @@
         <v>0,5 &amp; 0,5159 &amp; -0,5 &amp; -0,2236 &amp; 0,1118 &amp; -0,1878 \\</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C31" s="28">
         <f t="shared" ref="C31:H31" si="18">ROUND(C23,$A$27)</f>
         <v>-0.5</v>
@@ -7742,7 +7847,7 @@
         <v>-0,5 &amp; -0,0105 &amp; 0,5 &amp; 0,8944 &amp; -0,4472 &amp; 0,879 \\</v>
       </c>
     </row>
-    <row r="33" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C33" s="27">
         <f>SUM(C27:C32)</f>
         <v>0</v>
@@ -7783,7 +7888,7 @@
         <v>3.5714285714285705E-2</v>
       </c>
     </row>
-    <row r="34" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:20" x14ac:dyDescent="0.35">
       <c r="Q34">
         <v>2</v>
       </c>
@@ -7800,7 +7905,7 @@
         <v>0.14285714285714282</v>
       </c>
     </row>
-    <row r="35" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C35" s="25"/>
       <c r="I35" s="30">
         <v>-0.1024</v>
@@ -7833,7 +7938,7 @@
         <v>0.32142857142857145</v>
       </c>
     </row>
-    <row r="36" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C36" s="30">
         <v>0.5</v>
       </c>
@@ -7872,7 +7977,7 @@
         <v>3.5714285714285705E-2</v>
       </c>
     </row>
-    <row r="37" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C37" s="30">
         <v>-0.5</v>
       </c>
@@ -7911,7 +8016,7 @@
         <v>0.14285714285714282</v>
       </c>
     </row>
-    <row r="38" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C38" s="30">
         <v>0</v>
       </c>
@@ -7950,7 +8055,7 @@
         <v>0.32142857142857145</v>
       </c>
     </row>
-    <row r="39" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C39" s="30">
         <v>0.5</v>
       </c>
@@ -7974,7 +8079,7 @@
         <v>-9.3899999999999997E-2</v>
       </c>
     </row>
-    <row r="40" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C40" s="30">
         <v>-0.5</v>
       </c>
@@ -8010,13 +8115,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:20" x14ac:dyDescent="0.35">
       <c r="R41">
         <f>SQRT(R40)</f>
         <v>5.2915026221291814</v>
       </c>
     </row>
-    <row r="43" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C43" s="30">
         <v>0.5</v>
       </c>
@@ -8037,7 +8142,7 @@
         <v>0,5 \\ -0,5 \\ 0 \\ 0,5 \\ -0,5</v>
       </c>
     </row>
-    <row r="44" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C44" s="30">
         <v>0.30530000000000002</v>
       </c>
@@ -8054,7 +8159,7 @@
         <v>-1.0500000000000001E-2</v>
       </c>
     </row>
-    <row r="45" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C45" s="30">
         <v>0.5</v>
       </c>
@@ -8071,7 +8176,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C46" s="30">
         <v>-0.22359999999999999</v>
       </c>
@@ -8088,7 +8193,7 @@
         <v>0.89439999999999997</v>
       </c>
     </row>
-    <row r="47" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C47" s="30">
         <v>0.1118</v>
       </c>
@@ -8105,7 +8210,7 @@
         <v>-0.44719999999999999</v>
       </c>
     </row>
-    <row r="48" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C48" s="30">
         <v>-0.1024</v>
       </c>
@@ -8126,7 +8231,7 @@
         <v>-0,1024 &amp; -0,3584 &amp; -0,2304 &amp; -0,1878 &amp; 0,879</v>
       </c>
     </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C51" s="25"/>
       <c r="I51" s="30"/>
       <c r="J51" s="30"/>
@@ -8134,7 +8239,7 @@
       <c r="L51" s="30"/>
       <c r="M51" s="30"/>
     </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C52" s="30">
         <v>0.5</v>
       </c>
@@ -8158,7 +8263,7 @@
         <v>0,3053 &amp; -0,1024 \\</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C53" s="30">
         <v>-0.5</v>
       </c>
@@ -8182,7 +8287,7 @@
         <v>-0,8002 &amp; -0,3584 \\</v>
       </c>
     </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C54" s="30">
         <v>0</v>
       </c>
@@ -8206,7 +8311,7 @@
         <v>-0,0105 &amp; -0,2304 \\</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C55" s="30">
         <v>0.5</v>
       </c>
@@ -8230,7 +8335,7 @@
         <v>0,5159 &amp; -0,1878 \\</v>
       </c>
     </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C56" s="30">
         <v>-0.5</v>
       </c>
@@ -8254,7 +8359,7 @@
         <v>-0,0105 &amp; 0,879 \\</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C59" s="30">
         <v>0.5</v>
       </c>
@@ -8275,7 +8380,7 @@
         <v>0,5 \\ -0,5 \\ 0 \\ 0,5 \\ -0,5</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C60" s="30">
         <v>0.30530000000000002</v>
       </c>
@@ -8296,7 +8401,7 @@
         <v>0,3053 &amp; -0,8002 &amp; -0,0105 &amp; 0,5159 &amp; -0,0105</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C61" s="30">
         <v>0.5</v>
       </c>
@@ -8313,7 +8418,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C62" s="30">
         <v>-0.22359999999999999</v>
       </c>
@@ -8330,7 +8435,7 @@
         <v>0.89439999999999997</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C63" s="30">
         <v>0.1118</v>
       </c>
@@ -8347,7 +8452,7 @@
         <v>-0.44719999999999999</v>
       </c>
     </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C64" s="30">
         <v>-0.1024</v>
       </c>
@@ -8368,7 +8473,7 @@
         <v>-0,1024 &amp; -0,3584 &amp; -0,2304 &amp; -0,1878 &amp; 0,879</v>
       </c>
     </row>
-    <row r="69" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C69" s="11">
         <v>0.5</v>
       </c>
@@ -8416,7 +8521,7 @@
         <v>-0.0512054257867981 &amp; -0.0312709234598105 &amp; -0.0512054257867981 &amp; 0.0228997625752202 &amp; -0.0114498812876101 &amp; 0.0104879825200291</v>
       </c>
     </row>
-    <row r="70" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C70" s="11">
         <v>-0.5</v>
       </c>
@@ -8464,7 +8569,7 @@
         <v>0.179218990253793 &amp; 0.286829849665848 &amp; 0.179218990253793 &amp; 0.0801491690132708 &amp; -0.0400745845066354 &amp; 0.128477785870357</v>
       </c>
     </row>
-    <row r="71" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C71" s="11">
         <v>0</v>
       </c>
@@ -8512,7 +8617,7 @@
         <v>0 &amp; 0.00242619233739909 &amp; 0 &amp; 0.0515244657942455 &amp; -0.0257622328971228 &amp; 0.0530954115076475</v>
       </c>
     </row>
-    <row r="72" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C72" s="11">
         <v>0.5</v>
       </c>
@@ -8560,7 +8665,7 @@
         <v>-0.0938766139424631 &amp; -0.0968679755450451 &amp; 0.0938766139424631 &amp; 0.0419828980545704 &amp; -0.0209914490272852 &amp; 0.035251274581209</v>
       </c>
     </row>
-    <row r="73" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C73" s="11">
         <v>-0.5</v>
       </c>
@@ -8608,7 +8713,7 @@
         <v>-0.43951323800335 &amp; -0.00925547447230022 &amp; 0.43951323800335 &amp; 0.786225181749228 &amp; -0.393112590874614 &amp; 0.772687545520758</v>
       </c>
     </row>
-    <row r="75" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:17" x14ac:dyDescent="0.35">
       <c r="J75">
         <f>SUM(J69:J74)</f>
         <v>-0.40537628747881799</v>
@@ -8634,7 +8739,7 @@
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="77" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:17" x14ac:dyDescent="0.35">
       <c r="I77" s="26">
         <v>2</v>
       </c>
@@ -8667,7 +8772,7 @@
         <v>-0.05 &amp; -0.03 &amp; -0.05 &amp; 0.02 &amp; -0.01 &amp; 0.01</v>
       </c>
     </row>
-    <row r="78" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:17" x14ac:dyDescent="0.35">
       <c r="J78">
         <f t="shared" ref="J78:O78" si="35">ROUND(J70,$I$77)</f>
         <v>0.18</v>
@@ -8697,7 +8802,7 @@
         <v>0.18 &amp; 0.29 &amp; 0.18 &amp; 0.08 &amp; -0.04 &amp; 0.13</v>
       </c>
     </row>
-    <row r="79" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:17" x14ac:dyDescent="0.35">
       <c r="J79">
         <f t="shared" ref="J79:O79" si="36">ROUND(J71,$I$77)</f>
         <v>0</v>
@@ -8727,7 +8832,7 @@
         <v>0 &amp; 0 &amp; 0 &amp; 0.05 &amp; -0.03 &amp; 0.05</v>
       </c>
     </row>
-    <row r="80" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:17" x14ac:dyDescent="0.35">
       <c r="J80">
         <f t="shared" ref="J80:O80" si="37">ROUND(J72,$I$77)</f>
         <v>-0.09</v>
@@ -8757,7 +8862,7 @@
         <v>-0.09 &amp; -0.1 &amp; 0.09 &amp; 0.04 &amp; -0.02 &amp; 0.04</v>
       </c>
     </row>
-    <row r="81" spans="10:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="10:17" x14ac:dyDescent="0.35">
       <c r="J81">
         <f t="shared" ref="J81:O81" si="38">ROUND(J73,$I$77)</f>
         <v>-0.44</v>
@@ -8787,7 +8892,7 @@
         <v>-0.44 &amp; -0.01 &amp; 0.44 &amp; 0.79 &amp; -0.39 &amp; 0.77</v>
       </c>
     </row>
-    <row r="83" spans="10:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="10:17" x14ac:dyDescent="0.35">
       <c r="J83">
         <f>SUM(J77:J82)</f>
         <v>-0.4</v>
@@ -8821,4 +8926,494 @@
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{654E3EDC-9DB6-4DEA-B3D0-692910FDD27A}">
+  <dimension ref="G2:Z21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="17" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="7:26" x14ac:dyDescent="0.35">
+      <c r="U2" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+    </row>
+    <row r="3" spans="7:26" x14ac:dyDescent="0.35">
+      <c r="P3" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>105</v>
+      </c>
+      <c r="R3" t="s">
+        <v>107</v>
+      </c>
+      <c r="S3" t="s">
+        <v>110</v>
+      </c>
+      <c r="U3" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="V3" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="W3" s="26"/>
+      <c r="Y3" s="33"/>
+      <c r="Z3" s="33" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="7:26" x14ac:dyDescent="0.35">
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <f>AVERAGE(O4:O7)</f>
+        <v>1.25</v>
+      </c>
+      <c r="Q4">
+        <f>O4-P4</f>
+        <v>-0.25</v>
+      </c>
+      <c r="R4">
+        <f>Q4^2</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="S4">
+        <f>Q4/$R$10</f>
+        <v>-0.28867513459481292</v>
+      </c>
+      <c r="U4" s="26">
+        <f>S4+S13</f>
+        <v>-0.48696882675246722</v>
+      </c>
+      <c r="V4" s="26">
+        <f>U4/SQRT(2)</f>
+        <v>-0.34433895962312661</v>
+      </c>
+      <c r="W4" s="26">
+        <f>ROUND(V4,2)</f>
+        <v>-0.34</v>
+      </c>
+      <c r="X4">
+        <f>U4^2</f>
+        <v>0.23713863822867443</v>
+      </c>
+      <c r="Y4">
+        <f>U4/$X$10</f>
+        <v>-0.24396044147421997</v>
+      </c>
+      <c r="Z4" s="33">
+        <f>ROUND(Y4,2)</f>
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="5" spans="7:26" x14ac:dyDescent="0.35">
+      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
+        <f>AVERAGE(O4:O7)</f>
+        <v>1.25</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q7" si="0">O5-P5</f>
+        <v>0.75</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R7" si="1">Q5^2</f>
+        <v>0.5625</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S7" si="2">Q5/$R$10</f>
+        <v>0.86602540378443871</v>
+      </c>
+      <c r="U5" s="26">
+        <f t="shared" ref="U5:U7" si="3">S5+S14</f>
+        <v>1.7252980698009406</v>
+      </c>
+      <c r="V5" s="26">
+        <f t="shared" ref="V5:V7" si="4">U5/SQRT(2)</f>
+        <v>1.2199699647243063</v>
+      </c>
+      <c r="W5" s="35">
+        <f t="shared" ref="W5:W7" si="5">ROUND(V5,2)</f>
+        <v>1.22</v>
+      </c>
+      <c r="X5">
+        <f t="shared" ref="X5:X7" si="6">U5^2</f>
+        <v>2.9766534296588514</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" ref="Y5:Y7" si="7">U5/$X$10</f>
+        <v>0.86433557069805711</v>
+      </c>
+      <c r="Z5" s="36">
+        <f t="shared" ref="Z5:Z7" si="8">ROUND(Y5,2)</f>
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="6" spans="7:26" x14ac:dyDescent="0.35">
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <f>AVERAGE(O4:O7)</f>
+        <v>1.25</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>-0.25</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>-0.28867513459481292</v>
+      </c>
+      <c r="U6" s="26">
+        <f t="shared" si="3"/>
+        <v>-0.57509935660031353</v>
+      </c>
+      <c r="V6" s="26">
+        <f t="shared" si="4"/>
+        <v>-0.40665665490810216</v>
+      </c>
+      <c r="W6" s="26">
+        <f t="shared" si="5"/>
+        <v>-0.41</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="6"/>
+        <v>0.33073926996209457</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="7"/>
+        <v>-0.28811185689935237</v>
+      </c>
+      <c r="Z6" s="33">
+        <f t="shared" si="8"/>
+        <v>-0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="7:26" x14ac:dyDescent="0.35">
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <f>AVERAGE(O4:O7)</f>
+        <v>1.25</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>-0.25</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>-0.28867513459481292</v>
+      </c>
+      <c r="U7" s="26">
+        <f t="shared" si="3"/>
+        <v>-0.66322988644815983</v>
+      </c>
+      <c r="V7" s="26">
+        <f t="shared" si="4"/>
+        <v>-0.4689743501930777</v>
+      </c>
+      <c r="W7" s="26">
+        <f t="shared" si="5"/>
+        <v>-0.47</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="6"/>
+        <v>0.43987388227803897</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="7"/>
+        <v>-0.33226327232448477</v>
+      </c>
+      <c r="Z7" s="33">
+        <f t="shared" si="8"/>
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="8" spans="7:26" x14ac:dyDescent="0.35">
+      <c r="U8" s="26"/>
+      <c r="V8" s="26"/>
+      <c r="W8" s="26"/>
+    </row>
+    <row r="9" spans="7:26" x14ac:dyDescent="0.35">
+      <c r="P9" t="s">
+        <v>108</v>
+      </c>
+      <c r="R9">
+        <f>SUM(R4:R7)</f>
+        <v>0.75</v>
+      </c>
+      <c r="U9" s="26"/>
+      <c r="V9" s="26">
+        <f>V4^2+V5^2+V6^2+V7^2</f>
+        <v>1.9922026100638293</v>
+      </c>
+      <c r="W9" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="X9" s="33">
+        <f>SUM(X4:X7)</f>
+        <v>3.9844052201276594</v>
+      </c>
+      <c r="Y9">
+        <f>SUM(Y4:Y7)</f>
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <f>SUM(Z4:Z7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="7:26" x14ac:dyDescent="0.35">
+      <c r="P10" t="s">
+        <v>109</v>
+      </c>
+      <c r="R10">
+        <f>SQRT(R9)</f>
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="W10" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="X10" s="33">
+        <f>SQRT(X9)</f>
+        <v>1.9960974976507684</v>
+      </c>
+    </row>
+    <row r="12" spans="7:26" x14ac:dyDescent="0.35">
+      <c r="Q12" t="s">
+        <v>105</v>
+      </c>
+      <c r="S12" t="s">
+        <v>111</v>
+      </c>
+      <c r="W12" t="s">
+        <v>114</v>
+      </c>
+      <c r="X12">
+        <f>SQRT(2)</f>
+        <v>1.4142135623730951</v>
+      </c>
+    </row>
+    <row r="13" spans="7:26" x14ac:dyDescent="0.35">
+      <c r="O13">
+        <v>70</v>
+      </c>
+      <c r="P13">
+        <f>AVERAGE(O13:O16)</f>
+        <v>81.25</v>
+      </c>
+      <c r="Q13">
+        <f>O13-P13</f>
+        <v>-11.25</v>
+      </c>
+      <c r="R13">
+        <f>Q13^2</f>
+        <v>126.5625</v>
+      </c>
+      <c r="S13">
+        <f>Q13/$R$19</f>
+        <v>-0.19829369215765427</v>
+      </c>
+    </row>
+    <row r="14" spans="7:26" x14ac:dyDescent="0.35">
+      <c r="O14">
+        <v>130</v>
+      </c>
+      <c r="P14">
+        <f>AVERAGE(O13:O16)</f>
+        <v>81.25</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" ref="Q14:Q16" si="9">O14-P14</f>
+        <v>48.75</v>
+      </c>
+      <c r="R14">
+        <f t="shared" ref="R14:R16" si="10">Q14^2</f>
+        <v>2376.5625</v>
+      </c>
+      <c r="S14">
+        <f t="shared" ref="S14:S16" si="11">Q14/$R$19</f>
+        <v>0.85927266601650187</v>
+      </c>
+    </row>
+    <row r="15" spans="7:26" x14ac:dyDescent="0.35">
+      <c r="O15">
+        <v>65</v>
+      </c>
+      <c r="P15">
+        <f>AVERAGE(O13:O16)</f>
+        <v>81.25</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="9"/>
+        <v>-16.25</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="10"/>
+        <v>264.0625</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="11"/>
+        <v>-0.28642422200550061</v>
+      </c>
+    </row>
+    <row r="16" spans="7:26" x14ac:dyDescent="0.35">
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <f>G16</f>
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <f>H16</f>
+        <v>3</v>
+      </c>
+      <c r="O16">
+        <v>60</v>
+      </c>
+      <c r="P16">
+        <f>AVERAGE(O13:O16)</f>
+        <v>81.25</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="9"/>
+        <v>-21.25</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="10"/>
+        <v>451.5625</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="11"/>
+        <v>-0.37455475185334697</v>
+      </c>
+    </row>
+    <row r="17" spans="7:18" x14ac:dyDescent="0.35">
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17">
+        <v>-4</v>
+      </c>
+      <c r="I17">
+        <v>9</v>
+      </c>
+      <c r="J17">
+        <f t="shared" ref="J17:K18" si="12">G17</f>
+        <v>4</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="12"/>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="18" spans="7:18" x14ac:dyDescent="0.35">
+      <c r="G18">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>7</v>
+      </c>
+      <c r="I18">
+        <v>12</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="12"/>
+        <v>13</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="12"/>
+        <v>7</v>
+      </c>
+      <c r="Q18">
+        <f>Q13^2+Q14^2+Q15^2+Q16^2</f>
+        <v>3218.75</v>
+      </c>
+      <c r="R18">
+        <f>SUM(R13:R16)</f>
+        <v>3218.75</v>
+      </c>
+    </row>
+    <row r="19" spans="7:18" x14ac:dyDescent="0.35">
+      <c r="Q19">
+        <f>SQRT(Q18)</f>
+        <v>56.734028589551087</v>
+      </c>
+      <c r="R19">
+        <f>SQRT(R18)</f>
+        <v>56.734028589551087</v>
+      </c>
+    </row>
+    <row r="20" spans="7:18" x14ac:dyDescent="0.35">
+      <c r="G20">
+        <f>G16*H17*I18</f>
+        <v>-48</v>
+      </c>
+      <c r="H20">
+        <f>H16*I17*J18</f>
+        <v>351</v>
+      </c>
+      <c r="I20">
+        <f>I16*J17*K18</f>
+        <v>140</v>
+      </c>
+      <c r="K20">
+        <f>G20+H20+I20</f>
+        <v>443</v>
+      </c>
+    </row>
+    <row r="21" spans="7:18" x14ac:dyDescent="0.35">
+      <c r="G21">
+        <f>G18*H17*I16</f>
+        <v>-260</v>
+      </c>
+      <c r="H21">
+        <f>H18*I17*J16</f>
+        <v>63</v>
+      </c>
+      <c r="I21">
+        <f>I18*J17*K16</f>
+        <v>144</v>
+      </c>
+      <c r="K21">
+        <f>G21+H21+I21</f>
+        <v>-53</v>
+      </c>
+      <c r="L21" s="20">
+        <f>K20-K21</f>
+        <v>496</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Edu/Linear_algebra/linal_session_task.xlsx
+++ b/Edu/Linear_algebra/linal_session_task.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iTonyJah\DataScience\Edu\Linear_algebra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06E4F92-B9B9-494B-8D85-BF9BD368D0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AB5CCB-4C65-49AE-A464-EA453D8D8F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6B48EADF-CD2A-4593-B5B4-C8A55DF2A88B}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="118">
   <si>
     <t>Рабочая таблица с данными:</t>
   </si>
@@ -123,9 +123,6 @@
     <t>Решение:</t>
   </si>
   <si>
-    <t>Вычислим u, произведение матрицы Х размером 3 строки на 3 столбца и вектора столбца Y. В результате получим вектор столбец u размером 3х1</t>
-  </si>
-  <si>
     <t>u</t>
   </si>
   <si>
@@ -141,9 +138,6 @@
     <t xml:space="preserve">  =2*2200 + 45*1600 + 2 * 1900</t>
   </si>
   <si>
-    <t>Найдём произведение транспонированной матрицы Х слева на получившийся вектор u.</t>
-  </si>
-  <si>
     <t xml:space="preserve">   =3*93900 + 1*52100 + 2*80200</t>
   </si>
   <si>
@@ -171,12 +165,6 @@
     <t>матрица М</t>
   </si>
   <si>
-    <t>Найдём матрицу М, произведение транспонированой матрицы X (3*3) и Х (3*3), в резульате получим матрицу размера 3 на 3.</t>
-  </si>
-  <si>
-    <t>Первый столбец матрицы М получаем так же как и при умножении на первый вектор столбец, а второй и третий умножением на соответствующие столбцы.</t>
-  </si>
-  <si>
     <t xml:space="preserve">   =3*3 + 1*1 + 2*2</t>
   </si>
   <si>
@@ -186,33 +174,18 @@
     <t xml:space="preserve">   =3*3 + 1*1 + 2*</t>
   </si>
   <si>
-    <t>Итого 15 операций на столбец, всего 45 операций.</t>
-  </si>
-  <si>
-    <t>Итого в каждой строке у нас 3 умножения и 2 сложения, 5 операций на строку, 15 на весь вектор.</t>
-  </si>
-  <si>
-    <t>Найдём произведение матрицы М и вектора-столбца Y.</t>
-  </si>
-  <si>
     <t xml:space="preserve">   =273*2200 + 5526*1600 + 273*1900</t>
   </si>
   <si>
     <t xml:space="preserve">   = 14*2200 + 273*1600 + 14*1900</t>
   </si>
   <si>
-    <t>Первый и второй спсоб перемножения дают нам один и тот же ветор столбец.</t>
-  </si>
-  <si>
     <t>В первом способе нам потребовалось 30 операций, а во втором 60.</t>
   </si>
   <si>
     <t>Ответ:</t>
   </si>
   <si>
-    <t>Вывод: для задач по анализу данных следует выбирать порядок умножения матриц с меньшими размерностями справа,</t>
-  </si>
-  <si>
     <t>тогда нам понадобится меньше операций для вычисления, что может быть существенным при матрицах большого размера.</t>
   </si>
   <si>
@@ -349,34 +322,6 @@
   </si>
   <si>
     <t>Центральный</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Итого еще 15 операций или </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>всего 30 операций</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -441,6 +386,432 @@
   </si>
   <si>
     <t>st1+st2=st_n</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Итого 15 операций на столбец, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>всего 45 операций</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Найдём произведение транспонированной матрицы </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Х</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> слева на получившийся вектор </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Найдём матрицу </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>М</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, произведение транспонированой матрицы </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (3*3) и </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Х</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (3*3), в резульате получим матрицу размера 3 на 3.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Найдём произведение матрицы </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>М</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> и вектора-столбца </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Первый и второй способ перемножения дают нам один и тот же вектор столбец.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Вывод</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: для задач по анализу данных следует выбирать порядок умножения матриц с меньшими размерностями справа,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Вычислим </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, произведение матрицы </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Х</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> размером 3 строки на 3 столбца и вектора столбца </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. В результате получим вектор столбец </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> размером 3х1.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Итого в каждой строке у нас 3 умножения и 2 сложения, 5 операций на строку, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> на весь вектор.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Итого еще </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> операций или </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>всего 30 операций</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Первый столбец матрицы </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>М</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> получаем так же как и при умножении на первый вектор столбец, </t>
+    </r>
+  </si>
+  <si>
+    <t>а второй и третий умножением на соответствующие столбцы.</t>
   </si>
 </sst>
 </file>
@@ -745,7 +1116,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -960,7 +1331,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>374650</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>158750</xdr:rowOff>
@@ -1125,7 +1496,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>514350</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
@@ -1265,7 +1636,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1418,7 +1789,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>355600</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -1583,7 +1954,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1735,9 +2106,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="546100" cy="209550"/>
@@ -1882,9 +2253,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="546100" cy="177800"/>
@@ -2035,9 +2406,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="546100" cy="209550"/>
@@ -2182,9 +2553,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="546100" cy="190500"/>
@@ -2310,9 +2681,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="596900" cy="203200"/>
@@ -2475,9 +2846,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>473075</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1431353" cy="221214"/>
@@ -2701,9 +3072,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>109</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="991875" cy="461345"/>
@@ -3292,2293 +3663,2304 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:AD156"/>
+  <dimension ref="B1:AE158"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="25" max="25" width="12.7265625" customWidth="1"/>
+    <col min="7" max="9" width="7.6328125" customWidth="1"/>
+    <col min="11" max="11" width="6.08984375" customWidth="1"/>
+    <col min="26" max="26" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2">
+    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="2">
         <v>3</v>
       </c>
-      <c r="B3" s="2">
+      <c r="C3" s="2">
         <v>51</v>
       </c>
-      <c r="C3" s="2">
+      <c r="D3" s="2">
         <v>3</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <v>2200</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="3">
+    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="3">
+      <c r="C4" s="3">
         <v>30</v>
       </c>
-      <c r="C4" s="3">
+      <c r="D4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="3">
+      <c r="E4" s="3">
         <v>0</v>
       </c>
-      <c r="E4" s="3">
+      <c r="F4" s="3">
         <v>1</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>0</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3">
+    <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="3">
+      <c r="C5" s="3">
         <v>45</v>
       </c>
-      <c r="C5" s="3">
+      <c r="D5" s="3">
         <v>2</v>
       </c>
-      <c r="D5" s="3">
+      <c r="E5" s="3">
         <v>0</v>
       </c>
-      <c r="E5" s="3">
+      <c r="F5" s="3">
         <v>1</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>0</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="3">
+    <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="3">
+      <c r="C6" s="3">
         <v>55</v>
       </c>
-      <c r="C6" s="3">
+      <c r="D6" s="3">
         <v>1</v>
       </c>
-      <c r="D6" s="3">
+      <c r="E6" s="3">
         <v>0</v>
       </c>
-      <c r="E6" s="3">
+      <c r="F6" s="3">
         <v>1</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>0</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3">
+    <row r="7" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="B7" s="3">
+      <c r="C7" s="3">
         <v>45</v>
       </c>
-      <c r="C7" s="3">
+      <c r="D7" s="3">
         <v>3</v>
       </c>
-      <c r="D7" s="3">
+      <c r="E7" s="3">
         <v>1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
       </c>
       <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="23" x14ac:dyDescent="0.5">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="2:8" ht="23" x14ac:dyDescent="0.5">
+      <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C14" t="s">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C15" t="s">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
+    <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
         <v>8</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="2">
+    <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="2">
         <v>3</v>
       </c>
-      <c r="B18" s="2">
+      <c r="C18" s="2">
         <v>51</v>
       </c>
-      <c r="C18" s="2">
+      <c r="D18" s="2">
         <v>3</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" s="2">
         <v>2200</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="3">
+    <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="3">
         <v>1</v>
       </c>
-      <c r="B19" s="3">
+      <c r="C19" s="3">
         <v>30</v>
       </c>
-      <c r="C19" s="3">
+      <c r="D19" s="3">
         <v>1</v>
       </c>
-      <c r="E19" s="3">
+      <c r="F19" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="3">
+    <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="3">
         <v>2</v>
       </c>
-      <c r="B20" s="3">
+      <c r="C20" s="3">
         <v>45</v>
       </c>
-      <c r="C20" s="3">
+      <c r="D20" s="3">
         <v>2</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B22" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
         <v>19</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
         <v>21</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16" x14ac:dyDescent="0.4">
-      <c r="A33" s="14" t="s">
+    <row r="33" spans="2:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="B33" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34" s="6" t="s">
+    <row r="34" spans="2:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B37" s="10" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A37" s="10" t="s">
-        <v>28</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J37" s="10" t="s">
+      <c r="K37" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38" s="7">
-        <f>F38*J$38+G38*J$39+H38*J$40</f>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B38" s="12">
+        <f>G38*K$38+H38*K$39+I38*K$40</f>
         <v>93900</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="C38" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38" s="7">
+        <v>3</v>
+      </c>
+      <c r="H38" s="7">
+        <v>51</v>
+      </c>
+      <c r="I38" s="7">
+        <v>3</v>
+      </c>
+      <c r="K38" s="12">
+        <v>2200</v>
+      </c>
+      <c r="M38" s="8"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B39" s="12">
+        <f t="shared" ref="B39:B40" si="0">G39*K$38+H39*K$39+I39*K$40</f>
+        <v>52100</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F38" s="7">
-        <v>3</v>
-      </c>
-      <c r="G38" s="7">
-        <v>51</v>
-      </c>
-      <c r="H38" s="7">
-        <v>3</v>
-      </c>
-      <c r="J38" s="7">
-        <v>2200</v>
-      </c>
-      <c r="L38" s="8"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A39" s="7">
-        <f t="shared" ref="A39:A40" si="0">F39*J$38+G39*J$39+H39*J$40</f>
-        <v>52100</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" s="7">
+      <c r="G39" s="7">
         <v>1</v>
       </c>
-      <c r="G39" s="7">
+      <c r="H39" s="7">
         <v>30</v>
       </c>
-      <c r="H39" s="7">
+      <c r="I39" s="7">
         <v>1</v>
       </c>
-      <c r="J39" s="7">
+      <c r="K39" s="12">
         <v>1600</v>
       </c>
-      <c r="L39" s="8"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A40" s="7">
+      <c r="M39" s="8"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B40" s="12">
         <f t="shared" si="0"/>
         <v>80200</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="C40" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" s="7">
+        <v>2</v>
+      </c>
+      <c r="H40" s="7">
+        <v>45</v>
+      </c>
+      <c r="I40" s="7">
+        <v>2</v>
+      </c>
+      <c r="K40" s="12">
+        <v>1900</v>
+      </c>
+      <c r="M40" s="8"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B41" s="11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B42" s="11"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B43" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B44" s="10"/>
+      <c r="K44" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B45" s="12">
+        <f>G45*K$45+H45*K$46+I45*K$47</f>
+        <v>494200</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F40" s="7">
+      <c r="G45" s="7">
+        <v>3</v>
+      </c>
+      <c r="H45" s="7">
+        <v>1</v>
+      </c>
+      <c r="I45" s="7">
         <v>2</v>
       </c>
-      <c r="G40" s="7">
+      <c r="K45" s="12">
+        <v>93900</v>
+      </c>
+      <c r="M45" s="8"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B46" s="12">
+        <f t="shared" ref="B46:B47" si="1">G46*K$45+H46*K$46+I46*K$47</f>
+        <v>9960900</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G46" s="7">
+        <v>51</v>
+      </c>
+      <c r="H46" s="7">
+        <v>30</v>
+      </c>
+      <c r="I46" s="7">
         <v>45</v>
       </c>
-      <c r="H40" s="7">
-        <v>2</v>
-      </c>
-      <c r="J40" s="7">
-        <v>1900</v>
-      </c>
-      <c r="L40" s="8"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B41" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43" s="10"/>
-      <c r="J43" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A44" s="12">
-        <f>F44*J$44+G44*J$45+H44*J$46</f>
-        <v>494200</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F44" s="7">
-        <v>3</v>
-      </c>
-      <c r="G44" s="7">
-        <v>1</v>
-      </c>
-      <c r="H44" s="7">
-        <v>2</v>
-      </c>
-      <c r="J44" s="12">
-        <v>93900</v>
-      </c>
-      <c r="L44" s="8"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
-        <f t="shared" ref="A45:A46" si="1">F45*J$44+G45*J$45+H45*J$46</f>
-        <v>9960900</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F45" s="7">
-        <v>51</v>
-      </c>
-      <c r="G45" s="7">
-        <v>30</v>
-      </c>
-      <c r="H45" s="7">
-        <v>45</v>
-      </c>
-      <c r="J45" s="12">
+      <c r="K46" s="12">
         <v>52100</v>
       </c>
-      <c r="L45" s="8"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
+      <c r="M46" s="8"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B47" s="12">
         <f t="shared" si="1"/>
         <v>494200</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="C47" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G47" s="7">
+        <v>3</v>
+      </c>
+      <c r="H47" s="7">
+        <v>1</v>
+      </c>
+      <c r="I47" s="7">
+        <v>2</v>
+      </c>
+      <c r="K47" s="12">
+        <v>80200</v>
+      </c>
+      <c r="M47" s="8"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B48" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F46" s="7">
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="C51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H51" s="13"/>
+      <c r="L51" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B52" s="12">
+        <f>$G52*K$52+$H52*K$53+$I52*K$54</f>
+        <v>14</v>
+      </c>
+      <c r="C52" s="12">
+        <f t="shared" ref="C52:C54" si="2">$G52*L$52+$H52*L$53+$I52*L$54</f>
+        <v>273</v>
+      </c>
+      <c r="D52" s="12">
+        <f t="shared" ref="D52:D54" si="3">$G52*M$52+$H52*M$53+$I52*M$54</f>
+        <v>14</v>
+      </c>
+      <c r="G52" s="7">
         <v>3</v>
       </c>
-      <c r="G46" s="7">
+      <c r="H52" s="7">
         <v>1</v>
       </c>
-      <c r="H46" s="7">
+      <c r="I52" s="7">
         <v>2</v>
       </c>
-      <c r="J46" s="12">
-        <v>80200</v>
-      </c>
-      <c r="L46" s="8"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B47" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A48" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B50" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K50" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A51" s="12">
-        <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
-        <v>14</v>
-      </c>
-      <c r="B51" s="12">
-        <f t="shared" ref="B51:B53" si="2">$F51*K$51+$G51*K$52+$H51*K$53</f>
+      <c r="K52" s="7">
+        <v>3</v>
+      </c>
+      <c r="L52" s="7">
+        <v>51</v>
+      </c>
+      <c r="M52" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B53" s="12">
+        <f t="shared" ref="B53:B54" si="4">$G53*K$52+$H53*K$53+$I53*K$54</f>
         <v>273</v>
       </c>
-      <c r="C51" s="12">
-        <f t="shared" ref="C51:C53" si="3">$F51*L$51+$G51*L$52+$H51*L$53</f>
-        <v>14</v>
-      </c>
-      <c r="F51" s="7">
-        <v>3</v>
-      </c>
-      <c r="G51" s="7">
-        <v>1</v>
-      </c>
-      <c r="H51" s="7">
-        <v>2</v>
-      </c>
-      <c r="J51" s="7">
-        <v>3</v>
-      </c>
-      <c r="K51" s="7">
-        <v>51</v>
-      </c>
-      <c r="L51" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A52" s="12">
-        <f t="shared" ref="A52:A53" si="4">$F52*J$51+$G52*J$52+$H52*J$53</f>
-        <v>273</v>
-      </c>
-      <c r="B52" s="12">
+      <c r="C53" s="12">
         <f t="shared" si="2"/>
         <v>5526</v>
       </c>
-      <c r="C52" s="12">
+      <c r="D53" s="12">
         <f t="shared" si="3"/>
         <v>273</v>
       </c>
-      <c r="F52" s="7">
+      <c r="G53" s="7">
         <v>51</v>
       </c>
-      <c r="G52" s="7">
+      <c r="H53" s="7">
         <v>30</v>
       </c>
-      <c r="H52" s="7">
+      <c r="I53" s="7">
         <v>45</v>
       </c>
-      <c r="J52" s="7">
+      <c r="K53" s="7">
         <v>1</v>
       </c>
-      <c r="K52" s="7">
+      <c r="L53" s="7">
         <v>30</v>
       </c>
-      <c r="L52" s="7">
+      <c r="M53" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A53" s="12">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B54" s="12">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="B53" s="12">
+      <c r="C54" s="12">
         <f t="shared" si="2"/>
         <v>273</v>
       </c>
-      <c r="C53" s="12">
+      <c r="D54" s="12">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="F53" s="7">
+      <c r="G54" s="7">
         <v>3</v>
       </c>
-      <c r="G53" s="7">
+      <c r="H54" s="7">
         <v>1</v>
       </c>
-      <c r="H53" s="7">
+      <c r="I54" s="7">
         <v>2</v>
       </c>
-      <c r="J53" s="7">
+      <c r="K54" s="7">
         <v>2</v>
       </c>
-      <c r="K53" s="7">
+      <c r="L54" s="7">
         <v>45</v>
       </c>
-      <c r="L53" s="7">
+      <c r="M54" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B55" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
+        <v>35</v>
+      </c>
+      <c r="F57" t="s">
+        <v>36</v>
+      </c>
+      <c r="J57" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B58" s="12">
+        <f>$G52*K$52+$H52*K$53+$I52*K$54</f>
+        <v>14</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F58" s="12">
+        <f>$G52*L$52+$H52*L$53+$I52*L$54</f>
+        <v>273</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J58" s="12">
+        <f>$G52*M$52+$H52*M$53+$I52*M$54</f>
+        <v>14</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B59" s="12">
+        <f>$G53*K$52+$H53*K$53+$I53*K$54</f>
+        <v>273</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" s="12">
+        <f>$G53*L$52+$H53*L$53+$I53*L$54</f>
+        <v>5526</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J59" s="12">
+        <f>$G53*M$52+$H53*M$53+$I53*M$54</f>
+        <v>273</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B60" s="12">
+        <f>$G54*K$52+$H54*K$53+$I54*K$54</f>
+        <v>14</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F60" s="12">
+        <f>$G54*L$52+$H54*L$53+$I54*L$54</f>
+        <v>273</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J60" s="12">
+        <f>$G54*M$52+$H54*M$53+$I54*M$54</f>
+        <v>14</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="C61" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B62" t="s">
+        <v>110</v>
+      </c>
+      <c r="C62" s="8"/>
+      <c r="G62" s="8"/>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="H63" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B64" s="12">
+        <f>G64*K$64+H64*K$65+I64*K$66</f>
+        <v>494200</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G64" s="12">
+        <v>14</v>
+      </c>
+      <c r="H64" s="12">
+        <v>273</v>
+      </c>
+      <c r="I64" s="12">
+        <v>14</v>
+      </c>
+      <c r="K64" s="7">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B65" s="12">
+        <f t="shared" ref="B65:B66" si="5">G65*K$64+H65*K$65+I65*K$66</f>
+        <v>9960900</v>
+      </c>
+      <c r="C65" s="8" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>37</v>
-      </c>
-      <c r="E55" t="s">
-        <v>38</v>
-      </c>
-      <c r="I55" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A56" s="12">
-        <f>$F51*J$51+$G51*J$52+$H51*J$53</f>
-        <v>14</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E56" s="12">
-        <f>$F51*K$51+$G51*K$52+$H51*K$53</f>
+      <c r="G65" s="12">
         <v>273</v>
       </c>
-      <c r="F56" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I56" s="12">
-        <f>$F51*L$51+$G51*L$52+$H51*L$53</f>
-        <v>14</v>
-      </c>
-      <c r="J56" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A57" s="12">
-        <f>$F52*J$51+$G52*J$52+$H52*J$53</f>
+      <c r="H65" s="12">
+        <v>5526</v>
+      </c>
+      <c r="I65" s="12">
         <v>273</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E57" s="12">
-        <f>$F52*K$51+$G52*K$52+$H52*K$53</f>
-        <v>5526</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I57" s="12">
-        <f>$F52*L$51+$G52*L$52+$H52*L$53</f>
-        <v>273</v>
-      </c>
-      <c r="J57" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A58" s="12">
-        <f>$F53*J$51+$G53*J$52+$H53*J$53</f>
-        <v>14</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E58" s="12">
-        <f>$F53*K$51+$G53*K$52+$H53*K$53</f>
-        <v>273</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I58" s="12">
-        <f>$F53*L$51+$G53*L$52+$H53*L$53</f>
-        <v>14</v>
-      </c>
-      <c r="J58" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B59" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>50</v>
-      </c>
-      <c r="B60" s="8"/>
-      <c r="F60" s="8"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="G61" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J61" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A62" s="12">
-        <f>F62*J$62+G62*J$63+H62*J$64</f>
-        <v>494200</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F62" s="12">
-        <v>14</v>
-      </c>
-      <c r="G62" s="12">
-        <v>273</v>
-      </c>
-      <c r="H62" s="12">
-        <v>14</v>
-      </c>
-      <c r="J62" s="7">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A63" s="12">
-        <f t="shared" ref="A63:A64" si="5">F63*J$62+G63*J$63+H63*J$64</f>
-        <v>9960900</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F63" s="12">
-        <v>273</v>
-      </c>
-      <c r="G63" s="12">
-        <v>5526</v>
-      </c>
-      <c r="H63" s="12">
-        <v>273</v>
-      </c>
-      <c r="J63" s="7">
+      <c r="K65" s="7">
         <v>1600</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A64" s="12">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B66" s="12">
         <f t="shared" si="5"/>
         <v>494200</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="C66" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G66" s="12">
+        <v>14</v>
+      </c>
+      <c r="H66" s="12">
+        <v>273</v>
+      </c>
+      <c r="I66" s="12">
+        <v>14</v>
+      </c>
+      <c r="K66" s="7">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="C67" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B69" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C69" s="8"/>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="D70" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B71" s="12">
+        <v>494200</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B72" s="12">
+        <v>9960900</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B73" s="12">
+        <v>494200</v>
+      </c>
+      <c r="D73" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" ht="23" x14ac:dyDescent="0.35">
+      <c r="B76" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B78" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B80" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B81" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B82" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B83" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B84" t="s">
         <v>52</v>
       </c>
-      <c r="F64" s="12">
-        <v>14</v>
-      </c>
-      <c r="G64" s="12">
-        <v>273</v>
-      </c>
-      <c r="H64" s="12">
-        <v>14</v>
-      </c>
-      <c r="J64" s="7">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B65" s="11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="6" t="s">
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B85" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B86" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B87" t="s">
         <v>55</v>
       </c>
-      <c r="B67" s="8"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C68" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="12">
-        <v>494200</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="12">
-        <v>9960900</v>
-      </c>
-      <c r="C70" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="12">
-        <v>494200</v>
-      </c>
-      <c r="C71" t="s">
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B89" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B90" s="13" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="23" x14ac:dyDescent="0.35">
-      <c r="A74" s="15" t="s">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C91" t="s">
+        <v>1</v>
+      </c>
+      <c r="D91" t="s">
+        <v>2</v>
+      </c>
+      <c r="E91" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" t="s">
+        <v>6</v>
+      </c>
+      <c r="J91" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="D92" s="16"/>
+      <c r="E92" s="16"/>
+      <c r="F92" s="16" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+      <c r="G92" s="16"/>
+      <c r="H92" s="16"/>
+      <c r="J92" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A87" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A88" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B89" t="s">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C93" s="7">
+        <v>3</v>
+      </c>
+      <c r="D93" s="7">
+        <v>51</v>
+      </c>
+      <c r="E93" s="7">
+        <v>3</v>
+      </c>
+      <c r="F93" s="7">
+        <v>0</v>
+      </c>
+      <c r="G93" s="7">
         <v>1</v>
       </c>
-      <c r="C89" t="s">
+      <c r="H93" s="7">
+        <v>0</v>
+      </c>
+      <c r="J93" s="7">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C94" s="7">
+        <v>1</v>
+      </c>
+      <c r="D94" s="7">
+        <v>30</v>
+      </c>
+      <c r="E94" s="7">
+        <v>1</v>
+      </c>
+      <c r="F94" s="7">
+        <v>0</v>
+      </c>
+      <c r="G94" s="7">
+        <v>1</v>
+      </c>
+      <c r="H94" s="7">
+        <v>0</v>
+      </c>
+      <c r="J94" s="7">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C95" s="7">
         <v>2</v>
       </c>
-      <c r="D89" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" t="s">
-        <v>4</v>
-      </c>
-      <c r="F89" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" t="s">
-        <v>6</v>
-      </c>
-      <c r="I89" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C90" s="16"/>
-      <c r="D90" s="16"/>
-      <c r="E90" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="F90" s="16"/>
-      <c r="G90" s="16"/>
-      <c r="I90" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B91" s="7">
-        <v>3</v>
-      </c>
-      <c r="C91" s="7">
-        <v>51</v>
-      </c>
-      <c r="D91" s="7">
-        <v>3</v>
-      </c>
-      <c r="E91" s="7">
-        <v>0</v>
-      </c>
-      <c r="F91" s="7">
-        <v>1</v>
-      </c>
-      <c r="G91" s="7">
-        <v>0</v>
-      </c>
-      <c r="I91" s="7">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B92" s="7">
-        <v>1</v>
-      </c>
-      <c r="C92" s="7">
-        <v>30</v>
-      </c>
-      <c r="D92" s="7">
-        <v>1</v>
-      </c>
-      <c r="E92" s="7">
-        <v>0</v>
-      </c>
-      <c r="F92" s="7">
-        <v>1</v>
-      </c>
-      <c r="G92" s="7">
-        <v>0</v>
-      </c>
-      <c r="I92" s="7">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B93" s="7">
+      <c r="D95" s="7">
+        <v>45</v>
+      </c>
+      <c r="E95" s="7">
         <v>2</v>
-      </c>
-      <c r="C93" s="7">
-        <v>45</v>
-      </c>
-      <c r="D93" s="7">
-        <v>2</v>
-      </c>
-      <c r="E93" s="7">
-        <v>0</v>
-      </c>
-      <c r="F93" s="7">
-        <v>1</v>
-      </c>
-      <c r="G93" s="7">
-        <v>0</v>
-      </c>
-      <c r="I93" s="7">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B94" s="7">
-        <v>3</v>
-      </c>
-      <c r="C94" s="7">
-        <v>55</v>
-      </c>
-      <c r="D94" s="7">
-        <v>1</v>
-      </c>
-      <c r="E94" s="7">
-        <v>0</v>
-      </c>
-      <c r="F94" s="7">
-        <v>1</v>
-      </c>
-      <c r="G94" s="7">
-        <v>0</v>
-      </c>
-      <c r="I94" s="7">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B95" s="7">
-        <v>1</v>
-      </c>
-      <c r="C95" s="7">
-        <v>45</v>
-      </c>
-      <c r="D95" s="7">
-        <v>3</v>
-      </c>
-      <c r="E95" s="7">
-        <v>1</v>
       </c>
       <c r="F95" s="7">
         <v>0</v>
       </c>
       <c r="G95" s="7">
+        <v>1</v>
+      </c>
+      <c r="H95" s="7">
         <v>0</v>
       </c>
-      <c r="I95" s="7">
+      <c r="J95" s="7">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C96" s="7">
+        <v>3</v>
+      </c>
+      <c r="D96" s="7">
+        <v>55</v>
+      </c>
+      <c r="E96" s="7">
+        <v>1</v>
+      </c>
+      <c r="F96" s="7">
+        <v>0</v>
+      </c>
+      <c r="G96" s="7">
+        <v>1</v>
+      </c>
+      <c r="H96" s="7">
+        <v>0</v>
+      </c>
+      <c r="J96" s="7">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="97" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="C97" s="7">
+        <v>1</v>
+      </c>
+      <c r="D97" s="7">
+        <v>45</v>
+      </c>
+      <c r="E97" s="7">
+        <v>3</v>
+      </c>
+      <c r="F97" s="7">
+        <v>1</v>
+      </c>
+      <c r="G97" s="7">
+        <v>0</v>
+      </c>
+      <c r="H97" s="7">
+        <v>0</v>
+      </c>
+      <c r="J97" s="7">
         <v>4500</v>
       </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A97" s="13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>74</v>
-      </c>
-      <c r="B99">
-        <f>SUM(B91:B95)</f>
+    <row r="99" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B99" s="13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="100" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B100" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="101" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B101" t="s">
+        <v>65</v>
+      </c>
+      <c r="C101">
+        <f>SUM(C93:C97)</f>
         <v>10</v>
       </c>
-      <c r="C99">
-        <f t="shared" ref="C99:I99" si="6">SUM(C91:C95)</f>
+      <c r="D101">
+        <f t="shared" ref="D101:J101" si="6">SUM(D93:D97)</f>
         <v>226</v>
       </c>
-      <c r="D99">
+      <c r="E101">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="E99">
+      <c r="F101">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="F99">
+      <c r="G101">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="G99">
+      <c r="H101">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I99">
+      <c r="J101">
         <f t="shared" si="6"/>
         <v>12200</v>
       </c>
-      <c r="AB99">
+      <c r="AC101">
         <v>95</v>
       </c>
-      <c r="AC99">
+      <c r="AD101">
         <v>5</v>
       </c>
-      <c r="AD99">
-        <f>AB99/AC99</f>
+      <c r="AE101">
+        <f>AC101/AD101</f>
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>75</v>
-      </c>
-      <c r="B100">
-        <f>B99/5</f>
+    <row r="102" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B102" t="s">
+        <v>66</v>
+      </c>
+      <c r="C102">
+        <f>C101/5</f>
         <v>2</v>
       </c>
-      <c r="C100" s="17">
-        <f t="shared" ref="C100:I100" si="7">C99/5</f>
+      <c r="D102" s="17">
+        <f t="shared" ref="D102:J102" si="7">D101/5</f>
         <v>45.2</v>
       </c>
-      <c r="D100">
+      <c r="E102">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="E100" s="17">
+      <c r="F102" s="17">
         <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
-      <c r="F100" s="17">
+      <c r="G102" s="17">
         <f t="shared" si="7"/>
         <v>0.8</v>
       </c>
-      <c r="G100">
+      <c r="H102">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I100">
+      <c r="J102">
         <f t="shared" si="7"/>
         <v>2440</v>
       </c>
-      <c r="S100">
+      <c r="T102">
         <f>1/5</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>76</v>
-      </c>
-      <c r="S101">
-        <f>S100^2</f>
+    <row r="103" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B103" t="s">
+        <v>67</v>
+      </c>
+      <c r="T103">
+        <f>T102^2</f>
         <v>4.0000000000000008E-2</v>
       </c>
-      <c r="T101">
-        <f>S101*5</f>
+      <c r="U103">
+        <f>T103*5</f>
         <v>0.20000000000000004</v>
       </c>
-      <c r="U101">
-        <f>SQRT(T101)</f>
+      <c r="V103">
+        <f>SQRT(U103)</f>
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="B102" s="7">
-        <f>B91-B$100</f>
+    <row r="104" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="C104" s="7">
+        <f>C93-C$102</f>
         <v>1</v>
       </c>
-      <c r="C102" s="17">
-        <f t="shared" ref="C102:G102" si="8">C91-C$100</f>
+      <c r="D104" s="17">
+        <f t="shared" ref="D104:H104" si="8">D93-D$102</f>
         <v>5.7999999999999972</v>
       </c>
-      <c r="D102" s="7">
+      <c r="E104" s="7">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="E102" s="17">
+      <c r="F104" s="17">
         <f t="shared" si="8"/>
         <v>-0.2</v>
       </c>
-      <c r="F102" s="17">
+      <c r="G104" s="17">
         <f t="shared" si="8"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="G102" s="7">
+      <c r="H104" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I102" s="7">
-        <f t="shared" ref="I102" si="9">I91-I$100</f>
+      <c r="J104" s="7">
+        <f t="shared" ref="J104" si="9">J93-J$102</f>
         <v>-240</v>
       </c>
-      <c r="J102" s="19">
-        <f>I102^2</f>
+      <c r="K104" s="19">
+        <f>J104^2</f>
         <v>57600</v>
       </c>
-      <c r="K102">
-        <f>SQRT(ABS(I102))</f>
+      <c r="L104">
+        <f>SQRT(ABS(J104))</f>
         <v>15.491933384829668</v>
       </c>
-      <c r="M102" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z102">
+      <c r="N104" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA104">
         <v>2255</v>
       </c>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="B103" s="7">
-        <f t="shared" ref="B103:G103" si="10">B92-B$100</f>
+    <row r="105" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="C105" s="7">
+        <f t="shared" ref="C105:H105" si="10">C94-C$102</f>
         <v>-1</v>
       </c>
-      <c r="C103" s="17">
+      <c r="D105" s="17">
         <f t="shared" si="10"/>
         <v>-15.200000000000003</v>
       </c>
-      <c r="D103" s="7">
+      <c r="E105" s="7">
         <f t="shared" si="10"/>
         <v>-1</v>
       </c>
-      <c r="E103" s="17">
+      <c r="F105" s="17">
         <f t="shared" si="10"/>
         <v>-0.2</v>
       </c>
-      <c r="F103" s="17">
+      <c r="G105" s="17">
         <f t="shared" si="10"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="G103" s="7">
+      <c r="H105" s="7">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I103" s="7">
-        <f t="shared" ref="I103" si="11">I92-I$100</f>
+      <c r="J105" s="7">
+        <f t="shared" ref="J105" si="11">J94-J$102</f>
         <v>-840</v>
       </c>
-      <c r="J103" s="19">
-        <f t="shared" ref="J103:J106" si="12">I103^2</f>
+      <c r="K105" s="19">
+        <f t="shared" ref="K105:K108" si="12">J105^2</f>
         <v>705600</v>
       </c>
-      <c r="K103">
-        <f t="shared" ref="K103:K106" si="13">SQRT(ABS(I103))</f>
+      <c r="L105">
+        <f t="shared" ref="L105:L108" si="13">SQRT(ABS(J105))</f>
         <v>28.982753492378876</v>
       </c>
-      <c r="S103">
+      <c r="T105">
         <f>4/5</f>
         <v>0.8</v>
       </c>
-      <c r="T103">
-        <f>SQRT(S103)</f>
+      <c r="U105">
+        <f>SQRT(T105)</f>
         <v>0.89442719099991586</v>
       </c>
-      <c r="W103">
-        <f>W104*W105*W106</f>
+      <c r="X105">
+        <f>X106*X107*X108</f>
         <v>1805</v>
       </c>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="B104" s="7">
-        <f t="shared" ref="B104:G104" si="14">B93-B$100</f>
+    <row r="106" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="C106" s="7">
+        <f t="shared" ref="C106:H106" si="14">C95-C$102</f>
         <v>0</v>
       </c>
-      <c r="C104" s="17">
+      <c r="D106" s="17">
         <f t="shared" si="14"/>
         <v>-0.20000000000000284</v>
       </c>
-      <c r="D104" s="7">
+      <c r="E106" s="7">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="E104" s="17">
+      <c r="F106" s="17">
         <f t="shared" si="14"/>
         <v>-0.2</v>
       </c>
-      <c r="F104" s="17">
+      <c r="G106" s="17">
         <f t="shared" si="14"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="G104" s="7">
+      <c r="H106" s="7">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I104" s="7">
-        <f t="shared" ref="I104" si="15">I93-I$100</f>
+      <c r="J106" s="7">
+        <f t="shared" ref="J106" si="15">J95-J$102</f>
         <v>-540</v>
       </c>
-      <c r="J104" s="19">
+      <c r="K106" s="19">
         <f t="shared" si="12"/>
         <v>291600</v>
       </c>
-      <c r="K104">
+      <c r="L106">
         <f t="shared" si="13"/>
         <v>23.2379000772445</v>
       </c>
-      <c r="M104">
+      <c r="N106">
         <v>29</v>
       </c>
-      <c r="N104">
-        <f>M104^2</f>
+      <c r="O106">
+        <f>N106^2</f>
         <v>841</v>
       </c>
-      <c r="T104">
-        <f>T103*2</f>
+      <c r="U106">
+        <f>U105*2</f>
         <v>1.7888543819998317</v>
       </c>
-      <c r="W104">
+      <c r="X106">
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="B105" s="7">
-        <f t="shared" ref="B105:G105" si="16">B94-B$100</f>
+    <row r="107" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="C107" s="7">
+        <f t="shared" ref="C107:H107" si="16">C96-C$102</f>
         <v>1</v>
       </c>
-      <c r="C105" s="17">
+      <c r="D107" s="17">
         <f t="shared" si="16"/>
         <v>9.7999999999999972</v>
       </c>
-      <c r="D105" s="7">
+      <c r="E107" s="7">
         <f t="shared" si="16"/>
         <v>-1</v>
       </c>
-      <c r="E105" s="17">
+      <c r="F107" s="17">
         <f t="shared" si="16"/>
         <v>-0.2</v>
       </c>
-      <c r="F105" s="17">
+      <c r="G107" s="17">
         <f t="shared" si="16"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="G105" s="7">
+      <c r="H107" s="7">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I105" s="7">
-        <f t="shared" ref="I105" si="17">I94-I$100</f>
+      <c r="J107" s="7">
+        <f t="shared" ref="J107" si="17">J96-J$102</f>
         <v>-440</v>
       </c>
-      <c r="J105" s="19">
+      <c r="K107" s="19">
         <f t="shared" si="12"/>
         <v>193600</v>
       </c>
-      <c r="K105">
+      <c r="L107">
         <f t="shared" si="13"/>
         <v>20.976176963403031</v>
       </c>
-      <c r="M105">
+      <c r="N107">
         <v>76</v>
       </c>
-      <c r="N105">
-        <f t="shared" ref="N105:N108" si="18">M105^2</f>
+      <c r="O107">
+        <f t="shared" ref="O107:O110" si="18">N107^2</f>
         <v>5776</v>
       </c>
-      <c r="R105">
+      <c r="S107">
         <f>5*451</f>
         <v>2255</v>
       </c>
-      <c r="W105">
+      <c r="X107">
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="B106" s="7">
-        <f t="shared" ref="B106:G106" si="19">B95-B$100</f>
+    <row r="108" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="C108" s="7">
+        <f t="shared" ref="C108:H108" si="19">C97-C$102</f>
         <v>-1</v>
       </c>
-      <c r="C106" s="17">
+      <c r="D108" s="17">
         <f t="shared" si="19"/>
         <v>-0.20000000000000284</v>
       </c>
-      <c r="D106" s="7">
+      <c r="E108" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="E106" s="17">
+      <c r="F108" s="17">
         <f t="shared" si="19"/>
         <v>0.8</v>
       </c>
-      <c r="F106" s="17">
+      <c r="G108" s="17">
         <f t="shared" si="19"/>
         <v>-0.8</v>
       </c>
-      <c r="G106" s="7">
+      <c r="H108" s="7">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I106" s="7">
-        <f t="shared" ref="I106" si="20">I95-I$100</f>
+      <c r="J108" s="7">
+        <f t="shared" ref="J108" si="20">J97-J$102</f>
         <v>2060</v>
       </c>
-      <c r="J106" s="19">
+      <c r="K108" s="19">
         <f t="shared" si="12"/>
         <v>4243600</v>
       </c>
-      <c r="K106">
+      <c r="L108">
         <f t="shared" si="13"/>
         <v>45.387222871640866</v>
       </c>
-      <c r="M106">
+      <c r="N108">
         <v>1</v>
       </c>
-      <c r="N106">
+      <c r="O108">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="W106">
+      <c r="X108">
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>77</v>
-      </c>
-      <c r="J107" s="19">
-        <f>SUM(J102:J106)</f>
+    <row r="109" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B109" t="s">
+        <v>68</v>
+      </c>
+      <c r="K109" s="19">
+        <f>SUM(K104:K108)</f>
         <v>5492000</v>
       </c>
-      <c r="K107">
-        <f>SQRT(ABS(J107))</f>
+      <c r="L109">
+        <f>SQRT(ABS(K109))</f>
         <v>2343.5016535091245</v>
       </c>
-      <c r="M107">
+      <c r="N109">
         <v>49</v>
       </c>
-      <c r="N107">
+      <c r="O109">
         <f t="shared" si="18"/>
         <v>2401</v>
       </c>
-      <c r="V107">
+      <c r="W109">
         <v>95</v>
       </c>
-      <c r="W107">
-        <f>V107*V107</f>
+      <c r="X109">
+        <f>W109*W109</f>
         <v>9025</v>
       </c>
-      <c r="Y107">
-        <f>V107*V107</f>
+      <c r="Z109">
+        <f>W109*W109</f>
         <v>9025</v>
       </c>
-      <c r="Z107">
-        <f>Y107/5</f>
+      <c r="AA109">
+        <f>Z109/5</f>
         <v>1805</v>
       </c>
-      <c r="AA107">
+      <c r="AB109">
         <v>1804</v>
       </c>
-      <c r="AB107">
-        <f>AA107/Z107</f>
+      <c r="AC109">
+        <f>AB109/AA109</f>
         <v>0.99944598337950141</v>
       </c>
-      <c r="AC107">
-        <f>SQRT(AB107)</f>
+      <c r="AD109">
+        <f>SQRT(AC109)</f>
         <v>0.99972295331231709</v>
       </c>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>78</v>
-      </c>
-      <c r="M108">
+    <row r="110" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B110" t="s">
+        <v>69</v>
+      </c>
+      <c r="N110">
         <v>1</v>
       </c>
-      <c r="N108">
+      <c r="O110">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="V108">
+      <c r="W110">
         <v>9020</v>
       </c>
-      <c r="W108">
+      <c r="X110">
         <v>25</v>
       </c>
-      <c r="X108">
-        <f>V108/W108</f>
+      <c r="Y110">
+        <f>W110/X110</f>
         <v>360.8</v>
       </c>
-      <c r="Y108">
-        <f>SQRT(X108)</f>
+      <c r="Z110">
+        <f>SQRT(Y110)</f>
         <v>18.994736112934024</v>
       </c>
-      <c r="AC108">
+      <c r="AD110">
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="B109">
-        <f>(B102^2+B103^2+B104^2+B105^2+B106^2)^(1/2)</f>
+    <row r="111" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="C111">
+        <f>(C104^2+C105^2+C106^2+C107^2+C108^2)^(1/2)</f>
         <v>2</v>
       </c>
-      <c r="C109">
-        <f t="shared" ref="C109:I109" si="21">(C102^2+C103^2+C104^2+C105^2+C106^2)^(1/2)</f>
+      <c r="D111">
+        <f t="shared" ref="D111:J111" si="21">(D104^2+D105^2+D106^2+D107^2+D108^2)^(1/2)</f>
         <v>18.994736112934028</v>
       </c>
-      <c r="D109">
+      <c r="E111">
         <f t="shared" si="21"/>
         <v>2</v>
       </c>
-      <c r="E109">
+      <c r="F111">
         <f t="shared" si="21"/>
         <v>0.89442719099991597</v>
       </c>
-      <c r="F109">
+      <c r="G111">
         <f t="shared" si="21"/>
         <v>0.89442719099991586</v>
       </c>
-      <c r="G109">
+      <c r="H111">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="H109">
+      <c r="I111">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="I109">
+      <c r="J111">
         <f t="shared" si="21"/>
         <v>2343.5016535091245</v>
       </c>
-      <c r="N109">
-        <f>SUM(N104:N108)</f>
+      <c r="O111">
+        <f>SUM(O106:O110)</f>
         <v>9020</v>
       </c>
-      <c r="P109">
+      <c r="Q111">
         <v>2255</v>
       </c>
-      <c r="Q109">
+      <c r="R111">
         <v>4</v>
       </c>
-      <c r="R109">
-        <f>Q109*P109</f>
+      <c r="S111">
+        <f>R111*Q111</f>
         <v>9020</v>
       </c>
-      <c r="X109">
+      <c r="Y111">
         <v>441</v>
       </c>
-      <c r="Y109">
-        <f>SQRT(X109)</f>
+      <c r="Z111">
+        <f>SQRT(Y111)</f>
         <v>21</v>
       </c>
-      <c r="AC109">
-        <f>AC108*AC107</f>
+      <c r="AD111">
+        <f>AD110*AD109</f>
         <v>18.994736112934024</v>
       </c>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>79</v>
-      </c>
-      <c r="X110" s="17">
-        <f>X109-X108</f>
+    <row r="112" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B112" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y112" s="17">
+        <f>Y111-Y110</f>
         <v>80.199999999999989</v>
       </c>
-      <c r="Y110">
-        <f>SQRT(X110)</f>
+      <c r="Z112">
+        <f>SQRT(Y112)</f>
         <v>8.9554452708952432</v>
       </c>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="B111" s="18">
-        <f>B102/B$109</f>
+    <row r="113" spans="3:30" x14ac:dyDescent="0.35">
+      <c r="C113" s="18">
+        <f>C104/C$111</f>
         <v>0.5</v>
       </c>
-      <c r="C111" s="18">
-        <f t="shared" ref="C111:I111" si="22">C102/C$109</f>
+      <c r="D113" s="18">
+        <f t="shared" ref="D113:J113" si="22">D104/D$111</f>
         <v>0.30534775347842924</v>
       </c>
-      <c r="D111" s="18">
+      <c r="E113" s="18">
         <f t="shared" si="22"/>
         <v>0.5</v>
       </c>
-      <c r="E111" s="18">
+      <c r="F113" s="18">
         <f t="shared" si="22"/>
         <v>-0.22360679774997896</v>
       </c>
-      <c r="F111" s="18">
+      <c r="G113" s="18">
         <f t="shared" si="22"/>
         <v>0.22360679774997894</v>
       </c>
-      <c r="G111" s="18"/>
-      <c r="H111" s="18"/>
-      <c r="I111" s="18">
+      <c r="H113" s="18"/>
+      <c r="I113" s="18"/>
+      <c r="J113" s="18">
         <f t="shared" si="22"/>
         <v>-0.10241085157359611</v>
       </c>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="B112" s="18">
-        <f t="shared" ref="B112:I115" si="23">B103/B$109</f>
+    <row r="114" spans="3:30" x14ac:dyDescent="0.35">
+      <c r="C114" s="18">
+        <f t="shared" ref="C114:J117" si="23">C105/C$111</f>
         <v>-0.5</v>
       </c>
-      <c r="C112" s="18">
+      <c r="D114" s="18">
         <f t="shared" si="23"/>
         <v>-0.80022169877105653</v>
       </c>
-      <c r="D112" s="18">
+      <c r="E114" s="18">
         <f t="shared" si="23"/>
         <v>-0.5</v>
       </c>
-      <c r="E112" s="18">
+      <c r="F114" s="18">
         <f t="shared" si="23"/>
         <v>-0.22360679774997896</v>
       </c>
-      <c r="F112" s="18">
+      <c r="G114" s="18">
         <f t="shared" si="23"/>
         <v>0.22360679774997894</v>
       </c>
-      <c r="G112" s="18"/>
-      <c r="H112" s="18"/>
-      <c r="I112" s="18">
+      <c r="H114" s="18"/>
+      <c r="I114" s="18"/>
+      <c r="J114" s="18">
         <f t="shared" si="23"/>
         <v>-0.35843798050758635</v>
       </c>
-      <c r="N112" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y112">
+      <c r="O114" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z114">
         <v>4</v>
       </c>
-      <c r="Z112">
+      <c r="AA114">
         <f>1/5</f>
         <v>0.2</v>
       </c>
-      <c r="AA112">
-        <f>SQRT(Z112)</f>
+      <c r="AB114">
+        <f>SQRT(AA114)</f>
         <v>0.44721359549995793</v>
       </c>
-      <c r="AB112">
-        <f>Y112*AA112</f>
+      <c r="AC114">
+        <f>Z114*AB114</f>
         <v>1.7888543819998317</v>
       </c>
     </row>
-    <row r="113" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="B113" s="18">
+    <row r="115" spans="3:30" x14ac:dyDescent="0.35">
+      <c r="C115" s="18">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="C113" s="18">
+      <c r="D115" s="18">
         <f t="shared" si="23"/>
         <v>-1.0529232878566681E-2</v>
       </c>
-      <c r="D113" s="18">
+      <c r="E115" s="18">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="E113" s="18">
+      <c r="F115" s="18">
         <f t="shared" si="23"/>
         <v>-0.22360679774997896</v>
       </c>
-      <c r="F113" s="18">
+      <c r="G115" s="18">
         <f t="shared" si="23"/>
         <v>0.22360679774997894</v>
       </c>
-      <c r="G113" s="18"/>
-      <c r="H113" s="18"/>
-      <c r="I113" s="18">
+      <c r="H115" s="18"/>
+      <c r="I115" s="18"/>
+      <c r="J115" s="18">
         <f t="shared" si="23"/>
         <v>-0.23042441604059125</v>
       </c>
-      <c r="O113">
-        <f>O114</f>
+      <c r="P115">
+        <f>P116</f>
         <v>2255</v>
       </c>
-      <c r="R113">
+      <c r="S115">
         <f>38^2</f>
         <v>1444</v>
       </c>
-      <c r="S113">
-        <f>R113-O113</f>
+      <c r="T115">
+        <f>S115-P115</f>
         <v>-811</v>
       </c>
-      <c r="T113">
-        <f>SQRT(-S113)</f>
+      <c r="U115">
+        <f>SQRT(-T115)</f>
         <v>28.478061731796284</v>
       </c>
-      <c r="W113">
+      <c r="X115">
         <v>4</v>
       </c>
-      <c r="X113">
+      <c r="Y115">
         <v>5</v>
       </c>
-      <c r="Y113">
-        <f>W113/X113</f>
+      <c r="Z115">
+        <f>X115/Y115</f>
         <v>0.8</v>
       </c>
-      <c r="Z113">
-        <f>SQRT(Y113)</f>
+      <c r="AA115">
+        <f>SQRT(Z115)</f>
         <v>0.89442719099991586</v>
       </c>
     </row>
-    <row r="114" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="B114" s="18">
+    <row r="116" spans="3:30" x14ac:dyDescent="0.35">
+      <c r="C116" s="18">
         <f t="shared" si="23"/>
         <v>0.5</v>
       </c>
-      <c r="C114" s="18">
+      <c r="D116" s="18">
         <f t="shared" si="23"/>
         <v>0.51593241104975984</v>
       </c>
-      <c r="D114" s="18">
+      <c r="E116" s="18">
         <f t="shared" si="23"/>
         <v>-0.5</v>
       </c>
-      <c r="E114" s="18">
+      <c r="F116" s="18">
         <f t="shared" si="23"/>
         <v>-0.22360679774997896</v>
       </c>
-      <c r="F114" s="18">
+      <c r="G116" s="18">
         <f t="shared" si="23"/>
         <v>0.22360679774997894</v>
       </c>
-      <c r="G114" s="18"/>
-      <c r="H114" s="18"/>
-      <c r="I114" s="18">
+      <c r="H116" s="18"/>
+      <c r="I116" s="18"/>
+      <c r="J116" s="18">
         <f t="shared" si="23"/>
         <v>-0.18775322788492621</v>
       </c>
-      <c r="N114">
+      <c r="O116">
         <f>2/5</f>
         <v>0.4</v>
       </c>
-      <c r="O114">
+      <c r="P116">
         <v>2255</v>
       </c>
-      <c r="P114">
-        <f>SQRT(O114)</f>
+      <c r="Q116">
+        <f>SQRT(P116)</f>
         <v>47.486840282335066</v>
       </c>
-      <c r="R114">
+      <c r="S116">
         <f>48^2</f>
         <v>2304</v>
       </c>
-      <c r="S114">
-        <f>R114-O114</f>
+      <c r="T116">
+        <f>S116-P116</f>
         <v>49</v>
       </c>
-      <c r="T114">
-        <f>SQRT(S114)</f>
+      <c r="U116">
+        <f>SQRT(T116)</f>
         <v>7</v>
       </c>
-      <c r="U114">
+      <c r="V116">
         <f>48^2-7^2</f>
         <v>2255</v>
       </c>
-      <c r="X114">
-        <f>SQRT(X113)</f>
+      <c r="Y116">
+        <f>SQRT(Y115)</f>
         <v>2.2360679774997898</v>
       </c>
-      <c r="Y114">
-        <f>X114/5</f>
+      <c r="Z116">
+        <f>Y116/5</f>
         <v>0.44721359549995798</v>
       </c>
     </row>
-    <row r="115" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="B115" s="18">
+    <row r="117" spans="3:30" x14ac:dyDescent="0.35">
+      <c r="C117" s="18">
         <f t="shared" si="23"/>
         <v>-0.5</v>
       </c>
-      <c r="C115" s="18">
+      <c r="D117" s="18">
         <f t="shared" si="23"/>
         <v>-1.0529232878566681E-2</v>
       </c>
-      <c r="D115" s="18">
+      <c r="E117" s="18">
         <f t="shared" si="23"/>
         <v>0.5</v>
       </c>
-      <c r="E115" s="18">
+      <c r="F117" s="18">
         <f t="shared" si="23"/>
         <v>0.89442719099991586</v>
       </c>
-      <c r="F115" s="18">
+      <c r="G117" s="18">
         <f t="shared" si="23"/>
         <v>-0.89442719099991597</v>
       </c>
-      <c r="G115" s="18"/>
-      <c r="H115" s="18"/>
-      <c r="I115" s="18">
+      <c r="H117" s="18"/>
+      <c r="I117" s="18"/>
+      <c r="J117" s="18">
         <f t="shared" si="23"/>
         <v>0.87902647600669992</v>
       </c>
-      <c r="P115">
-        <f>P114*2/5</f>
+      <c r="Q117">
+        <f>Q116*2/5</f>
         <v>18.994736112934028</v>
       </c>
-      <c r="S115">
-        <f>R114-S114</f>
+      <c r="T117">
+        <f>S116-T116</f>
         <v>2255</v>
       </c>
-      <c r="W115">
-        <f>S115*4</f>
+      <c r="X117">
+        <f>T117*4</f>
         <v>9020</v>
       </c>
-      <c r="X115">
-        <f>SQRT(W115)</f>
+      <c r="Y117">
+        <f>SQRT(X117)</f>
         <v>94.973680564670133</v>
       </c>
-      <c r="Z115">
+      <c r="AA117">
         <v>96</v>
       </c>
-      <c r="AA115">
-        <f>Z115^2</f>
+      <c r="AB117">
+        <f>AA117^2</f>
         <v>9216</v>
       </c>
-      <c r="AB115">
-        <f>AA115-W115</f>
+      <c r="AC117">
+        <f>AB117-X117</f>
         <v>196</v>
       </c>
-      <c r="AC115">
-        <f>SQRT(AB115)</f>
+      <c r="AD117">
+        <f>SQRT(AC117)</f>
         <v>14</v>
       </c>
     </row>
-    <row r="117" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="Z117" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA117">
+    <row r="119" spans="3:30" x14ac:dyDescent="0.35">
+      <c r="AA119" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB119">
         <f>90-14</f>
         <v>76</v>
       </c>
-      <c r="AB117">
-        <f>SQRT(AA117)</f>
+      <c r="AC119">
+        <f>SQRT(AB119)</f>
         <v>8.717797887081348</v>
       </c>
     </row>
-    <row r="118" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="L118">
+    <row r="120" spans="3:30" x14ac:dyDescent="0.35">
+      <c r="M120">
         <f>51/5</f>
         <v>10.199999999999999</v>
       </c>
-      <c r="N118">
+      <c r="O120">
         <v>45.2</v>
       </c>
-      <c r="O118">
-        <f>N118/5</f>
+      <c r="P120">
+        <f>O120/5</f>
         <v>9.0400000000000009</v>
       </c>
-      <c r="Q118">
+      <c r="R120">
         <f>9*25</f>
         <v>225</v>
       </c>
-      <c r="R118">
+      <c r="S120">
         <v>25</v>
       </c>
-      <c r="S118">
-        <f>Q118/R118</f>
+      <c r="T120">
+        <f>R120/S120</f>
         <v>9</v>
       </c>
-      <c r="U118">
+      <c r="V120">
         <v>2</v>
       </c>
-      <c r="V118">
+      <c r="W120">
         <f>4/5</f>
         <v>0.8</v>
       </c>
-      <c r="W118">
-        <f>SQRT(V118)</f>
+      <c r="X120">
+        <f>SQRT(W120)</f>
         <v>0.89442719099991586</v>
       </c>
-      <c r="X118">
-        <f>W118*U118</f>
+      <c r="Y120">
+        <f>X120*V120</f>
         <v>1.7888543819998317</v>
       </c>
-      <c r="Z118" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA118">
+      <c r="AA120" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB120">
         <f>90+14</f>
         <v>104</v>
       </c>
-      <c r="AB118">
-        <f>SQRT(AA118)</f>
+      <c r="AC120">
+        <f>SQRT(AB120)</f>
         <v>10.198039027185569</v>
       </c>
     </row>
-    <row r="120" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="H120">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="121" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="H121">
-        <v>5</v>
-      </c>
-      <c r="R121">
-        <f>Q118/5</f>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="122" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="H122">
-        <v>10</v>
-      </c>
+    <row r="122" spans="3:30" x14ac:dyDescent="0.35">
       <c r="I122">
         <v>2</v>
       </c>
-      <c r="K122">
+    </row>
+    <row r="123" spans="3:30" x14ac:dyDescent="0.35">
+      <c r="I123">
+        <v>5</v>
+      </c>
+      <c r="S123">
+        <f>R120/5</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="124" spans="3:30" x14ac:dyDescent="0.35">
+      <c r="I124">
+        <v>10</v>
+      </c>
+      <c r="J124">
         <v>2</v>
       </c>
-    </row>
-    <row r="123" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="F123">
+      <c r="L124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="3:30" x14ac:dyDescent="0.35">
+      <c r="G125">
         <v>-240</v>
       </c>
-      <c r="G123">
-        <f>ABS(F123)</f>
+      <c r="H125">
+        <f>ABS(G125)</f>
         <v>240</v>
       </c>
-      <c r="H123">
-        <f>$G123/H$122</f>
+      <c r="I125">
+        <f>$H125/I$124</f>
         <v>24</v>
       </c>
-      <c r="I123">
-        <f>$H123/I$122</f>
+      <c r="J125">
+        <f>$I125/J$124</f>
         <v>12</v>
       </c>
-      <c r="J123">
-        <f>I123^2</f>
+      <c r="K125">
+        <f>J125^2</f>
         <v>144</v>
       </c>
-      <c r="K123">
-        <f>I123/K$122</f>
+      <c r="L125">
+        <f>J125/L$124</f>
         <v>6</v>
       </c>
-      <c r="M123">
+      <c r="N125">
         <f>2^4*3*5</f>
         <v>240</v>
       </c>
-      <c r="N123" s="8" t="s">
+      <c r="O125" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q125">
+        <f>H125/10/2</f>
+        <v>12</v>
+      </c>
+      <c r="R125">
+        <f>Q125^2</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="126" spans="3:30" x14ac:dyDescent="0.35">
+      <c r="G126">
+        <v>-840</v>
+      </c>
+      <c r="H126">
+        <f t="shared" ref="H126:H129" si="24">ABS(G126)</f>
+        <v>840</v>
+      </c>
+      <c r="I126">
+        <f t="shared" ref="I126:I129" si="25">$H126/I$124</f>
         <v>84</v>
       </c>
-      <c r="P123">
-        <f>G123/10/2</f>
-        <v>12</v>
-      </c>
-      <c r="Q123">
-        <f>P123^2</f>
-        <v>144</v>
-      </c>
-    </row>
-    <row r="124" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="F124">
-        <v>-840</v>
-      </c>
-      <c r="G124">
-        <f t="shared" ref="G124:G127" si="24">ABS(F124)</f>
-        <v>840</v>
-      </c>
-      <c r="H124">
-        <f t="shared" ref="H124:H127" si="25">$G124/H$122</f>
-        <v>84</v>
-      </c>
-      <c r="I124">
-        <f t="shared" ref="I124:I127" si="26">$H124/I$122</f>
+      <c r="J126">
+        <f t="shared" ref="J126:J129" si="26">$I126/J$124</f>
         <v>42</v>
       </c>
-      <c r="J124">
-        <f t="shared" ref="J124:J127" si="27">I124^2</f>
+      <c r="K126">
+        <f t="shared" ref="K126:K129" si="27">J126^2</f>
         <v>1764</v>
       </c>
-      <c r="K124">
-        <f>I124/K$122</f>
+      <c r="L126">
+        <f>J126/L$124</f>
         <v>21</v>
       </c>
-      <c r="M124">
+      <c r="N126">
         <f>7*5*3*2^3</f>
         <v>840</v>
       </c>
-      <c r="N124" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="P124">
-        <f>G124/10/2</f>
+      <c r="O126" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q126">
+        <f>H126/10/2</f>
         <v>42</v>
       </c>
-      <c r="Q124">
-        <f t="shared" ref="Q124:Q127" si="28">P124^2</f>
+      <c r="R126">
+        <f t="shared" ref="R126:R129" si="28">Q126^2</f>
         <v>1764</v>
       </c>
     </row>
-    <row r="125" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="F125">
+    <row r="127" spans="3:30" x14ac:dyDescent="0.35">
+      <c r="G127">
         <v>-540</v>
       </c>
-      <c r="G125">
+      <c r="H127">
         <f t="shared" si="24"/>
         <v>540</v>
       </c>
-      <c r="H125">
+      <c r="I127">
         <f t="shared" si="25"/>
         <v>54</v>
       </c>
-      <c r="I125">
+      <c r="J127">
         <f t="shared" si="26"/>
         <v>27</v>
       </c>
-      <c r="J125">
+      <c r="K127">
         <f t="shared" si="27"/>
         <v>729</v>
       </c>
-      <c r="M125">
+      <c r="N127">
         <f>5*3^3*2^2</f>
         <v>540</v>
       </c>
-      <c r="N125" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="P125">
-        <f>G125/10/2</f>
+      <c r="O127" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q127">
+        <f>H127/10/2</f>
         <v>27</v>
       </c>
-      <c r="Q125">
+      <c r="R127">
         <f t="shared" si="28"/>
         <v>729</v>
       </c>
     </row>
-    <row r="126" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="F126">
+    <row r="128" spans="3:30" x14ac:dyDescent="0.35">
+      <c r="G128">
         <v>-440</v>
       </c>
-      <c r="G126">
+      <c r="H128">
         <f t="shared" si="24"/>
         <v>440</v>
       </c>
-      <c r="H126">
+      <c r="I128">
         <f t="shared" si="25"/>
         <v>44</v>
       </c>
-      <c r="I126">
+      <c r="J128">
         <f t="shared" si="26"/>
         <v>22</v>
       </c>
-      <c r="J126">
+      <c r="K128">
         <f t="shared" si="27"/>
         <v>484</v>
       </c>
-      <c r="K126">
-        <f>I126/K$122</f>
+      <c r="L128">
+        <f>J128/L$124</f>
         <v>11</v>
       </c>
-      <c r="M126">
+      <c r="N128">
         <f>11*5*2^3</f>
         <v>440</v>
       </c>
-      <c r="N126" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="P126">
-        <f>G126/10/2</f>
+      <c r="O128" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q128">
+        <f>H128/10/2</f>
         <v>22</v>
       </c>
-      <c r="Q126">
+      <c r="R128">
         <f t="shared" si="28"/>
         <v>484</v>
       </c>
     </row>
-    <row r="127" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="F127">
+    <row r="129" spans="6:25" x14ac:dyDescent="0.35">
+      <c r="G129">
         <v>2060</v>
       </c>
-      <c r="G127">
+      <c r="H129">
         <f t="shared" si="24"/>
         <v>2060</v>
       </c>
-      <c r="H127">
+      <c r="I129">
         <f t="shared" si="25"/>
         <v>206</v>
       </c>
-      <c r="I127">
+      <c r="J129">
         <f t="shared" si="26"/>
         <v>103</v>
       </c>
-      <c r="J127">
+      <c r="K129">
         <f t="shared" si="27"/>
         <v>10609</v>
       </c>
-      <c r="M127">
+      <c r="N129">
         <f>103*5*2^2</f>
         <v>2060</v>
       </c>
-      <c r="N127" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="P127">
-        <f>G127/10/2</f>
+      <c r="O129" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q129">
+        <f>H129/10/2</f>
         <v>103</v>
       </c>
-      <c r="Q127">
+      <c r="R129">
         <f t="shared" si="28"/>
         <v>10609</v>
       </c>
     </row>
-    <row r="128" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="W128">
+    <row r="130" spans="6:25" x14ac:dyDescent="0.35">
+      <c r="X130">
         <v>2</v>
       </c>
-      <c r="X128">
-        <f>SQRT(W128)</f>
+      <c r="Y130">
+        <f>SQRT(X130)</f>
         <v>1.4142135623730951</v>
       </c>
     </row>
-    <row r="129" spans="5:24" x14ac:dyDescent="0.35">
-      <c r="J129">
-        <f>SUM(J123:J128)</f>
+    <row r="131" spans="6:25" x14ac:dyDescent="0.35">
+      <c r="K131">
+        <f>SUM(K125:K130)</f>
         <v>13730</v>
       </c>
-      <c r="P129">
-        <f>SUM(P123:P128)</f>
+      <c r="Q131">
+        <f>SUM(Q125:Q130)</f>
         <v>206</v>
       </c>
-      <c r="Q129">
-        <f>SUM(Q123:Q128)</f>
+      <c r="R131">
+        <f>SUM(R125:R130)</f>
         <v>13730</v>
       </c>
-      <c r="W129">
+      <c r="X131">
         <v>3</v>
       </c>
-      <c r="X129">
-        <f>SQRT(W129)</f>
+      <c r="Y131">
+        <f>SQRT(X131)</f>
         <v>1.7320508075688772</v>
       </c>
     </row>
-    <row r="130" spans="5:24" x14ac:dyDescent="0.35">
-      <c r="J130">
-        <f>SQRT(J129)</f>
+    <row r="132" spans="6:25" x14ac:dyDescent="0.35">
+      <c r="K132">
+        <f>SQRT(K131)</f>
         <v>117.17508267545622</v>
       </c>
-      <c r="R130">
+      <c r="S132">
         <f>2*5*1373</f>
         <v>13730</v>
       </c>
-      <c r="S130">
-        <f>SQRT(R130)</f>
+      <c r="T132">
+        <f>SQRT(S132)</f>
         <v>117.17508267545622</v>
       </c>
     </row>
-    <row r="131" spans="5:24" x14ac:dyDescent="0.35">
-      <c r="W131">
-        <f>W128/W129</f>
+    <row r="133" spans="6:25" x14ac:dyDescent="0.35">
+      <c r="X133">
+        <f>X130/X131</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="X131">
-        <f>X128/X129</f>
+      <c r="Y133">
+        <f>Y130/Y131</f>
         <v>0.81649658092772615</v>
       </c>
     </row>
-    <row r="132" spans="5:24" x14ac:dyDescent="0.35">
-      <c r="F132">
-        <f>G132*H132</f>
+    <row r="134" spans="6:25" x14ac:dyDescent="0.35">
+      <c r="G134">
+        <f>H134*I134</f>
         <v>117</v>
       </c>
-      <c r="G132">
+      <c r="H134">
         <v>13</v>
       </c>
-      <c r="H132">
-        <f>I132/13</f>
+      <c r="I134">
+        <f>J134/13</f>
         <v>9</v>
       </c>
-      <c r="I132">
+      <c r="J134">
         <v>117</v>
       </c>
-      <c r="J132">
-        <f>I132^2</f>
+      <c r="K134">
+        <f>J134^2</f>
         <v>13689</v>
       </c>
-      <c r="K132">
+      <c r="L134">
         <v>41</v>
       </c>
-      <c r="L132">
-        <f>K132+J132</f>
+      <c r="M134">
+        <f>L134+K134</f>
         <v>13730</v>
       </c>
-      <c r="M132">
-        <f>L132/J132</f>
+      <c r="N134">
+        <f>M134/K134</f>
         <v>1.0029951055592081</v>
       </c>
-      <c r="N132">
-        <f>SQRT(M132)</f>
+      <c r="O134">
+        <f>SQRT(N134)</f>
         <v>1.0014964331235574</v>
       </c>
-      <c r="O132">
+      <c r="P134">
         <v>2340</v>
       </c>
-      <c r="P132">
-        <f>O132*N132</f>
+      <c r="Q134">
+        <f>P134*O134</f>
         <v>2343.5016535091245</v>
       </c>
-      <c r="W132">
-        <f>SQRT(W131)</f>
+      <c r="X134">
+        <f>SQRT(X133)</f>
         <v>0.81649658092772603</v>
       </c>
     </row>
-    <row r="133" spans="5:24" x14ac:dyDescent="0.35">
-      <c r="I133">
-        <f>I132*20</f>
+    <row r="135" spans="6:25" x14ac:dyDescent="0.35">
+      <c r="J135">
+        <f>J134*20</f>
         <v>2340</v>
       </c>
-      <c r="J133">
-        <f>J132-J129</f>
+      <c r="K135">
+        <f>K134-K131</f>
         <v>-41</v>
       </c>
     </row>
-    <row r="135" spans="5:24" x14ac:dyDescent="0.35">
-      <c r="H135">
-        <f>I135/2</f>
+    <row r="137" spans="6:25" x14ac:dyDescent="0.35">
+      <c r="I137">
+        <f>J137/2</f>
         <v>59</v>
       </c>
-      <c r="I135">
+      <c r="J137">
         <v>118</v>
       </c>
-      <c r="J135">
-        <f>I135^2</f>
+      <c r="K137">
+        <f>J137^2</f>
         <v>13924</v>
       </c>
-      <c r="K135">
-        <f>J135-J129</f>
+      <c r="L137">
+        <f>K137-K131</f>
         <v>194</v>
       </c>
-      <c r="L135">
-        <f>K135/2</f>
+      <c r="M137">
+        <f>L137/2</f>
         <v>97</v>
       </c>
-      <c r="M135">
-        <f>L135/7</f>
+      <c r="N137">
+        <f>M137/7</f>
         <v>13.857142857142858</v>
       </c>
     </row>
-    <row r="136" spans="5:24" x14ac:dyDescent="0.35">
-      <c r="I136">
-        <f>I135*20</f>
+    <row r="138" spans="6:25" x14ac:dyDescent="0.35">
+      <c r="J138">
+        <f>J137*20</f>
         <v>2360</v>
       </c>
     </row>
-    <row r="139" spans="5:24" x14ac:dyDescent="0.35">
-      <c r="E139">
+    <row r="141" spans="6:25" x14ac:dyDescent="0.35">
+      <c r="F141">
         <v>19</v>
       </c>
-      <c r="F139">
+      <c r="G141">
         <v>1804</v>
       </c>
-      <c r="H139">
-        <f>SQRT(F139/F140)*E139</f>
+      <c r="I141">
+        <f>SQRT(G141/G142)*F141</f>
         <v>18.994736112934024</v>
       </c>
-      <c r="J139">
+      <c r="K141">
         <v>9020</v>
       </c>
-      <c r="K139">
-        <f>SQRT(J139)</f>
+      <c r="L141">
+        <f>SQRT(K141)</f>
         <v>94.973680564670133</v>
       </c>
     </row>
-    <row r="140" spans="5:24" x14ac:dyDescent="0.35">
-      <c r="F140">
+    <row r="142" spans="6:25" x14ac:dyDescent="0.35">
+      <c r="G142">
         <v>1805</v>
       </c>
-      <c r="J140">
+      <c r="K142">
         <v>25</v>
       </c>
-      <c r="N140">
+      <c r="O142">
         <f>2 * 5 * 7 * 7 * 7 * 7</f>
         <v>24010</v>
       </c>
     </row>
-    <row r="141" spans="5:24" x14ac:dyDescent="0.35">
-      <c r="J141">
-        <f>J139/J140</f>
+    <row r="143" spans="6:25" x14ac:dyDescent="0.35">
+      <c r="K143">
+        <f>K141/K142</f>
         <v>360.8</v>
       </c>
     </row>
-    <row r="142" spans="5:24" x14ac:dyDescent="0.35">
-      <c r="M142">
+    <row r="144" spans="6:25" x14ac:dyDescent="0.35">
+      <c r="N144">
         <v>7</v>
       </c>
-      <c r="N142">
-        <f>M142^2</f>
+      <c r="O144">
+        <f>N144^2</f>
         <v>49</v>
       </c>
-      <c r="O142">
-        <f>N142^2</f>
+      <c r="P144">
+        <f>O144^2</f>
         <v>2401</v>
       </c>
     </row>
-    <row r="148" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="D148">
+    <row r="150" spans="4:8" x14ac:dyDescent="0.35">
+      <c r="E150">
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="D149">
+    <row r="151" spans="4:8" x14ac:dyDescent="0.35">
+      <c r="E151">
         <v>5</v>
       </c>
-      <c r="E149">
-        <f>SQRT(D149)</f>
+      <c r="F151">
+        <f>SQRT(E151)</f>
         <v>2.2360679774997898</v>
       </c>
     </row>
-    <row r="150" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="D150">
-        <f>D148/D149</f>
+    <row r="152" spans="4:8" x14ac:dyDescent="0.35">
+      <c r="E152">
+        <f>E150/E151</f>
         <v>0.4</v>
       </c>
-      <c r="E150">
-        <f>D150*E149</f>
+      <c r="F152">
+        <f>E152*F151</f>
         <v>0.89442719099991597</v>
       </c>
     </row>
-    <row r="151" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C151">
+    <row r="153" spans="4:8" x14ac:dyDescent="0.35">
+      <c r="D153">
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C152">
+    <row r="154" spans="4:8" x14ac:dyDescent="0.35">
+      <c r="D154">
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C153">
-        <f>C151/C152</f>
+    <row r="155" spans="4:8" x14ac:dyDescent="0.35">
+      <c r="D155">
+        <f>D153/D154</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="154" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C154">
-        <f>SQRT(C153)</f>
+    <row r="156" spans="4:8" x14ac:dyDescent="0.35">
+      <c r="D156">
+        <f>SQRT(D155)</f>
         <v>0.89442719099991586</v>
       </c>
-      <c r="E154">
+      <c r="F156">
         <v>20</v>
       </c>
     </row>
-    <row r="155" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="E155">
-        <f>SQRT(E154)</f>
+    <row r="157" spans="4:8" x14ac:dyDescent="0.35">
+      <c r="F157">
+        <f>SQRT(F156)</f>
         <v>4.4721359549995796</v>
       </c>
-      <c r="G155">
+      <c r="H157">
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="G156">
-        <f>G155/E155</f>
+    <row r="158" spans="4:8" x14ac:dyDescent="0.35">
+      <c r="H158">
+        <f>H157/F157</f>
         <v>0.22360679774997896</v>
       </c>
     </row>
@@ -5596,7 +5978,7 @@
   <sheetData>
     <row r="1" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -5611,7 +5993,7 @@
         <v>7</v>
       </c>
       <c r="L1" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
@@ -5689,7 +6071,7 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C8">
         <f>AVERAGE(C3:C6)</f>
@@ -5726,7 +6108,7 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C10">
         <f>C3-C$8</f>
@@ -5923,7 +6305,7 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C21">
         <f>SQRT(C20)</f>
@@ -5944,7 +6326,7 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C23" s="32">
         <f>C10/C$21</f>
@@ -6098,7 +6480,7 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C28" s="32">
         <f>SUM(C23:C27)</f>
@@ -6736,7 +7118,7 @@
         <v>2</v>
       </c>
       <c r="O44" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.35">
@@ -7494,22 +7876,22 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="G17" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="H17" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.35">
@@ -8941,34 +9323,34 @@
   <sheetData>
     <row r="2" spans="7:26" x14ac:dyDescent="0.35">
       <c r="U2" s="26" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="V2" s="26"/>
       <c r="W2" s="26"/>
     </row>
     <row r="3" spans="7:26" x14ac:dyDescent="0.35">
       <c r="P3" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>95</v>
+      </c>
+      <c r="R3" t="s">
+        <v>97</v>
+      </c>
+      <c r="S3" t="s">
+        <v>100</v>
+      </c>
+      <c r="U3" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="Q3" t="s">
-        <v>105</v>
-      </c>
-      <c r="R3" t="s">
-        <v>107</v>
-      </c>
-      <c r="S3" t="s">
-        <v>110</v>
-      </c>
-      <c r="U3" s="26" t="s">
-        <v>116</v>
-      </c>
       <c r="V3" s="26" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="W3" s="26"/>
       <c r="Y3" s="33"/>
       <c r="Z3" s="33" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="7:26" x14ac:dyDescent="0.35">
@@ -9158,7 +9540,7 @@
     </row>
     <row r="9" spans="7:26" x14ac:dyDescent="0.35">
       <c r="P9" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="R9">
         <f>SUM(R4:R7)</f>
@@ -9170,7 +9552,7 @@
         <v>1.9922026100638293</v>
       </c>
       <c r="W9" s="34" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="X9" s="33">
         <f>SUM(X4:X7)</f>
@@ -9187,14 +9569,14 @@
     </row>
     <row r="10" spans="7:26" x14ac:dyDescent="0.35">
       <c r="P10" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="R10">
         <f>SQRT(R9)</f>
         <v>0.8660254037844386</v>
       </c>
       <c r="W10" s="34" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="X10" s="33">
         <f>SQRT(X9)</f>
@@ -9203,13 +9585,13 @@
     </row>
     <row r="12" spans="7:26" x14ac:dyDescent="0.35">
       <c r="Q12" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="S12" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="W12" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="X12">
         <f>SQRT(2)</f>
